--- a/KURIKULUM2026_REVISI/005_STRUKTUR_KURIKULUM_8_SEMESTER_DAN_PEMINATAN.xlsx
+++ b/KURIKULUM2026_REVISI/005_STRUKTUR_KURIKULUM_8_SEMESTER_DAN_PEMINATAN.xlsx
@@ -708,17 +708,17 @@
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
-          <t>14 MK</t>
+          <t>13 MK</t>
         </is>
       </c>
       <c r="C10" s="10" t="inlineStr">
         <is>
-          <t>38 SKS</t>
+          <t>36 SKS</t>
         </is>
       </c>
       <c r="D10" s="10" t="inlineStr">
         <is>
-          <t>26,0%</t>
+          <t>24,7%</t>
         </is>
       </c>
     </row>
@@ -730,17 +730,17 @@
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>27 MK</t>
+          <t>28 MK</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>77 SKS</t>
+          <t>79 SKS</t>
         </is>
       </c>
       <c r="D11" s="8" t="inlineStr">
         <is>
-          <t>52,7%</t>
+          <t>54,1%</t>
         </is>
       </c>
     </row>
@@ -939,7 +939,7 @@
       </c>
       <c r="B21" s="9" t="inlineStr">
         <is>
-          <t>AI/ML, Cloud &amp; Keamanan</t>
+          <t>AI/ML, NLP, Cloud &amp; Keamanan</t>
         </is>
       </c>
       <c r="C21" s="10" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="E21" s="9" t="inlineStr">
         <is>
-          <t>Machine Learning, DW/BI, Web Back, Cloud</t>
+          <t>ML, NLP/IR, DW/BI, Web Back, Cloud, Probstat</t>
         </is>
       </c>
     </row>
@@ -1089,7 +1089,7 @@
       </c>
       <c r="E26" s="7" t="inlineStr">
         <is>
-          <t>**Standar Sarjana Terapan Komputasi**</t>
+          <t>**Standar Sarjana S1 Komputasi**</t>
         </is>
       </c>
     </row>
@@ -2212,7 +2212,7 @@
     <row r="63" ht="20" customHeight="1">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>SEMESTER 4 (21 SKS) — Penguatan Core AI/ML, DW &amp; Cloud</t>
+          <t>SEMESTER 4 (21 SKS) — Penguatan Core AI/ML, NLP, DW &amp; Cloud</t>
         </is>
       </c>
       <c r="B63" s="4" t="n"/>
@@ -2304,17 +2304,17 @@
       </c>
       <c r="B66" s="9" t="inlineStr">
         <is>
-          <t>`STI-402`</t>
+          <t>`STI-403`</t>
         </is>
       </c>
       <c r="C66" s="9" t="inlineStr">
         <is>
-          <t>Data Warehouse &amp; Business Intelligence</t>
+          <t>Pengantar NLP &amp; Information Retrieval</t>
         </is>
       </c>
       <c r="D66" s="10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E66" s="9" t="inlineStr">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="G66" s="9" t="inlineStr">
         <is>
-          <t>`FST-207`</t>
+          <t>`STI-302`</t>
         </is>
       </c>
     </row>
@@ -2341,12 +2341,12 @@
       </c>
       <c r="B67" s="7" t="inlineStr">
         <is>
-          <t>`STI-407`</t>
+          <t>`STI-402`</t>
         </is>
       </c>
       <c r="C67" s="7" t="inlineStr">
         <is>
-          <t>Web Back End Development</t>
+          <t>Data Warehouse &amp; Business Intelligence</t>
         </is>
       </c>
       <c r="D67" s="8" t="inlineStr">
@@ -2366,7 +2366,7 @@
       </c>
       <c r="G67" s="7" t="inlineStr">
         <is>
-          <t>`FST-207`, `STI-306`</t>
+          <t>`FST-207`</t>
         </is>
       </c>
     </row>
@@ -2378,12 +2378,12 @@
       </c>
       <c r="B68" s="9" t="inlineStr">
         <is>
-          <t>`STI-404`</t>
+          <t>`STI-407`</t>
         </is>
       </c>
       <c r="C68" s="9" t="inlineStr">
         <is>
-          <t>Komputasi Awan (Cloud Computing)</t>
+          <t>Web Back End Development</t>
         </is>
       </c>
       <c r="D68" s="10" t="inlineStr">
@@ -2393,7 +2393,7 @@
       </c>
       <c r="E68" s="9" t="inlineStr">
         <is>
-          <t>Teori</t>
+          <t>+P</t>
         </is>
       </c>
       <c r="F68" s="9" t="inlineStr">
@@ -2403,7 +2403,7 @@
       </c>
       <c r="G68" s="9" t="inlineStr">
         <is>
-          <t>`STI-307`, `STI-305`</t>
+          <t>`FST-207`, `STI-306`</t>
         </is>
       </c>
     </row>
@@ -2415,17 +2415,17 @@
       </c>
       <c r="B69" s="7" t="inlineStr">
         <is>
-          <t>`STI-405`</t>
+          <t>`STI-404`</t>
         </is>
       </c>
       <c r="C69" s="7" t="inlineStr">
         <is>
-          <t>Dasar Keamanan Informasi</t>
+          <t>Komputasi Awan (Cloud Computing)</t>
         </is>
       </c>
       <c r="D69" s="8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E69" s="7" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="G69" s="7" t="inlineStr">
         <is>
-          <t>`STI-307`</t>
+          <t>`STI-307`, `STI-305`</t>
         </is>
       </c>
     </row>
@@ -2452,17 +2452,17 @@
       </c>
       <c r="B70" s="9" t="inlineStr">
         <is>
-          <t>`FST-408`</t>
+          <t>`STI-405`</t>
         </is>
       </c>
       <c r="C70" s="9" t="inlineStr">
         <is>
-          <t>Probabilitas dan Statistika</t>
+          <t>Dasar Keamanan Informasi</t>
         </is>
       </c>
       <c r="D70" s="10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E70" s="9" t="inlineStr">
@@ -2472,12 +2472,12 @@
       </c>
       <c r="F70" s="9" t="inlineStr">
         <is>
-          <t>FSTI</t>
+          <t>Core STI</t>
         </is>
       </c>
       <c r="G70" s="9" t="inlineStr">
         <is>
-          <t>`STI-102`</t>
+          <t>`STI-307`</t>
         </is>
       </c>
     </row>
@@ -2489,17 +2489,17 @@
       </c>
       <c r="B71" s="7" t="inlineStr">
         <is>
-          <t>`FST-409`</t>
+          <t>`FST-408`</t>
         </is>
       </c>
       <c r="C71" s="7" t="inlineStr">
         <is>
-          <t>Manajemen Sains &amp; Riset Operasi</t>
+          <t>Probabilitas dan Statistika</t>
         </is>
       </c>
       <c r="D71" s="8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E71" s="7" t="inlineStr">
@@ -2514,7 +2514,7 @@
       </c>
       <c r="G71" s="7" t="inlineStr">
         <is>
-          <t>`STI-202`</t>
+          <t>`STI-102`</t>
         </is>
       </c>
     </row>
@@ -4001,7 +4001,7 @@
       </c>
       <c r="F120" s="9" t="inlineStr">
         <is>
-          <t>Tahap Penguatan Core AI/ML, DW &amp; Cloud</t>
+          <t>Tahap Penguatan Core AI/ML, NLP &amp; Cloud</t>
         </is>
       </c>
     </row>

--- a/KURIKULUM2026_REVISI/005_STRUKTUR_KURIKULUM_8_SEMESTER_DAN_PEMINATAN.xlsx
+++ b/KURIKULUM2026_REVISI/005_STRUKTUR_KURIKULUM_8_SEMESTER_DAN_PEMINATAN.xlsx
@@ -1097,7 +1097,7 @@
     <row r="28" ht="20" customHeight="1">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>SEMESTER 1 (19 SKS) — Fondasi Sains, Algoritma &amp; MKWU</t>
+          <t>SEMESTER 1 (19 SKS) — Fondasi Sains, Algoritma, Arsitektur STI &amp; MKWU</t>
         </is>
       </c>
       <c r="B28" s="4" t="n"/>
@@ -1152,27 +1152,27 @@
       </c>
       <c r="B30" s="7" t="inlineStr">
         <is>
-          <t>`STI-101`</t>
+          <t>`FST-101`</t>
         </is>
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
-          <t>Algoritma dan Pemrograman</t>
+          <t>Dasar Teknologi Digital</t>
         </is>
       </c>
       <c r="D30" s="8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E30" s="7" t="inlineStr">
         <is>
-          <t>+P</t>
+          <t>Teori</t>
         </is>
       </c>
       <c r="F30" s="7" t="inlineStr">
         <is>
-          <t>Core STI</t>
+          <t>FSTI</t>
         </is>
       </c>
       <c r="G30" s="7" t="inlineStr">
@@ -1189,12 +1189,12 @@
       </c>
       <c r="B31" s="9" t="inlineStr">
         <is>
-          <t>`STI-102`</t>
+          <t>`FST-102`</t>
         </is>
       </c>
       <c r="C31" s="9" t="inlineStr">
         <is>
-          <t>Kalkulus dan Aljabar Linier</t>
+          <t>Algoritma dan Pemrograman</t>
         </is>
       </c>
       <c r="D31" s="10" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="E31" s="9" t="inlineStr">
         <is>
-          <t>Teori</t>
+          <t>+P</t>
         </is>
       </c>
       <c r="F31" s="9" t="inlineStr">
         <is>
-          <t>Core STI</t>
+          <t>FSTI</t>
         </is>
       </c>
       <c r="G31" s="9" t="inlineStr">
@@ -1226,17 +1226,17 @@
       </c>
       <c r="B32" s="7" t="inlineStr">
         <is>
-          <t>`STI-103`</t>
+          <t>`STI-101`</t>
         </is>
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
-          <t>Logika Informatika dan Matematika Diskrit</t>
+          <t>Pengantar Sistem dan Teknologi Informasi</t>
         </is>
       </c>
       <c r="D32" s="8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E32" s="7" t="inlineStr">
@@ -1263,17 +1263,17 @@
       </c>
       <c r="B33" s="9" t="inlineStr">
         <is>
-          <t>`STI-104`</t>
-        </is>
-      </c>
-      <c r="C33" s="9" t="inlineStr">
-        <is>
-          <t>Pengantar Sistem dan Teknologi Informasi</t>
+          <t>`STI-102`</t>
+        </is>
+      </c>
+      <c r="C33" s="10" t="inlineStr">
+        <is>
+          <t>Kalkulus</t>
         </is>
       </c>
       <c r="D33" s="10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E33" s="9" t="inlineStr">
@@ -1300,17 +1300,17 @@
       </c>
       <c r="B34" s="7" t="inlineStr">
         <is>
-          <t>`MKU-101`</t>
-        </is>
-      </c>
-      <c r="C34" s="8" t="inlineStr">
-        <is>
-          <t>Agama I</t>
+          <t>`STI-103`</t>
+        </is>
+      </c>
+      <c r="C34" s="7" t="inlineStr">
+        <is>
+          <t>Arsitektur dan Organisasi Sistem Teknologi Informasi</t>
         </is>
       </c>
       <c r="D34" s="8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E34" s="7" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="F34" s="7" t="inlineStr">
         <is>
-          <t>MKWU</t>
+          <t>Core STI</t>
         </is>
       </c>
       <c r="G34" s="7" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="B35" s="9" t="inlineStr">
         <is>
-          <t>`MKU-102`</t>
-        </is>
-      </c>
-      <c r="C35" s="9" t="inlineStr">
-        <is>
-          <t>Pancasila</t>
+          <t>`MKU-101`</t>
+        </is>
+      </c>
+      <c r="C35" s="10" t="inlineStr">
+        <is>
+          <t>Agama I</t>
         </is>
       </c>
       <c r="D35" s="10" t="inlineStr">
@@ -1374,12 +1374,12 @@
       </c>
       <c r="B36" s="7" t="inlineStr">
         <is>
-          <t>`MKU-103`</t>
+          <t>`MKU-102`</t>
         </is>
       </c>
       <c r="C36" s="7" t="inlineStr">
         <is>
-          <t>Bahasa Indonesia</t>
+          <t>Pancasila</t>
         </is>
       </c>
       <c r="D36" s="8" t="inlineStr">
@@ -1411,12 +1411,12 @@
       </c>
       <c r="B37" s="9" t="inlineStr">
         <is>
-          <t>`MKU-104`</t>
+          <t>`MKU-103`</t>
         </is>
       </c>
       <c r="C37" s="9" t="inlineStr">
         <is>
-          <t>Bahasa Inggris Komunikasi Saintifik</t>
+          <t>Bahasa Indonesia</t>
         </is>
       </c>
       <c r="D37" s="10" t="inlineStr">
@@ -1481,7 +1481,7 @@
     <row r="40" ht="20" customHeight="1">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>SEMESTER 2 (20 SKS) — Fondasi Data, Matdis, OOP &amp; Etika</t>
+          <t>SEMESTER 2 (20 SKS) — Fondasi Data, Matdis &amp; Logika, Aljabar &amp; Etika</t>
         </is>
       </c>
       <c r="B40" s="4" t="n"/>
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C42" s="7" t="inlineStr">
         <is>
-          <t>Struktur Data dan Algoritma Lanjut</t>
+          <t>Matematika Diskrit dan Logika</t>
         </is>
       </c>
       <c r="D42" s="8" t="inlineStr">
@@ -1551,7 +1551,7 @@
       </c>
       <c r="E42" s="7" t="inlineStr">
         <is>
-          <t>+P</t>
+          <t>Teori</t>
         </is>
       </c>
       <c r="F42" s="7" t="inlineStr">
@@ -1561,7 +1561,7 @@
       </c>
       <c r="G42" s="7" t="inlineStr">
         <is>
-          <t>`STI-101`</t>
+          <t>`STI-103`</t>
         </is>
       </c>
     </row>
@@ -1578,7 +1578,7 @@
       </c>
       <c r="C43" s="9" t="inlineStr">
         <is>
-          <t>Pemrograman Berorientasi Objek</t>
+          <t>Aljabar Linear dan Matriks</t>
         </is>
       </c>
       <c r="D43" s="10" t="inlineStr">
@@ -1588,7 +1588,7 @@
       </c>
       <c r="E43" s="9" t="inlineStr">
         <is>
-          <t>+P</t>
+          <t>Teori</t>
         </is>
       </c>
       <c r="F43" s="9" t="inlineStr">
@@ -1598,7 +1598,7 @@
       </c>
       <c r="G43" s="9" t="inlineStr">
         <is>
-          <t>`STI-101`</t>
+          <t>`STI-102`</t>
         </is>
       </c>
     </row>
@@ -1610,12 +1610,12 @@
       </c>
       <c r="B44" s="7" t="inlineStr">
         <is>
-          <t>`FST-207`</t>
+          <t>`FST-203`</t>
         </is>
       </c>
       <c r="C44" s="7" t="inlineStr">
         <is>
-          <t>Sistem Basis Data</t>
+          <t>Struktur Data dan Algoritma</t>
         </is>
       </c>
       <c r="D44" s="8" t="inlineStr">
@@ -1635,7 +1635,7 @@
       </c>
       <c r="G44" s="7" t="inlineStr">
         <is>
-          <t>`STI-101`</t>
+          <t>`FST-102`</t>
         </is>
       </c>
     </row>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="B45" s="9" t="inlineStr">
         <is>
-          <t>`STI-203`</t>
+          <t>`FST-204`</t>
         </is>
       </c>
       <c r="C45" s="9" t="inlineStr">
         <is>
-          <t>Matematika Diskrit Lanjut</t>
+          <t>Pengantar Kecerdasan Artifisial &amp; Data</t>
         </is>
       </c>
       <c r="D45" s="10" t="inlineStr">
@@ -1667,12 +1667,12 @@
       </c>
       <c r="F45" s="9" t="inlineStr">
         <is>
-          <t>Core STI</t>
+          <t>FSTI</t>
         </is>
       </c>
       <c r="G45" s="9" t="inlineStr">
         <is>
-          <t>`STI-103`</t>
+          <t>`FST-101`</t>
         </is>
       </c>
     </row>
@@ -1684,12 +1684,12 @@
       </c>
       <c r="B46" s="7" t="inlineStr">
         <is>
-          <t>`STI-204`</t>
+          <t>`FST-205`</t>
         </is>
       </c>
       <c r="C46" s="7" t="inlineStr">
         <is>
-          <t>Aljabar Linear Terapan &amp; Matriks</t>
+          <t>Basic English for IT</t>
         </is>
       </c>
       <c r="D46" s="8" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="F46" s="7" t="inlineStr">
         <is>
-          <t>Core STI</t>
+          <t>FSTI</t>
         </is>
       </c>
       <c r="G46" s="7" t="inlineStr">
         <is>
-          <t>`STI-102`</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -1721,12 +1721,12 @@
       </c>
       <c r="B47" s="9" t="inlineStr">
         <is>
-          <t>`STI-205`</t>
+          <t>`FST-206`</t>
         </is>
       </c>
       <c r="C47" s="9" t="inlineStr">
         <is>
-          <t>Etika Profesi &amp; Hukum Siber</t>
+          <t>Etika Profesi &amp; Hukum Digital</t>
         </is>
       </c>
       <c r="D47" s="10" t="inlineStr">
@@ -1741,7 +1741,7 @@
       </c>
       <c r="F47" s="9" t="inlineStr">
         <is>
-          <t>Core STI</t>
+          <t>FSTI</t>
         </is>
       </c>
       <c r="G47" s="9" t="inlineStr">
@@ -1758,32 +1758,32 @@
       </c>
       <c r="B48" s="7" t="inlineStr">
         <is>
-          <t>`MKU-204`</t>
+          <t>`FST-207`</t>
         </is>
       </c>
       <c r="C48" s="7" t="inlineStr">
         <is>
-          <t>Kewirausahaan I</t>
+          <t>Sistem Basis Data</t>
         </is>
       </c>
       <c r="D48" s="8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E48" s="7" t="inlineStr">
         <is>
-          <t>Teori</t>
+          <t>+P</t>
         </is>
       </c>
       <c r="F48" s="7" t="inlineStr">
         <is>
-          <t>MKWU</t>
+          <t>FSTI</t>
         </is>
       </c>
       <c r="G48" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>`FST-102`</t>
         </is>
       </c>
     </row>
@@ -1795,17 +1795,17 @@
       </c>
       <c r="B49" s="9" t="inlineStr">
         <is>
-          <t>`FST-208`</t>
+          <t>`MKU-204`</t>
         </is>
       </c>
       <c r="C49" s="9" t="inlineStr">
         <is>
-          <t>Statistika Dasar</t>
+          <t>Kewirausahaan I</t>
         </is>
       </c>
       <c r="D49" s="10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E49" s="9" t="inlineStr">
@@ -1815,12 +1815,12 @@
       </c>
       <c r="F49" s="9" t="inlineStr">
         <is>
-          <t>FSTI</t>
+          <t>MKWU</t>
         </is>
       </c>
       <c r="G49" s="9" t="inlineStr">
         <is>
-          <t>`STI-102`</t>
+          <t>—</t>
         </is>
       </c>
     </row>

--- a/KURIKULUM2026_REVISI/005_STRUKTUR_KURIKULUM_8_SEMESTER_DAN_PEMINATAN.xlsx
+++ b/KURIKULUM2026_REVISI/005_STRUKTUR_KURIKULUM_8_SEMESTER_DAN_PEMINATAN.xlsx
@@ -1865,7 +1865,7 @@
     <row r="52" ht="20" customHeight="1">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>SEMESTER 3 (20 SKS) — Penguatan Core RPL, OS &amp; Jaringan Komputer</t>
+          <t>SEMESTER 3 (20 SKS) — Penguatan Core RPL, OS, Jarkom &amp; UI/UX</t>
         </is>
       </c>
       <c r="B52" s="4" t="n"/>
@@ -1945,7 +1945,7 @@
       </c>
       <c r="G54" s="7" t="inlineStr">
         <is>
-          <t>`STI-104`, `FST-207`</t>
+          <t>`STI-101`, `FST-207`</t>
         </is>
       </c>
     </row>
@@ -1962,17 +1962,17 @@
       </c>
       <c r="C55" s="9" t="inlineStr">
         <is>
-          <t>Kecerdasan Buatan (Artificial Intelligence)</t>
+          <t>Sistem Cerdas</t>
         </is>
       </c>
       <c r="D55" s="10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E55" s="9" t="inlineStr">
         <is>
-          <t>+P</t>
+          <t>Teori</t>
         </is>
       </c>
       <c r="F55" s="9" t="inlineStr">
@@ -1982,7 +1982,7 @@
       </c>
       <c r="G55" s="9" t="inlineStr">
         <is>
-          <t>`STI-201`, `STI-202`</t>
+          <t>`STI-201`, `FST-204`</t>
         </is>
       </c>
     </row>
@@ -1999,7 +1999,7 @@
       </c>
       <c r="C56" s="7" t="inlineStr">
         <is>
-          <t>Desain Pengalaman Pengguna (UI/UX Design)</t>
+          <t>UI/UX Design &amp; Prototyping</t>
         </is>
       </c>
       <c r="D56" s="8" t="inlineStr">
@@ -2019,7 +2019,7 @@
       </c>
       <c r="G56" s="7" t="inlineStr">
         <is>
-          <t>`STI-104`</t>
+          <t>`FST-101`</t>
         </is>
       </c>
     </row>
@@ -2056,7 +2056,7 @@
       </c>
       <c r="G57" s="9" t="inlineStr">
         <is>
-          <t>`STI-202`</t>
+          <t>`FST-203`</t>
         </is>
       </c>
     </row>
@@ -2093,7 +2093,7 @@
       </c>
       <c r="G58" s="7" t="inlineStr">
         <is>
-          <t>`STI-201`</t>
+          <t>`STI-103`</t>
         </is>
       </c>
     </row>
@@ -2110,12 +2110,12 @@
       </c>
       <c r="C59" s="9" t="inlineStr">
         <is>
-          <t>Pemrograman Web Front-End</t>
+          <t>Web Front End Development</t>
         </is>
       </c>
       <c r="D59" s="10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E59" s="9" t="inlineStr">
@@ -2130,7 +2130,7 @@
       </c>
       <c r="G59" s="9" t="inlineStr">
         <is>
-          <t>`STI-202`</t>
+          <t>`FST-102`</t>
         </is>
       </c>
     </row>
@@ -2167,7 +2167,7 @@
       </c>
       <c r="G60" s="7" t="inlineStr">
         <is>
-          <t>`STI-104`</t>
+          <t>`STI-103`</t>
         </is>
       </c>
     </row>

--- a/KURIKULUM2026_REVISI/005_STRUKTUR_KURIKULUM_8_SEMESTER_DAN_PEMINATAN.xlsx
+++ b/KURIKULUM2026_REVISI/005_STRUKTUR_KURIKULUM_8_SEMESTER_DAN_PEMINATAN.xlsx
@@ -558,8 +558,8 @@
     <col width="56.34999999999999" customWidth="1" min="2" max="2"/>
     <col width="69" customWidth="1" min="3" max="3"/>
     <col width="40.25" customWidth="1" min="4" max="4"/>
-    <col width="50.59999999999999" customWidth="1" min="5" max="5"/>
-    <col width="46" customWidth="1" min="6" max="6"/>
+    <col width="69" customWidth="1" min="5" max="5"/>
+    <col width="54.05" customWidth="1" min="6" max="6"/>
     <col width="35.65" customWidth="1" min="7" max="7"/>
     <col width="47.15" customWidth="1" min="8" max="8"/>
   </cols>
@@ -3095,7 +3095,7 @@
       </c>
       <c r="B83" s="7" t="inlineStr">
         <is>
-          <t>Deep Learning &amp; IoT</t>
+          <t>Keamanan Lanjut &amp; IoT</t>
         </is>
       </c>
       <c r="C83" s="8" t="inlineStr">
@@ -3110,7 +3110,7 @@
       </c>
       <c r="E83" s="7" t="inlineStr">
         <is>
-          <t>Deep Learning, IoT, Mobile, KPM, Peminatan 1</t>
+          <t>Keamanan Lanjut, Data Mining, IoT, Mobile, KPM, Peminatan 1</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="B84" s="9" t="inlineStr">
         <is>
-          <t>AI Integrasi &amp; Platform</t>
+          <t>Deep Learning &amp; Platform</t>
         </is>
       </c>
       <c r="C84" s="10" t="inlineStr">
@@ -3137,7 +3137,7 @@
       </c>
       <c r="E84" s="9" t="inlineStr">
         <is>
-          <t>Smart AI, Smart City, Platform, Metopel</t>
+          <t>Integrasi AI, Smart City, Deep Learning, Platform Eng, Metopen</t>
         </is>
       </c>
     </row>
@@ -4762,7 +4762,7 @@
     <row r="137" ht="20" customHeight="1">
       <c r="A137" s="3" t="inlineStr">
         <is>
-          <t>SEMESTER 5 (21 SKS) — Tahap Spesialisasi Deep Learning, IoT &amp; Peminatan 1</t>
+          <t>SEMESTER 5 (21 SKS) — Tahap Spesialisasi Keamanan Lanjut, IoT &amp; Peminatan 1</t>
         </is>
       </c>
       <c r="B137" s="4" t="n"/>
@@ -5146,7 +5146,7 @@
     <row r="149" ht="20" customHeight="1">
       <c r="A149" s="3" t="inlineStr">
         <is>
-          <t>SEMESTER 6 (19 SKS) — Tahap Spesialisasi MBKM &amp; Platform Engineering</t>
+          <t>SEMESTER 6 (19 SKS) — Tahap Spesialisasi Deep Learning, Platform Engineering &amp; MBKM</t>
         </is>
       </c>
       <c r="B149" s="4" t="n"/>
@@ -6162,7 +6162,7 @@
       </c>
       <c r="F182" s="7" t="inlineStr">
         <is>
-          <t>Tahap Spesialisasi Deep Learning &amp; IoT</t>
+          <t>Tahap Spesialisasi Keamanan Lanjut &amp; IoT</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="F183" s="9" t="inlineStr">
         <is>
-          <t>Tahap Spesialisasi MBKM &amp; Platform Eng</t>
+          <t>Tahap Spesialisasi Deep Learning &amp; Platform Eng</t>
         </is>
       </c>
     </row>

--- a/KURIKULUM2026_REVISI/005_STRUKTUR_KURIKULUM_8_SEMESTER_DAN_PEMINATAN.xlsx
+++ b/KURIKULUM2026_REVISI/005_STRUKTUR_KURIKULUM_8_SEMESTER_DAN_PEMINATAN.xlsx
@@ -551,7 +551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H192"/>
+  <dimension ref="A1:H241"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="69" customWidth="1" min="1" max="1"/>
@@ -560,8 +560,8 @@
     <col width="40.25" customWidth="1" min="4" max="4"/>
     <col width="69" customWidth="1" min="5" max="5"/>
     <col width="54.05" customWidth="1" min="6" max="6"/>
-    <col width="35.65" customWidth="1" min="7" max="7"/>
-    <col width="47.15" customWidth="1" min="8" max="8"/>
+    <col width="46" customWidth="1" min="7" max="7"/>
+    <col width="54.05" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -2943,387 +2943,619 @@
     <row r="77" ht="20" customHeight="1">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>SEBARAN 8 SEMESTER KURIKULUM SISTEKIN</t>
+          <t>1.4 KELOMPOK MATA KULIAH PILIHAN PEMINATAN (ELEKTIF) (18 MK DITAWARKAN / 18 SKS DITEMPUH)</t>
         </is>
       </c>
       <c r="B77" s="4" t="n"/>
       <c r="C77" s="4" t="n"/>
       <c r="D77" s="4" t="n"/>
       <c r="E77" s="4" t="n"/>
-      <c r="F77" s="5" t="n"/>
+      <c r="F77" s="4" t="n"/>
+      <c r="G77" s="4" t="n"/>
+      <c r="H77" s="5" t="n"/>
     </row>
     <row r="78" ht="26" customHeight="1">
       <c r="A78" s="6" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B78" s="6" t="inlineStr">
+        <is>
+          <t>Kode MK</t>
+        </is>
+      </c>
+      <c r="C78" s="6" t="inlineStr">
+        <is>
+          <t>Nama Mata Kuliah</t>
+        </is>
+      </c>
+      <c r="D78" s="6" t="inlineStr">
+        <is>
+          <t>SKS</t>
+        </is>
+      </c>
+      <c r="E78" s="6" t="inlineStr">
+        <is>
+          <t>Tipe</t>
+        </is>
+      </c>
+      <c r="F78" s="6" t="inlineStr">
+        <is>
           <t>Semester</t>
         </is>
       </c>
-      <c r="B78" s="6" t="inlineStr">
-        <is>
-          <t>Fokus Pembelajaran</t>
-        </is>
-      </c>
-      <c r="C78" s="6" t="inlineStr">
-        <is>
-          <t>Jml MK</t>
-        </is>
-      </c>
-      <c r="D78" s="6" t="inlineStr">
-        <is>
-          <t>Jml SKS</t>
-        </is>
-      </c>
-      <c r="E78" s="6" t="inlineStr">
-        <is>
-          <t>Karakteristik Kurikulum</t>
+      <c r="G78" s="6" t="inlineStr">
+        <is>
+          <t>Prasyarat</t>
+        </is>
+      </c>
+      <c r="H78" s="6" t="inlineStr">
+        <is>
+          <t>Jalur Peminatan</t>
         </is>
       </c>
     </row>
     <row r="79" ht="16" customHeight="1">
-      <c r="A79" s="7" t="inlineStr">
-        <is>
-          <t>**Sem 1**</t>
-        </is>
-      </c>
-      <c r="B79" s="7" t="inlineStr">
-        <is>
-          <t>Fondasi Sains &amp; MKWU</t>
-        </is>
-      </c>
-      <c r="C79" s="8" t="inlineStr">
-        <is>
-          <t>8 MK</t>
+      <c r="A79" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B79" s="8" t="inlineStr">
+        <is>
+          <t>`STA-01`</t>
+        </is>
+      </c>
+      <c r="C79" s="7" t="inlineStr">
+        <is>
+          <t>Decision Support Systems</t>
         </is>
       </c>
       <c r="D79" s="8" t="inlineStr">
         <is>
-          <t>19 SKS</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E79" s="7" t="inlineStr">
         <is>
-          <t>Sains, Algoritma Dasar, Logika, Agama</t>
+          <t>+P</t>
+        </is>
+      </c>
+      <c r="F79" s="7" t="inlineStr">
+        <is>
+          <t>Sem 5</t>
+        </is>
+      </c>
+      <c r="G79" s="7" t="inlineStr">
+        <is>
+          <t>`STI-307`</t>
+        </is>
+      </c>
+      <c r="H79" s="7" t="inlineStr">
+        <is>
+          <t>P1: Integrated Smart Systems</t>
         </is>
       </c>
     </row>
     <row r="80" ht="16" customHeight="1">
-      <c r="A80" s="9" t="inlineStr">
-        <is>
-          <t>**Sem 2**</t>
-        </is>
-      </c>
-      <c r="B80" s="9" t="inlineStr">
-        <is>
-          <t>Data, Matdis &amp; Etika</t>
-        </is>
-      </c>
-      <c r="C80" s="10" t="inlineStr">
-        <is>
-          <t>8 MK</t>
+      <c r="A80" s="10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B80" s="10" t="inlineStr">
+        <is>
+          <t>`STA-02`</t>
+        </is>
+      </c>
+      <c r="C80" s="9" t="inlineStr">
+        <is>
+          <t>Computational Methods and Numerics</t>
         </is>
       </c>
       <c r="D80" s="10" t="inlineStr">
         <is>
-          <t>20 SKS</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E80" s="9" t="inlineStr">
         <is>
-          <t>Struktur Data, Basis Data, Matdis, Etika</t>
+          <t>+P</t>
+        </is>
+      </c>
+      <c r="F80" s="9" t="inlineStr">
+        <is>
+          <t>Sem 6</t>
+        </is>
+      </c>
+      <c r="G80" s="9" t="inlineStr">
+        <is>
+          <t>`STI-102`, `STI-205`</t>
+        </is>
+      </c>
+      <c r="H80" s="9" t="inlineStr">
+        <is>
+          <t>P1: Integrated Smart Systems</t>
         </is>
       </c>
     </row>
     <row r="81" ht="16" customHeight="1">
-      <c r="A81" s="7" t="inlineStr">
-        <is>
-          <t>**Sem 3**</t>
-        </is>
-      </c>
-      <c r="B81" s="7" t="inlineStr">
-        <is>
-          <t>RPL, UI/UX &amp; Infra</t>
-        </is>
-      </c>
-      <c r="C81" s="8" t="inlineStr">
-        <is>
-          <t>7 MK</t>
+      <c r="A81" s="8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B81" s="8" t="inlineStr">
+        <is>
+          <t>`STA-03`</t>
+        </is>
+      </c>
+      <c r="C81" s="7" t="inlineStr">
+        <is>
+          <t>Intelligent Agent Systems</t>
         </is>
       </c>
       <c r="D81" s="8" t="inlineStr">
         <is>
-          <t>20 SKS</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E81" s="7" t="inlineStr">
         <is>
-          <t>APSI, RPL, Web Front, Jarkom, OS, Cerdas</t>
+          <t>+P</t>
+        </is>
+      </c>
+      <c r="F81" s="7" t="inlineStr">
+        <is>
+          <t>Sem 6</t>
+        </is>
+      </c>
+      <c r="G81" s="7" t="inlineStr">
+        <is>
+          <t>`STI-307`</t>
+        </is>
+      </c>
+      <c r="H81" s="7" t="inlineStr">
+        <is>
+          <t>P1: Integrated Smart Systems</t>
         </is>
       </c>
     </row>
     <row r="82" ht="16" customHeight="1">
-      <c r="A82" s="9" t="inlineStr">
-        <is>
-          <t>**Sem 4**</t>
-        </is>
-      </c>
-      <c r="B82" s="9" t="inlineStr">
-        <is>
-          <t>AI/ML, NLP, Cloud &amp; Keamanan</t>
-        </is>
-      </c>
-      <c r="C82" s="10" t="inlineStr">
-        <is>
-          <t>8 MK</t>
+      <c r="A82" s="10" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B82" s="10" t="inlineStr">
+        <is>
+          <t>`STA-04`</t>
+        </is>
+      </c>
+      <c r="C82" s="9" t="inlineStr">
+        <is>
+          <t>MLOps and AI Pipeline</t>
         </is>
       </c>
       <c r="D82" s="10" t="inlineStr">
         <is>
-          <t>21 SKS</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E82" s="9" t="inlineStr">
         <is>
-          <t>ML, NLP/IR, DW/BI, Web Back, Cloud, Probstat</t>
+          <t>+P</t>
+        </is>
+      </c>
+      <c r="F82" s="9" t="inlineStr">
+        <is>
+          <t>Sem 7</t>
+        </is>
+      </c>
+      <c r="G82" s="9" t="inlineStr">
+        <is>
+          <t>`STI-413`, `STI-624`</t>
+        </is>
+      </c>
+      <c r="H82" s="9" t="inlineStr">
+        <is>
+          <t>P1: Integrated Smart Systems</t>
         </is>
       </c>
     </row>
     <row r="83" ht="16" customHeight="1">
-      <c r="A83" s="7" t="inlineStr">
-        <is>
-          <t>**Sem 5**</t>
-        </is>
-      </c>
-      <c r="B83" s="7" t="inlineStr">
-        <is>
-          <t>Keamanan Lanjut &amp; IoT</t>
-        </is>
-      </c>
-      <c r="C83" s="8" t="inlineStr">
-        <is>
-          <t>7 MK</t>
+      <c r="A83" s="8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B83" s="8" t="inlineStr">
+        <is>
+          <t>`STA-05`</t>
+        </is>
+      </c>
+      <c r="C83" s="7" t="inlineStr">
+        <is>
+          <t>Conversational AI and Intelligent Assistant</t>
         </is>
       </c>
       <c r="D83" s="8" t="inlineStr">
         <is>
-          <t>21 SKS</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E83" s="7" t="inlineStr">
         <is>
-          <t>Keamanan Lanjut, Data Mining, IoT, Mobile, KPM, Peminatan 1</t>
+          <t>+P</t>
+        </is>
+      </c>
+      <c r="F83" s="7" t="inlineStr">
+        <is>
+          <t>Sem 7</t>
+        </is>
+      </c>
+      <c r="G83" s="7" t="inlineStr">
+        <is>
+          <t>`STI-413`, `STI-416`</t>
+        </is>
+      </c>
+      <c r="H83" s="7" t="inlineStr">
+        <is>
+          <t>P1: Integrated Smart Systems</t>
         </is>
       </c>
     </row>
     <row r="84" ht="16" customHeight="1">
-      <c r="A84" s="9" t="inlineStr">
-        <is>
-          <t>**Sem 6**</t>
-        </is>
-      </c>
-      <c r="B84" s="9" t="inlineStr">
-        <is>
-          <t>Deep Learning &amp; Platform</t>
-        </is>
-      </c>
-      <c r="C84" s="10" t="inlineStr">
-        <is>
-          <t>7 MK</t>
+      <c r="A84" s="10" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B84" s="10" t="inlineStr">
+        <is>
+          <t>`STA-06`</t>
+        </is>
+      </c>
+      <c r="C84" s="9" t="inlineStr">
+        <is>
+          <t>Smart Surveillance and IoT Analytics</t>
         </is>
       </c>
       <c r="D84" s="10" t="inlineStr">
         <is>
-          <t>19 SKS</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E84" s="9" t="inlineStr">
         <is>
-          <t>Integrasi AI, Smart City, Deep Learning, Platform Eng, Metopen</t>
+          <t>+P</t>
+        </is>
+      </c>
+      <c r="F84" s="9" t="inlineStr">
+        <is>
+          <t>Sem 7</t>
+        </is>
+      </c>
+      <c r="G84" s="9" t="inlineStr">
+        <is>
+          <t>`STI-626`, `STI-521`</t>
+        </is>
+      </c>
+      <c r="H84" s="9" t="inlineStr">
+        <is>
+          <t>P1: Integrated Smart Systems</t>
         </is>
       </c>
     </row>
     <row r="85" ht="16" customHeight="1">
-      <c r="A85" s="7" t="inlineStr">
-        <is>
-          <t>**Sem 7**</t>
-        </is>
-      </c>
-      <c r="B85" s="7" t="inlineStr">
-        <is>
-          <t>Capstone, PKL &amp; Sempro</t>
-        </is>
-      </c>
-      <c r="C85" s="8" t="inlineStr">
-        <is>
-          <t>7 MK</t>
+      <c r="A85" s="8" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B85" s="8" t="inlineStr">
+        <is>
+          <t>`STB-01`</t>
+        </is>
+      </c>
+      <c r="C85" s="7" t="inlineStr">
+        <is>
+          <t>Network Security and Digital Forensics</t>
         </is>
       </c>
       <c r="D85" s="8" t="inlineStr">
         <is>
-          <t>20 SKS</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E85" s="7" t="inlineStr">
         <is>
-          <t>Startup, Capstone FSTI, PKL, Pra-Skripsi</t>
+          <t>+P</t>
+        </is>
+      </c>
+      <c r="F85" s="7" t="inlineStr">
+        <is>
+          <t>Sem 5</t>
+        </is>
+      </c>
+      <c r="G85" s="7" t="inlineStr">
+        <is>
+          <t>`STI-312`, `STI-418`</t>
+        </is>
+      </c>
+      <c r="H85" s="7" t="inlineStr">
+        <is>
+          <t>P2: Cloud Infra &amp; Cybersecurity</t>
         </is>
       </c>
     </row>
     <row r="86" ht="16" customHeight="1">
-      <c r="A86" s="9" t="inlineStr">
-        <is>
-          <t>**Sem 8**</t>
-        </is>
-      </c>
-      <c r="B86" s="9" t="inlineStr">
-        <is>
-          <t>Skripsi Mandiri</t>
-        </is>
-      </c>
-      <c r="C86" s="10" t="inlineStr">
-        <is>
-          <t>1 MK</t>
+      <c r="A86" s="10" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B86" s="10" t="inlineStr">
+        <is>
+          <t>`STB-02`</t>
+        </is>
+      </c>
+      <c r="C86" s="9" t="inlineStr">
+        <is>
+          <t>Cloud Architecture &amp; DevOps</t>
         </is>
       </c>
       <c r="D86" s="10" t="inlineStr">
         <is>
-          <t>6 SKS</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E86" s="9" t="inlineStr">
         <is>
-          <t>Skripsi Murni / 4 Opsi Non-Skripsi</t>
+          <t>+P</t>
+        </is>
+      </c>
+      <c r="F86" s="9" t="inlineStr">
+        <is>
+          <t>Sem 6</t>
+        </is>
+      </c>
+      <c r="G86" s="9" t="inlineStr">
+        <is>
+          <t>`STI-417`</t>
+        </is>
+      </c>
+      <c r="H86" s="9" t="inlineStr">
+        <is>
+          <t>P2: Cloud Infra &amp; Cybersecurity</t>
         </is>
       </c>
     </row>
     <row r="87" ht="16" customHeight="1">
-      <c r="A87" s="7" t="inlineStr">
-        <is>
-          <t>**TOTAL**</t>
-        </is>
-      </c>
-      <c r="B87" s="7" t="inlineStr">
-        <is>
-          <t>**Paket Lulus Tepat Waktu**</t>
+      <c r="A87" s="8" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B87" s="8" t="inlineStr">
+        <is>
+          <t>`STB-03`</t>
         </is>
       </c>
       <c r="C87" s="7" t="inlineStr">
         <is>
-          <t>**55 MK**</t>
-        </is>
-      </c>
-      <c r="D87" s="7" t="inlineStr">
-        <is>
-          <t>**146 SKS**</t>
+          <t>Cybersecurity Risk Management</t>
+        </is>
+      </c>
+      <c r="D87" s="8" t="inlineStr">
+        <is>
+          <t>3</t>
         </is>
       </c>
       <c r="E87" s="7" t="inlineStr">
         <is>
-          <t>**Standar Sarjana S1 Komputasi**</t>
-        </is>
-      </c>
-    </row>
-    <row r="88"/>
-    <row r="89" ht="20" customHeight="1">
-      <c r="A89" s="3" t="inlineStr">
-        <is>
-          <t>SEMESTER 1 (19 SKS) — Fondasi Sains, Algoritma, Arsitektur STI &amp; MKWU</t>
-        </is>
-      </c>
-      <c r="B89" s="4" t="n"/>
-      <c r="C89" s="4" t="n"/>
-      <c r="D89" s="4" t="n"/>
-      <c r="E89" s="4" t="n"/>
-      <c r="F89" s="4" t="n"/>
-      <c r="G89" s="5" t="n"/>
-    </row>
-    <row r="90" ht="26" customHeight="1">
-      <c r="A90" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="B90" s="6" t="inlineStr">
-        <is>
-          <t>Kode MK</t>
-        </is>
-      </c>
-      <c r="C90" s="6" t="inlineStr">
-        <is>
-          <t>Nama Mata Kuliah</t>
-        </is>
-      </c>
-      <c r="D90" s="6" t="inlineStr">
-        <is>
-          <t>SKS</t>
-        </is>
-      </c>
-      <c r="E90" s="6" t="inlineStr">
-        <is>
-          <t>Tipe</t>
-        </is>
-      </c>
-      <c r="F90" s="6" t="inlineStr">
-        <is>
-          <t>Kategori</t>
-        </is>
-      </c>
-      <c r="G90" s="6" t="inlineStr">
-        <is>
-          <t>Prasyarat</t>
+          <t>Teori</t>
+        </is>
+      </c>
+      <c r="F87" s="7" t="inlineStr">
+        <is>
+          <t>Sem 6</t>
+        </is>
+      </c>
+      <c r="G87" s="7" t="inlineStr">
+        <is>
+          <t>`STI-418`</t>
+        </is>
+      </c>
+      <c r="H87" s="7" t="inlineStr">
+        <is>
+          <t>P2: Cloud Infra &amp; Cybersecurity</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="16" customHeight="1">
+      <c r="A88" s="10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B88" s="10" t="inlineStr">
+        <is>
+          <t>`STB-04`</t>
+        </is>
+      </c>
+      <c r="C88" s="9" t="inlineStr">
+        <is>
+          <t>IT Governance &amp; Compliance (COBIT 2019)</t>
+        </is>
+      </c>
+      <c r="D88" s="10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E88" s="9" t="inlineStr">
+        <is>
+          <t>Teori</t>
+        </is>
+      </c>
+      <c r="F88" s="9" t="inlineStr">
+        <is>
+          <t>Sem 7</t>
+        </is>
+      </c>
+      <c r="G88" s="9" t="inlineStr">
+        <is>
+          <t>`STI-101`</t>
+        </is>
+      </c>
+      <c r="H88" s="9" t="inlineStr">
+        <is>
+          <t>P2: Cloud Infra &amp; Cybersecurity</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="16" customHeight="1">
+      <c r="A89" s="8" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B89" s="8" t="inlineStr">
+        <is>
+          <t>`STB-05`</t>
+        </is>
+      </c>
+      <c r="C89" s="7" t="inlineStr">
+        <is>
+          <t>IT Service Management (ITIL 4)</t>
+        </is>
+      </c>
+      <c r="D89" s="8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E89" s="7" t="inlineStr">
+        <is>
+          <t>Teori</t>
+        </is>
+      </c>
+      <c r="F89" s="7" t="inlineStr">
+        <is>
+          <t>Sem 7</t>
+        </is>
+      </c>
+      <c r="G89" s="7" t="inlineStr">
+        <is>
+          <t>`STI-101`</t>
+        </is>
+      </c>
+      <c r="H89" s="7" t="inlineStr">
+        <is>
+          <t>P2: Cloud Infra &amp; Cybersecurity</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="16" customHeight="1">
+      <c r="A90" s="10" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B90" s="10" t="inlineStr">
+        <is>
+          <t>`STB-06`</t>
+        </is>
+      </c>
+      <c r="C90" s="9" t="inlineStr">
+        <is>
+          <t>Enterprise Architecture (TOGAF)</t>
+        </is>
+      </c>
+      <c r="D90" s="10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E90" s="9" t="inlineStr">
+        <is>
+          <t>Teori</t>
+        </is>
+      </c>
+      <c r="F90" s="9" t="inlineStr">
+        <is>
+          <t>Sem 7</t>
+        </is>
+      </c>
+      <c r="G90" s="9" t="inlineStr">
+        <is>
+          <t>`STI-306`</t>
+        </is>
+      </c>
+      <c r="H90" s="9" t="inlineStr">
+        <is>
+          <t>P2: Cloud Infra &amp; Cybersecurity</t>
         </is>
       </c>
     </row>
     <row r="91" ht="16" customHeight="1">
       <c r="A91" s="8" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B91" s="7" t="inlineStr">
-        <is>
-          <t>`FST-101`</t>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B91" s="8" t="inlineStr">
+        <is>
+          <t>`STC-01`</t>
         </is>
       </c>
       <c r="C91" s="7" t="inlineStr">
         <is>
-          <t>Dasar Teknologi Digital</t>
+          <t>User Experience Research &amp; Design</t>
         </is>
       </c>
       <c r="D91" s="8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E91" s="7" t="inlineStr">
         <is>
-          <t>Teori</t>
+          <t>+P</t>
         </is>
       </c>
       <c r="F91" s="7" t="inlineStr">
         <is>
-          <t>FSTI</t>
+          <t>Sem 5</t>
         </is>
       </c>
       <c r="G91" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>`STI-308`</t>
+        </is>
+      </c>
+      <c r="H91" s="7" t="inlineStr">
+        <is>
+          <t>P3: Digital Platform Engineering</t>
         </is>
       </c>
     </row>
     <row r="92" ht="16" customHeight="1">
       <c r="A92" s="10" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B92" s="9" t="inlineStr">
-        <is>
-          <t>`FST-102`</t>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="B92" s="10" t="inlineStr">
+        <is>
+          <t>`STC-02`</t>
         </is>
       </c>
       <c r="C92" s="9" t="inlineStr">
         <is>
-          <t>Algoritma dan Pemrograman</t>
+          <t>Rekayasa &amp; Otomasi Proses Bisnis (BPA)</t>
         </is>
       </c>
       <c r="D92" s="10" t="inlineStr">
@@ -3338,66 +3570,76 @@
       </c>
       <c r="F92" s="9" t="inlineStr">
         <is>
-          <t>FSTI</t>
+          <t>Sem 6</t>
         </is>
       </c>
       <c r="G92" s="9" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>`STI-306`</t>
+        </is>
+      </c>
+      <c r="H92" s="9" t="inlineStr">
+        <is>
+          <t>P3: Digital Platform Engineering</t>
         </is>
       </c>
     </row>
     <row r="93" ht="16" customHeight="1">
       <c r="A93" s="8" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B93" s="7" t="inlineStr">
-        <is>
-          <t>`STI-101`</t>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B93" s="8" t="inlineStr">
+        <is>
+          <t>`STC-03`</t>
         </is>
       </c>
       <c r="C93" s="7" t="inlineStr">
         <is>
-          <t>Pengantar Sistem dan Teknologi Informasi</t>
+          <t>Rekayasa Aplikasi Industri Vertikal (FinTech &amp; EdTech)</t>
         </is>
       </c>
       <c r="D93" s="8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E93" s="7" t="inlineStr">
         <is>
-          <t>Teori</t>
+          <t>+P</t>
         </is>
       </c>
       <c r="F93" s="7" t="inlineStr">
         <is>
-          <t>Core STI</t>
+          <t>Sem 6</t>
         </is>
       </c>
       <c r="G93" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>`STI-416`</t>
+        </is>
+      </c>
+      <c r="H93" s="7" t="inlineStr">
+        <is>
+          <t>P3: Digital Platform Engineering</t>
         </is>
       </c>
     </row>
     <row r="94" ht="16" customHeight="1">
       <c r="A94" s="10" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B94" s="9" t="inlineStr">
-        <is>
-          <t>`STI-102`</t>
-        </is>
-      </c>
-      <c r="C94" s="10" t="inlineStr">
-        <is>
-          <t>Kalkulus</t>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B94" s="10" t="inlineStr">
+        <is>
+          <t>`STC-04`</t>
+        </is>
+      </c>
+      <c r="C94" s="9" t="inlineStr">
+        <is>
+          <t>Immersive Media &amp; XR Development</t>
         </is>
       </c>
       <c r="D94" s="10" t="inlineStr">
@@ -3407,34 +3649,39 @@
       </c>
       <c r="E94" s="9" t="inlineStr">
         <is>
-          <t>Teori</t>
+          <t>+P</t>
         </is>
       </c>
       <c r="F94" s="9" t="inlineStr">
         <is>
-          <t>Core STI</t>
+          <t>Sem 7</t>
         </is>
       </c>
       <c r="G94" s="9" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>`STI-311`</t>
+        </is>
+      </c>
+      <c r="H94" s="9" t="inlineStr">
+        <is>
+          <t>P3: Digital Platform Engineering</t>
         </is>
       </c>
     </row>
     <row r="95" ht="16" customHeight="1">
       <c r="A95" s="8" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B95" s="7" t="inlineStr">
-        <is>
-          <t>`STI-103`</t>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B95" s="8" t="inlineStr">
+        <is>
+          <t>`STC-05`</t>
         </is>
       </c>
       <c r="C95" s="7" t="inlineStr">
         <is>
-          <t>Arsitektur dan Organisasi Sistem Teknologi Informasi</t>
+          <t>SaaS Architecture &amp; Multi-Tenancy</t>
         </is>
       </c>
       <c r="D95" s="8" t="inlineStr">
@@ -3444,622 +3691,536 @@
       </c>
       <c r="E95" s="7" t="inlineStr">
         <is>
-          <t>Teori</t>
+          <t>+P</t>
         </is>
       </c>
       <c r="F95" s="7" t="inlineStr">
         <is>
-          <t>Core STI</t>
+          <t>Sem 7</t>
         </is>
       </c>
       <c r="G95" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>`STI-416`</t>
+        </is>
+      </c>
+      <c r="H95" s="7" t="inlineStr">
+        <is>
+          <t>P3: Digital Platform Engineering</t>
         </is>
       </c>
     </row>
     <row r="96" ht="16" customHeight="1">
       <c r="A96" s="10" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="B96" s="9" t="inlineStr">
-        <is>
-          <t>`MKU-101`</t>
-        </is>
-      </c>
-      <c r="C96" s="10" t="inlineStr">
-        <is>
-          <t>Agama I</t>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B96" s="10" t="inlineStr">
+        <is>
+          <t>`STC-06`</t>
+        </is>
+      </c>
+      <c r="C96" s="9" t="inlineStr">
+        <is>
+          <t>Digital Product Management &amp; Agile Practices</t>
         </is>
       </c>
       <c r="D96" s="10" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E96" s="9" t="inlineStr">
+        <is>
+          <t>Teori</t>
+        </is>
+      </c>
+      <c r="F96" s="9" t="inlineStr">
+        <is>
+          <t>Sem 7</t>
+        </is>
+      </c>
+      <c r="G96" s="9" t="inlineStr">
+        <is>
+          <t>`STI-523`</t>
+        </is>
+      </c>
+      <c r="H96" s="9" t="inlineStr">
+        <is>
+          <t>P3: Digital Platform Engineering</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="16" customHeight="1">
+      <c r="A97" s="7" t="inlineStr">
+        <is>
+          <t>**TOTAL**</t>
+        </is>
+      </c>
+      <c r="B97" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C97" s="7" t="inlineStr">
+        <is>
+          <t>**18 Mata Kuliah Pilihan Ditawarkan (Portofolio SIAKAD)**</t>
+        </is>
+      </c>
+      <c r="D97" s="8" t="inlineStr">
+        <is>
+          <t>**54**</t>
+        </is>
+      </c>
+      <c r="E97" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F97" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G97" s="7" t="inlineStr">
+        <is>
+          <t>**Ditempuh 6 MK (18 SKS) per Mahasiswa**</t>
+        </is>
+      </c>
+      <c r="H97" s="7" t="inlineStr">
+        <is>
+          <t>**3 Jalur Peminatan Seimbang**</t>
+        </is>
+      </c>
+    </row>
+    <row r="98"/>
+    <row r="99" ht="20" customHeight="1">
+      <c r="A99" s="3" t="inlineStr">
+        <is>
+          <t>SEBARAN 8 SEMESTER KURIKULUM SISTEKIN</t>
+        </is>
+      </c>
+      <c r="B99" s="4" t="n"/>
+      <c r="C99" s="4" t="n"/>
+      <c r="D99" s="4" t="n"/>
+      <c r="E99" s="4" t="n"/>
+      <c r="F99" s="5" t="n"/>
+    </row>
+    <row r="100" ht="26" customHeight="1">
+      <c r="A100" s="6" t="inlineStr">
+        <is>
+          <t>Semester</t>
+        </is>
+      </c>
+      <c r="B100" s="6" t="inlineStr">
+        <is>
+          <t>Fokus Pembelajaran</t>
+        </is>
+      </c>
+      <c r="C100" s="6" t="inlineStr">
+        <is>
+          <t>Jml MK</t>
+        </is>
+      </c>
+      <c r="D100" s="6" t="inlineStr">
+        <is>
+          <t>Jml SKS</t>
+        </is>
+      </c>
+      <c r="E100" s="6" t="inlineStr">
+        <is>
+          <t>Karakteristik Kurikulum</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="16" customHeight="1">
+      <c r="A101" s="7" t="inlineStr">
+        <is>
+          <t>**Sem 1**</t>
+        </is>
+      </c>
+      <c r="B101" s="7" t="inlineStr">
+        <is>
+          <t>Fondasi Sains &amp; MKWU</t>
+        </is>
+      </c>
+      <c r="C101" s="8" t="inlineStr">
+        <is>
+          <t>8 MK</t>
+        </is>
+      </c>
+      <c r="D101" s="8" t="inlineStr">
+        <is>
+          <t>19 SKS</t>
+        </is>
+      </c>
+      <c r="E101" s="7" t="inlineStr">
+        <is>
+          <t>Sains, Algoritma Dasar, Logika, Agama</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="16" customHeight="1">
+      <c r="A102" s="9" t="inlineStr">
+        <is>
+          <t>**Sem 2**</t>
+        </is>
+      </c>
+      <c r="B102" s="9" t="inlineStr">
+        <is>
+          <t>Data, Matdis &amp; Etika</t>
+        </is>
+      </c>
+      <c r="C102" s="10" t="inlineStr">
+        <is>
+          <t>8 MK</t>
+        </is>
+      </c>
+      <c r="D102" s="10" t="inlineStr">
+        <is>
+          <t>20 SKS</t>
+        </is>
+      </c>
+      <c r="E102" s="9" t="inlineStr">
+        <is>
+          <t>Struktur Data, Basis Data, Matdis, Etika</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="16" customHeight="1">
+      <c r="A103" s="7" t="inlineStr">
+        <is>
+          <t>**Sem 3**</t>
+        </is>
+      </c>
+      <c r="B103" s="7" t="inlineStr">
+        <is>
+          <t>RPL, UI/UX &amp; Infra</t>
+        </is>
+      </c>
+      <c r="C103" s="8" t="inlineStr">
+        <is>
+          <t>7 MK</t>
+        </is>
+      </c>
+      <c r="D103" s="8" t="inlineStr">
+        <is>
+          <t>20 SKS</t>
+        </is>
+      </c>
+      <c r="E103" s="7" t="inlineStr">
+        <is>
+          <t>APSI, RPL, Web Front, Jarkom, OS, Cerdas</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="16" customHeight="1">
+      <c r="A104" s="9" t="inlineStr">
+        <is>
+          <t>**Sem 4**</t>
+        </is>
+      </c>
+      <c r="B104" s="9" t="inlineStr">
+        <is>
+          <t>AI/ML, NLP, Cloud &amp; Keamanan</t>
+        </is>
+      </c>
+      <c r="C104" s="10" t="inlineStr">
+        <is>
+          <t>8 MK</t>
+        </is>
+      </c>
+      <c r="D104" s="10" t="inlineStr">
+        <is>
+          <t>21 SKS</t>
+        </is>
+      </c>
+      <c r="E104" s="9" t="inlineStr">
+        <is>
+          <t>ML, NLP/IR, DW/BI, Web Back, Cloud, Probstat</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="16" customHeight="1">
+      <c r="A105" s="7" t="inlineStr">
+        <is>
+          <t>**Sem 5**</t>
+        </is>
+      </c>
+      <c r="B105" s="7" t="inlineStr">
+        <is>
+          <t>Keamanan Lanjut &amp; IoT</t>
+        </is>
+      </c>
+      <c r="C105" s="8" t="inlineStr">
+        <is>
+          <t>7 MK</t>
+        </is>
+      </c>
+      <c r="D105" s="8" t="inlineStr">
+        <is>
+          <t>21 SKS</t>
+        </is>
+      </c>
+      <c r="E105" s="7" t="inlineStr">
+        <is>
+          <t>Keamanan Lanjut, Data Mining, IoT, Mobile, KPM, Peminatan 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="16" customHeight="1">
+      <c r="A106" s="9" t="inlineStr">
+        <is>
+          <t>**Sem 6**</t>
+        </is>
+      </c>
+      <c r="B106" s="9" t="inlineStr">
+        <is>
+          <t>Deep Learning &amp; Platform</t>
+        </is>
+      </c>
+      <c r="C106" s="10" t="inlineStr">
+        <is>
+          <t>7 MK</t>
+        </is>
+      </c>
+      <c r="D106" s="10" t="inlineStr">
+        <is>
+          <t>19 SKS</t>
+        </is>
+      </c>
+      <c r="E106" s="9" t="inlineStr">
+        <is>
+          <t>Integrasi AI, Smart City, Deep Learning, Platform Eng, Metopen</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="16" customHeight="1">
+      <c r="A107" s="7" t="inlineStr">
+        <is>
+          <t>**Sem 7**</t>
+        </is>
+      </c>
+      <c r="B107" s="7" t="inlineStr">
+        <is>
+          <t>Capstone, PKL &amp; Sempro</t>
+        </is>
+      </c>
+      <c r="C107" s="8" t="inlineStr">
+        <is>
+          <t>7 MK</t>
+        </is>
+      </c>
+      <c r="D107" s="8" t="inlineStr">
+        <is>
+          <t>20 SKS</t>
+        </is>
+      </c>
+      <c r="E107" s="7" t="inlineStr">
+        <is>
+          <t>Startup, Capstone FSTI, PKL, Pra-Skripsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="16" customHeight="1">
+      <c r="A108" s="9" t="inlineStr">
+        <is>
+          <t>**Sem 8**</t>
+        </is>
+      </c>
+      <c r="B108" s="9" t="inlineStr">
+        <is>
+          <t>Skripsi Mandiri</t>
+        </is>
+      </c>
+      <c r="C108" s="10" t="inlineStr">
+        <is>
+          <t>1 MK</t>
+        </is>
+      </c>
+      <c r="D108" s="10" t="inlineStr">
+        <is>
+          <t>6 SKS</t>
+        </is>
+      </c>
+      <c r="E108" s="9" t="inlineStr">
+        <is>
+          <t>Skripsi Murni / 4 Opsi Non-Skripsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="16" customHeight="1">
+      <c r="A109" s="7" t="inlineStr">
+        <is>
+          <t>**TOTAL**</t>
+        </is>
+      </c>
+      <c r="B109" s="7" t="inlineStr">
+        <is>
+          <t>**Paket Lulus Tepat Waktu**</t>
+        </is>
+      </c>
+      <c r="C109" s="7" t="inlineStr">
+        <is>
+          <t>**55 MK**</t>
+        </is>
+      </c>
+      <c r="D109" s="7" t="inlineStr">
+        <is>
+          <t>**146 SKS**</t>
+        </is>
+      </c>
+      <c r="E109" s="7" t="inlineStr">
+        <is>
+          <t>**Standar Sarjana S1 Komputasi**</t>
+        </is>
+      </c>
+    </row>
+    <row r="110"/>
+    <row r="111" ht="20" customHeight="1">
+      <c r="A111" s="3" t="inlineStr">
+        <is>
+          <t>SEMESTER 1 (19 SKS) — Fondasi Sains, Algoritma, Arsitektur STI &amp; MKWU</t>
+        </is>
+      </c>
+      <c r="B111" s="4" t="n"/>
+      <c r="C111" s="4" t="n"/>
+      <c r="D111" s="4" t="n"/>
+      <c r="E111" s="4" t="n"/>
+      <c r="F111" s="4" t="n"/>
+      <c r="G111" s="5" t="n"/>
+    </row>
+    <row r="112" ht="26" customHeight="1">
+      <c r="A112" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B112" s="6" t="inlineStr">
+        <is>
+          <t>Kode MK</t>
+        </is>
+      </c>
+      <c r="C112" s="6" t="inlineStr">
+        <is>
+          <t>Nama Mata Kuliah</t>
+        </is>
+      </c>
+      <c r="D112" s="6" t="inlineStr">
+        <is>
+          <t>SKS</t>
+        </is>
+      </c>
+      <c r="E112" s="6" t="inlineStr">
+        <is>
+          <t>Tipe</t>
+        </is>
+      </c>
+      <c r="F112" s="6" t="inlineStr">
+        <is>
+          <t>Kategori</t>
+        </is>
+      </c>
+      <c r="G112" s="6" t="inlineStr">
+        <is>
+          <t>Prasyarat</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="16" customHeight="1">
+      <c r="A113" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B113" s="7" t="inlineStr">
+        <is>
+          <t>`FST-101`</t>
+        </is>
+      </c>
+      <c r="C113" s="7" t="inlineStr">
+        <is>
+          <t>Dasar Teknologi Digital</t>
+        </is>
+      </c>
+      <c r="D113" s="8" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E96" s="9" t="inlineStr">
+      <c r="E113" s="7" t="inlineStr">
         <is>
           <t>Teori</t>
         </is>
       </c>
-      <c r="F96" s="9" t="inlineStr">
-        <is>
-          <t>MKWU</t>
-        </is>
-      </c>
-      <c r="G96" s="9" t="inlineStr">
+      <c r="F113" s="7" t="inlineStr">
+        <is>
+          <t>FSTI</t>
+        </is>
+      </c>
+      <c r="G113" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
-    <row r="97" ht="16" customHeight="1">
-      <c r="A97" s="8" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="B97" s="7" t="inlineStr">
-        <is>
-          <t>`MKU-102`</t>
-        </is>
-      </c>
-      <c r="C97" s="7" t="inlineStr">
-        <is>
-          <t>Pancasila</t>
-        </is>
-      </c>
-      <c r="D97" s="8" t="inlineStr">
+    <row r="114" ht="16" customHeight="1">
+      <c r="A114" s="10" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E97" s="7" t="inlineStr">
-        <is>
-          <t>Teori</t>
-        </is>
-      </c>
-      <c r="F97" s="7" t="inlineStr">
-        <is>
-          <t>MKWU</t>
-        </is>
-      </c>
-      <c r="G97" s="7" t="inlineStr">
+      <c r="B114" s="9" t="inlineStr">
+        <is>
+          <t>`FST-102`</t>
+        </is>
+      </c>
+      <c r="C114" s="9" t="inlineStr">
+        <is>
+          <t>Algoritma dan Pemrograman</t>
+        </is>
+      </c>
+      <c r="D114" s="10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E114" s="9" t="inlineStr">
+        <is>
+          <t>+P</t>
+        </is>
+      </c>
+      <c r="F114" s="9" t="inlineStr">
+        <is>
+          <t>FSTI</t>
+        </is>
+      </c>
+      <c r="G114" s="9" t="inlineStr">
         <is>
           <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="98" ht="16" customHeight="1">
-      <c r="A98" s="10" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="B98" s="9" t="inlineStr">
-        <is>
-          <t>`MKU-103`</t>
-        </is>
-      </c>
-      <c r="C98" s="9" t="inlineStr">
-        <is>
-          <t>Bahasa Indonesia</t>
-        </is>
-      </c>
-      <c r="D98" s="10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E98" s="9" t="inlineStr">
-        <is>
-          <t>Teori</t>
-        </is>
-      </c>
-      <c r="F98" s="9" t="inlineStr">
-        <is>
-          <t>MKWU</t>
-        </is>
-      </c>
-      <c r="G98" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="99" ht="16" customHeight="1">
-      <c r="A99" s="7" t="inlineStr">
-        <is>
-          <t>**SUBTOTAL**</t>
-        </is>
-      </c>
-      <c r="B99" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C99" s="7" t="inlineStr">
-        <is>
-          <t>**Total SKS Semester 1 (8 MK)**</t>
-        </is>
-      </c>
-      <c r="D99" s="8" t="inlineStr">
-        <is>
-          <t>**19**</t>
-        </is>
-      </c>
-      <c r="E99" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F99" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G99" s="7" t="inlineStr">
-        <is>
-          <t>**Kumulatif: 19 SKS**</t>
-        </is>
-      </c>
-    </row>
-    <row r="100"/>
-    <row r="101" ht="20" customHeight="1">
-      <c r="A101" s="3" t="inlineStr">
-        <is>
-          <t>SEMESTER 2 (20 SKS) — Fondasi Data, Matdis &amp; Logika, Aljabar &amp; Etika</t>
-        </is>
-      </c>
-      <c r="B101" s="4" t="n"/>
-      <c r="C101" s="4" t="n"/>
-      <c r="D101" s="4" t="n"/>
-      <c r="E101" s="4" t="n"/>
-      <c r="F101" s="4" t="n"/>
-      <c r="G101" s="5" t="n"/>
-    </row>
-    <row r="102" ht="26" customHeight="1">
-      <c r="A102" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="B102" s="6" t="inlineStr">
-        <is>
-          <t>Kode MK</t>
-        </is>
-      </c>
-      <c r="C102" s="6" t="inlineStr">
-        <is>
-          <t>Nama Mata Kuliah</t>
-        </is>
-      </c>
-      <c r="D102" s="6" t="inlineStr">
-        <is>
-          <t>SKS</t>
-        </is>
-      </c>
-      <c r="E102" s="6" t="inlineStr">
-        <is>
-          <t>Tipe</t>
-        </is>
-      </c>
-      <c r="F102" s="6" t="inlineStr">
-        <is>
-          <t>Kategori</t>
-        </is>
-      </c>
-      <c r="G102" s="6" t="inlineStr">
-        <is>
-          <t>Prasyarat</t>
-        </is>
-      </c>
-    </row>
-    <row r="103" ht="16" customHeight="1">
-      <c r="A103" s="8" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="B103" s="7" t="inlineStr">
-        <is>
-          <t>`STI-204`</t>
-        </is>
-      </c>
-      <c r="C103" s="7" t="inlineStr">
-        <is>
-          <t>Matematika Diskrit dan Logika</t>
-        </is>
-      </c>
-      <c r="D103" s="8" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E103" s="7" t="inlineStr">
-        <is>
-          <t>Teori</t>
-        </is>
-      </c>
-      <c r="F103" s="7" t="inlineStr">
-        <is>
-          <t>Core STI</t>
-        </is>
-      </c>
-      <c r="G103" s="7" t="inlineStr">
-        <is>
-          <t>`STI-103`</t>
-        </is>
-      </c>
-    </row>
-    <row r="104" ht="16" customHeight="1">
-      <c r="A104" s="10" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="B104" s="9" t="inlineStr">
-        <is>
-          <t>`STI-205`</t>
-        </is>
-      </c>
-      <c r="C104" s="9" t="inlineStr">
-        <is>
-          <t>Aljabar Linear dan Matriks</t>
-        </is>
-      </c>
-      <c r="D104" s="10" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E104" s="9" t="inlineStr">
-        <is>
-          <t>Teori</t>
-        </is>
-      </c>
-      <c r="F104" s="9" t="inlineStr">
-        <is>
-          <t>Core STI</t>
-        </is>
-      </c>
-      <c r="G104" s="9" t="inlineStr">
-        <is>
-          <t>`STI-102`</t>
-        </is>
-      </c>
-    </row>
-    <row r="105" ht="16" customHeight="1">
-      <c r="A105" s="8" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="B105" s="7" t="inlineStr">
-        <is>
-          <t>`FST-203`</t>
-        </is>
-      </c>
-      <c r="C105" s="7" t="inlineStr">
-        <is>
-          <t>Struktur Data dan Algoritma</t>
-        </is>
-      </c>
-      <c r="D105" s="8" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E105" s="7" t="inlineStr">
-        <is>
-          <t>+P</t>
-        </is>
-      </c>
-      <c r="F105" s="7" t="inlineStr">
-        <is>
-          <t>FSTI</t>
-        </is>
-      </c>
-      <c r="G105" s="7" t="inlineStr">
-        <is>
-          <t>`FST-102`</t>
-        </is>
-      </c>
-    </row>
-    <row r="106" ht="16" customHeight="1">
-      <c r="A106" s="10" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="B106" s="9" t="inlineStr">
-        <is>
-          <t>`FST-204`</t>
-        </is>
-      </c>
-      <c r="C106" s="9" t="inlineStr">
-        <is>
-          <t>Pengantar Kecerdasan Artifisial &amp; Data</t>
-        </is>
-      </c>
-      <c r="D106" s="10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E106" s="9" t="inlineStr">
-        <is>
-          <t>Teori</t>
-        </is>
-      </c>
-      <c r="F106" s="9" t="inlineStr">
-        <is>
-          <t>FSTI</t>
-        </is>
-      </c>
-      <c r="G106" s="9" t="inlineStr">
-        <is>
-          <t>`FST-101`</t>
-        </is>
-      </c>
-    </row>
-    <row r="107" ht="16" customHeight="1">
-      <c r="A107" s="8" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="B107" s="7" t="inlineStr">
-        <is>
-          <t>`FST-205`</t>
-        </is>
-      </c>
-      <c r="C107" s="7" t="inlineStr">
-        <is>
-          <t>Basic English for IT</t>
-        </is>
-      </c>
-      <c r="D107" s="8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E107" s="7" t="inlineStr">
-        <is>
-          <t>Teori</t>
-        </is>
-      </c>
-      <c r="F107" s="7" t="inlineStr">
-        <is>
-          <t>FSTI</t>
-        </is>
-      </c>
-      <c r="G107" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="108" ht="16" customHeight="1">
-      <c r="A108" s="10" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="B108" s="9" t="inlineStr">
-        <is>
-          <t>`FST-206`</t>
-        </is>
-      </c>
-      <c r="C108" s="9" t="inlineStr">
-        <is>
-          <t>Etika Profesi &amp; Hukum Digital</t>
-        </is>
-      </c>
-      <c r="D108" s="10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E108" s="9" t="inlineStr">
-        <is>
-          <t>Teori</t>
-        </is>
-      </c>
-      <c r="F108" s="9" t="inlineStr">
-        <is>
-          <t>FSTI</t>
-        </is>
-      </c>
-      <c r="G108" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="109" ht="16" customHeight="1">
-      <c r="A109" s="8" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="B109" s="7" t="inlineStr">
-        <is>
-          <t>`FST-207`</t>
-        </is>
-      </c>
-      <c r="C109" s="7" t="inlineStr">
-        <is>
-          <t>Sistem Basis Data</t>
-        </is>
-      </c>
-      <c r="D109" s="8" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E109" s="7" t="inlineStr">
-        <is>
-          <t>+P</t>
-        </is>
-      </c>
-      <c r="F109" s="7" t="inlineStr">
-        <is>
-          <t>FSTI</t>
-        </is>
-      </c>
-      <c r="G109" s="7" t="inlineStr">
-        <is>
-          <t>`FST-102`</t>
-        </is>
-      </c>
-    </row>
-    <row r="110" ht="16" customHeight="1">
-      <c r="A110" s="10" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="B110" s="9" t="inlineStr">
-        <is>
-          <t>`MKU-204`</t>
-        </is>
-      </c>
-      <c r="C110" s="9" t="inlineStr">
-        <is>
-          <t>Kewirausahaan I</t>
-        </is>
-      </c>
-      <c r="D110" s="10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E110" s="9" t="inlineStr">
-        <is>
-          <t>Teori</t>
-        </is>
-      </c>
-      <c r="F110" s="9" t="inlineStr">
-        <is>
-          <t>MKWU</t>
-        </is>
-      </c>
-      <c r="G110" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="111" ht="16" customHeight="1">
-      <c r="A111" s="7" t="inlineStr">
-        <is>
-          <t>**SUBTOTAL**</t>
-        </is>
-      </c>
-      <c r="B111" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C111" s="7" t="inlineStr">
-        <is>
-          <t>**Total SKS Semester 2 (8 MK)**</t>
-        </is>
-      </c>
-      <c r="D111" s="8" t="inlineStr">
-        <is>
-          <t>**20**</t>
-        </is>
-      </c>
-      <c r="E111" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F111" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G111" s="7" t="inlineStr">
-        <is>
-          <t>**Kumulatif: 39 SKS**</t>
-        </is>
-      </c>
-    </row>
-    <row r="112"/>
-    <row r="113" ht="20" customHeight="1">
-      <c r="A113" s="3" t="inlineStr">
-        <is>
-          <t>SEMESTER 3 (20 SKS) — Penguatan Core RPL, OS, Jarkom &amp; UI/UX</t>
-        </is>
-      </c>
-      <c r="B113" s="4" t="n"/>
-      <c r="C113" s="4" t="n"/>
-      <c r="D113" s="4" t="n"/>
-      <c r="E113" s="4" t="n"/>
-      <c r="F113" s="4" t="n"/>
-      <c r="G113" s="5" t="n"/>
-    </row>
-    <row r="114" ht="26" customHeight="1">
-      <c r="A114" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="B114" s="6" t="inlineStr">
-        <is>
-          <t>Kode MK</t>
-        </is>
-      </c>
-      <c r="C114" s="6" t="inlineStr">
-        <is>
-          <t>Nama Mata Kuliah</t>
-        </is>
-      </c>
-      <c r="D114" s="6" t="inlineStr">
-        <is>
-          <t>SKS</t>
-        </is>
-      </c>
-      <c r="E114" s="6" t="inlineStr">
-        <is>
-          <t>Tipe</t>
-        </is>
-      </c>
-      <c r="F114" s="6" t="inlineStr">
-        <is>
-          <t>Kategori</t>
-        </is>
-      </c>
-      <c r="G114" s="6" t="inlineStr">
-        <is>
-          <t>Prasyarat</t>
         </is>
       </c>
     </row>
     <row r="115" ht="16" customHeight="1">
       <c r="A115" s="8" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B115" s="7" t="inlineStr">
         <is>
-          <t>`STI-306`</t>
+          <t>`STI-101`</t>
         </is>
       </c>
       <c r="C115" s="7" t="inlineStr">
         <is>
-          <t>Analisis dan Perancangan Sistem Informasi</t>
+          <t>Pengantar Sistem dan Teknologi Informasi</t>
         </is>
       </c>
       <c r="D115" s="8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E115" s="7" t="inlineStr">
@@ -4074,29 +4235,29 @@
       </c>
       <c r="G115" s="7" t="inlineStr">
         <is>
-          <t>`STI-101`, `FST-207`</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="116" ht="16" customHeight="1">
       <c r="A116" s="10" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B116" s="9" t="inlineStr">
         <is>
-          <t>`STI-307`</t>
-        </is>
-      </c>
-      <c r="C116" s="9" t="inlineStr">
-        <is>
-          <t>Sistem Cerdas</t>
+          <t>`STI-102`</t>
+        </is>
+      </c>
+      <c r="C116" s="10" t="inlineStr">
+        <is>
+          <t>Kalkulus</t>
         </is>
       </c>
       <c r="D116" s="10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E116" s="9" t="inlineStr">
@@ -4111,24 +4272,24 @@
       </c>
       <c r="G116" s="9" t="inlineStr">
         <is>
-          <t>`STI-204`, `FST-204`</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="117" ht="16" customHeight="1">
       <c r="A117" s="8" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B117" s="7" t="inlineStr">
         <is>
-          <t>`STI-308`</t>
+          <t>`STI-103`</t>
         </is>
       </c>
       <c r="C117" s="7" t="inlineStr">
         <is>
-          <t>UI/UX Design &amp; Prototyping</t>
+          <t>Arsitektur dan Organisasi Sistem Teknologi Informasi</t>
         </is>
       </c>
       <c r="D117" s="8" t="inlineStr">
@@ -4138,7 +4299,7 @@
       </c>
       <c r="E117" s="7" t="inlineStr">
         <is>
-          <t>+P</t>
+          <t>Teori</t>
         </is>
       </c>
       <c r="F117" s="7" t="inlineStr">
@@ -4148,29 +4309,29 @@
       </c>
       <c r="G117" s="7" t="inlineStr">
         <is>
-          <t>`FST-101`</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="118" ht="16" customHeight="1">
       <c r="A118" s="10" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B118" s="9" t="inlineStr">
         <is>
-          <t>`STI-309`</t>
-        </is>
-      </c>
-      <c r="C118" s="9" t="inlineStr">
-        <is>
-          <t>Rekayasa Perangkat Lunak</t>
+          <t>`MKU-101`</t>
+        </is>
+      </c>
+      <c r="C118" s="10" t="inlineStr">
+        <is>
+          <t>Agama I</t>
         </is>
       </c>
       <c r="D118" s="10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E118" s="9" t="inlineStr">
@@ -4180,34 +4341,34 @@
       </c>
       <c r="F118" s="9" t="inlineStr">
         <is>
-          <t>Core STI</t>
+          <t>MKWU</t>
         </is>
       </c>
       <c r="G118" s="9" t="inlineStr">
         <is>
-          <t>`FST-203`</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="119" ht="16" customHeight="1">
       <c r="A119" s="8" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B119" s="7" t="inlineStr">
         <is>
-          <t>`STI-310`</t>
+          <t>`MKU-102`</t>
         </is>
       </c>
       <c r="C119" s="7" t="inlineStr">
         <is>
-          <t>Sistem Operasi</t>
+          <t>Pancasila</t>
         </is>
       </c>
       <c r="D119" s="8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E119" s="7" t="inlineStr">
@@ -4217,612 +4378,612 @@
       </c>
       <c r="F119" s="7" t="inlineStr">
         <is>
-          <t>Core STI</t>
+          <t>MKWU</t>
         </is>
       </c>
       <c r="G119" s="7" t="inlineStr">
         <is>
-          <t>`STI-103`</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="120" ht="16" customHeight="1">
       <c r="A120" s="10" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B120" s="9" t="inlineStr">
         <is>
-          <t>`STI-311`</t>
+          <t>`MKU-103`</t>
         </is>
       </c>
       <c r="C120" s="9" t="inlineStr">
         <is>
-          <t>Web Front End Development</t>
+          <t>Bahasa Indonesia</t>
         </is>
       </c>
       <c r="D120" s="10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E120" s="9" t="inlineStr">
         <is>
+          <t>Teori</t>
+        </is>
+      </c>
+      <c r="F120" s="9" t="inlineStr">
+        <is>
+          <t>MKWU</t>
+        </is>
+      </c>
+      <c r="G120" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="16" customHeight="1">
+      <c r="A121" s="7" t="inlineStr">
+        <is>
+          <t>**SUBTOTAL**</t>
+        </is>
+      </c>
+      <c r="B121" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C121" s="7" t="inlineStr">
+        <is>
+          <t>**Total SKS Semester 1 (8 MK)**</t>
+        </is>
+      </c>
+      <c r="D121" s="8" t="inlineStr">
+        <is>
+          <t>**19**</t>
+        </is>
+      </c>
+      <c r="E121" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F121" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G121" s="7" t="inlineStr">
+        <is>
+          <t>**Kumulatif: 19 SKS**</t>
+        </is>
+      </c>
+    </row>
+    <row r="122"/>
+    <row r="123" ht="20" customHeight="1">
+      <c r="A123" s="3" t="inlineStr">
+        <is>
+          <t>SEMESTER 2 (20 SKS) — Fondasi Data, Matdis &amp; Logika, Aljabar &amp; Etika</t>
+        </is>
+      </c>
+      <c r="B123" s="4" t="n"/>
+      <c r="C123" s="4" t="n"/>
+      <c r="D123" s="4" t="n"/>
+      <c r="E123" s="4" t="n"/>
+      <c r="F123" s="4" t="n"/>
+      <c r="G123" s="5" t="n"/>
+    </row>
+    <row r="124" ht="26" customHeight="1">
+      <c r="A124" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B124" s="6" t="inlineStr">
+        <is>
+          <t>Kode MK</t>
+        </is>
+      </c>
+      <c r="C124" s="6" t="inlineStr">
+        <is>
+          <t>Nama Mata Kuliah</t>
+        </is>
+      </c>
+      <c r="D124" s="6" t="inlineStr">
+        <is>
+          <t>SKS</t>
+        </is>
+      </c>
+      <c r="E124" s="6" t="inlineStr">
+        <is>
+          <t>Tipe</t>
+        </is>
+      </c>
+      <c r="F124" s="6" t="inlineStr">
+        <is>
+          <t>Kategori</t>
+        </is>
+      </c>
+      <c r="G124" s="6" t="inlineStr">
+        <is>
+          <t>Prasyarat</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" ht="16" customHeight="1">
+      <c r="A125" s="8" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B125" s="7" t="inlineStr">
+        <is>
+          <t>`STI-204`</t>
+        </is>
+      </c>
+      <c r="C125" s="7" t="inlineStr">
+        <is>
+          <t>Matematika Diskrit dan Logika</t>
+        </is>
+      </c>
+      <c r="D125" s="8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E125" s="7" t="inlineStr">
+        <is>
+          <t>Teori</t>
+        </is>
+      </c>
+      <c r="F125" s="7" t="inlineStr">
+        <is>
+          <t>Core STI</t>
+        </is>
+      </c>
+      <c r="G125" s="7" t="inlineStr">
+        <is>
+          <t>`STI-103`</t>
+        </is>
+      </c>
+    </row>
+    <row r="126" ht="16" customHeight="1">
+      <c r="A126" s="10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B126" s="9" t="inlineStr">
+        <is>
+          <t>`STI-205`</t>
+        </is>
+      </c>
+      <c r="C126" s="9" t="inlineStr">
+        <is>
+          <t>Aljabar Linear dan Matriks</t>
+        </is>
+      </c>
+      <c r="D126" s="10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E126" s="9" t="inlineStr">
+        <is>
+          <t>Teori</t>
+        </is>
+      </c>
+      <c r="F126" s="9" t="inlineStr">
+        <is>
+          <t>Core STI</t>
+        </is>
+      </c>
+      <c r="G126" s="9" t="inlineStr">
+        <is>
+          <t>`STI-102`</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="16" customHeight="1">
+      <c r="A127" s="8" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B127" s="7" t="inlineStr">
+        <is>
+          <t>`FST-203`</t>
+        </is>
+      </c>
+      <c r="C127" s="7" t="inlineStr">
+        <is>
+          <t>Struktur Data dan Algoritma</t>
+        </is>
+      </c>
+      <c r="D127" s="8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E127" s="7" t="inlineStr">
+        <is>
           <t>+P</t>
         </is>
       </c>
-      <c r="F120" s="9" t="inlineStr">
+      <c r="F127" s="7" t="inlineStr">
+        <is>
+          <t>FSTI</t>
+        </is>
+      </c>
+      <c r="G127" s="7" t="inlineStr">
+        <is>
+          <t>`FST-102`</t>
+        </is>
+      </c>
+    </row>
+    <row r="128" ht="16" customHeight="1">
+      <c r="A128" s="10" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B128" s="9" t="inlineStr">
+        <is>
+          <t>`FST-204`</t>
+        </is>
+      </c>
+      <c r="C128" s="9" t="inlineStr">
+        <is>
+          <t>Pengantar Kecerdasan Artifisial &amp; Data</t>
+        </is>
+      </c>
+      <c r="D128" s="10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E128" s="9" t="inlineStr">
+        <is>
+          <t>Teori</t>
+        </is>
+      </c>
+      <c r="F128" s="9" t="inlineStr">
+        <is>
+          <t>FSTI</t>
+        </is>
+      </c>
+      <c r="G128" s="9" t="inlineStr">
+        <is>
+          <t>`FST-101`</t>
+        </is>
+      </c>
+    </row>
+    <row r="129" ht="16" customHeight="1">
+      <c r="A129" s="8" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B129" s="7" t="inlineStr">
+        <is>
+          <t>`FST-205`</t>
+        </is>
+      </c>
+      <c r="C129" s="7" t="inlineStr">
+        <is>
+          <t>Basic English for IT</t>
+        </is>
+      </c>
+      <c r="D129" s="8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E129" s="7" t="inlineStr">
+        <is>
+          <t>Teori</t>
+        </is>
+      </c>
+      <c r="F129" s="7" t="inlineStr">
+        <is>
+          <t>FSTI</t>
+        </is>
+      </c>
+      <c r="G129" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="130" ht="16" customHeight="1">
+      <c r="A130" s="10" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="B130" s="9" t="inlineStr">
+        <is>
+          <t>`FST-206`</t>
+        </is>
+      </c>
+      <c r="C130" s="9" t="inlineStr">
+        <is>
+          <t>Etika Profesi &amp; Hukum Digital</t>
+        </is>
+      </c>
+      <c r="D130" s="10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E130" s="9" t="inlineStr">
+        <is>
+          <t>Teori</t>
+        </is>
+      </c>
+      <c r="F130" s="9" t="inlineStr">
+        <is>
+          <t>FSTI</t>
+        </is>
+      </c>
+      <c r="G130" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="131" ht="16" customHeight="1">
+      <c r="A131" s="8" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B131" s="7" t="inlineStr">
+        <is>
+          <t>`FST-207`</t>
+        </is>
+      </c>
+      <c r="C131" s="7" t="inlineStr">
+        <is>
+          <t>Sistem Basis Data</t>
+        </is>
+      </c>
+      <c r="D131" s="8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E131" s="7" t="inlineStr">
+        <is>
+          <t>+P</t>
+        </is>
+      </c>
+      <c r="F131" s="7" t="inlineStr">
+        <is>
+          <t>FSTI</t>
+        </is>
+      </c>
+      <c r="G131" s="7" t="inlineStr">
+        <is>
+          <t>`FST-102`</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" ht="16" customHeight="1">
+      <c r="A132" s="10" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B132" s="9" t="inlineStr">
+        <is>
+          <t>`MKU-204`</t>
+        </is>
+      </c>
+      <c r="C132" s="9" t="inlineStr">
+        <is>
+          <t>Kewirausahaan I</t>
+        </is>
+      </c>
+      <c r="D132" s="10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E132" s="9" t="inlineStr">
+        <is>
+          <t>Teori</t>
+        </is>
+      </c>
+      <c r="F132" s="9" t="inlineStr">
+        <is>
+          <t>MKWU</t>
+        </is>
+      </c>
+      <c r="G132" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="133" ht="16" customHeight="1">
+      <c r="A133" s="7" t="inlineStr">
+        <is>
+          <t>**SUBTOTAL**</t>
+        </is>
+      </c>
+      <c r="B133" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C133" s="7" t="inlineStr">
+        <is>
+          <t>**Total SKS Semester 2 (8 MK)**</t>
+        </is>
+      </c>
+      <c r="D133" s="8" t="inlineStr">
+        <is>
+          <t>**20**</t>
+        </is>
+      </c>
+      <c r="E133" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F133" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G133" s="7" t="inlineStr">
+        <is>
+          <t>**Kumulatif: 39 SKS**</t>
+        </is>
+      </c>
+    </row>
+    <row r="134"/>
+    <row r="135" ht="20" customHeight="1">
+      <c r="A135" s="3" t="inlineStr">
+        <is>
+          <t>SEMESTER 3 (20 SKS) — Penguatan Core RPL, OS, Jarkom &amp; UI/UX</t>
+        </is>
+      </c>
+      <c r="B135" s="4" t="n"/>
+      <c r="C135" s="4" t="n"/>
+      <c r="D135" s="4" t="n"/>
+      <c r="E135" s="4" t="n"/>
+      <c r="F135" s="4" t="n"/>
+      <c r="G135" s="5" t="n"/>
+    </row>
+    <row r="136" ht="26" customHeight="1">
+      <c r="A136" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B136" s="6" t="inlineStr">
+        <is>
+          <t>Kode MK</t>
+        </is>
+      </c>
+      <c r="C136" s="6" t="inlineStr">
+        <is>
+          <t>Nama Mata Kuliah</t>
+        </is>
+      </c>
+      <c r="D136" s="6" t="inlineStr">
+        <is>
+          <t>SKS</t>
+        </is>
+      </c>
+      <c r="E136" s="6" t="inlineStr">
+        <is>
+          <t>Tipe</t>
+        </is>
+      </c>
+      <c r="F136" s="6" t="inlineStr">
+        <is>
+          <t>Kategori</t>
+        </is>
+      </c>
+      <c r="G136" s="6" t="inlineStr">
+        <is>
+          <t>Prasyarat</t>
+        </is>
+      </c>
+    </row>
+    <row r="137" ht="16" customHeight="1">
+      <c r="A137" s="8" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B137" s="7" t="inlineStr">
+        <is>
+          <t>`STI-306`</t>
+        </is>
+      </c>
+      <c r="C137" s="7" t="inlineStr">
+        <is>
+          <t>Analisis dan Perancangan Sistem Informasi</t>
+        </is>
+      </c>
+      <c r="D137" s="8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E137" s="7" t="inlineStr">
+        <is>
+          <t>Teori</t>
+        </is>
+      </c>
+      <c r="F137" s="7" t="inlineStr">
         <is>
           <t>Core STI</t>
         </is>
       </c>
-      <c r="G120" s="9" t="inlineStr">
-        <is>
-          <t>`FST-102`</t>
-        </is>
-      </c>
-    </row>
-    <row r="121" ht="16" customHeight="1">
-      <c r="A121" s="8" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="B121" s="7" t="inlineStr">
-        <is>
-          <t>`STI-312`</t>
-        </is>
-      </c>
-      <c r="C121" s="7" t="inlineStr">
-        <is>
-          <t>Jaringan Komputer</t>
-        </is>
-      </c>
-      <c r="D121" s="8" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E121" s="7" t="inlineStr">
-        <is>
-          <t>+P</t>
-        </is>
-      </c>
-      <c r="F121" s="7" t="inlineStr">
+      <c r="G137" s="7" t="inlineStr">
+        <is>
+          <t>`STI-101`, `FST-207`</t>
+        </is>
+      </c>
+    </row>
+    <row r="138" ht="16" customHeight="1">
+      <c r="A138" s="10" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B138" s="9" t="inlineStr">
+        <is>
+          <t>`STI-307`</t>
+        </is>
+      </c>
+      <c r="C138" s="9" t="inlineStr">
+        <is>
+          <t>Sistem Cerdas</t>
+        </is>
+      </c>
+      <c r="D138" s="10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E138" s="9" t="inlineStr">
+        <is>
+          <t>Teori</t>
+        </is>
+      </c>
+      <c r="F138" s="9" t="inlineStr">
         <is>
           <t>Core STI</t>
         </is>
       </c>
-      <c r="G121" s="7" t="inlineStr">
-        <is>
-          <t>`STI-103`</t>
-        </is>
-      </c>
-    </row>
-    <row r="122" ht="16" customHeight="1">
-      <c r="A122" s="9" t="inlineStr">
-        <is>
-          <t>**SUBTOTAL**</t>
-        </is>
-      </c>
-      <c r="B122" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C122" s="9" t="inlineStr">
-        <is>
-          <t>**Total SKS Semester 3 (7 MK)**</t>
-        </is>
-      </c>
-      <c r="D122" s="10" t="inlineStr">
-        <is>
-          <t>**20**</t>
-        </is>
-      </c>
-      <c r="E122" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F122" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G122" s="9" t="inlineStr">
-        <is>
-          <t>**Kumulatif: 59 SKS**</t>
-        </is>
-      </c>
-    </row>
-    <row r="123"/>
-    <row r="124" ht="20" customHeight="1">
-      <c r="A124" s="3" t="inlineStr">
-        <is>
-          <t>SEMESTER 4 (21 SKS) — Penguatan Core AI/ML, NLP, DW &amp; Cloud</t>
-        </is>
-      </c>
-      <c r="B124" s="4" t="n"/>
-      <c r="C124" s="4" t="n"/>
-      <c r="D124" s="4" t="n"/>
-      <c r="E124" s="4" t="n"/>
-      <c r="F124" s="4" t="n"/>
-      <c r="G124" s="5" t="n"/>
-    </row>
-    <row r="125" ht="26" customHeight="1">
-      <c r="A125" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="B125" s="6" t="inlineStr">
-        <is>
-          <t>Kode MK</t>
-        </is>
-      </c>
-      <c r="C125" s="6" t="inlineStr">
-        <is>
-          <t>Nama Mata Kuliah</t>
-        </is>
-      </c>
-      <c r="D125" s="6" t="inlineStr">
-        <is>
-          <t>SKS</t>
-        </is>
-      </c>
-      <c r="E125" s="6" t="inlineStr">
-        <is>
-          <t>Tipe</t>
-        </is>
-      </c>
-      <c r="F125" s="6" t="inlineStr">
-        <is>
-          <t>Kategori</t>
-        </is>
-      </c>
-      <c r="G125" s="6" t="inlineStr">
-        <is>
-          <t>Prasyarat</t>
-        </is>
-      </c>
-    </row>
-    <row r="126" ht="16" customHeight="1">
-      <c r="A126" s="8" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="B126" s="7" t="inlineStr">
-        <is>
-          <t>`STI-413`</t>
-        </is>
-      </c>
-      <c r="C126" s="7" t="inlineStr">
-        <is>
-          <t>Machine Learning</t>
-        </is>
-      </c>
-      <c r="D126" s="8" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E126" s="7" t="inlineStr">
-        <is>
-          <t>+P</t>
-        </is>
-      </c>
-      <c r="F126" s="7" t="inlineStr">
-        <is>
-          <t>Core STI</t>
-        </is>
-      </c>
-      <c r="G126" s="7" t="inlineStr">
-        <is>
-          <t>`STI-205`, `STI-307`</t>
-        </is>
-      </c>
-    </row>
-    <row r="127" ht="16" customHeight="1">
-      <c r="A127" s="10" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="B127" s="9" t="inlineStr">
-        <is>
-          <t>`STI-414`</t>
-        </is>
-      </c>
-      <c r="C127" s="9" t="inlineStr">
-        <is>
-          <t>Pengantar NLP &amp; Information Retrieval</t>
-        </is>
-      </c>
-      <c r="D127" s="10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E127" s="9" t="inlineStr">
-        <is>
-          <t>+P</t>
-        </is>
-      </c>
-      <c r="F127" s="9" t="inlineStr">
-        <is>
-          <t>Core STI</t>
-        </is>
-      </c>
-      <c r="G127" s="9" t="inlineStr">
-        <is>
-          <t>`STI-307`</t>
-        </is>
-      </c>
-    </row>
-    <row r="128" ht="16" customHeight="1">
-      <c r="A128" s="8" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="B128" s="7" t="inlineStr">
-        <is>
-          <t>`STI-415`</t>
-        </is>
-      </c>
-      <c r="C128" s="7" t="inlineStr">
-        <is>
-          <t>Data Warehouse &amp; Business Intelligence</t>
-        </is>
-      </c>
-      <c r="D128" s="8" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E128" s="7" t="inlineStr">
-        <is>
-          <t>+P</t>
-        </is>
-      </c>
-      <c r="F128" s="7" t="inlineStr">
-        <is>
-          <t>Core STI</t>
-        </is>
-      </c>
-      <c r="G128" s="7" t="inlineStr">
-        <is>
-          <t>`FST-207`</t>
-        </is>
-      </c>
-    </row>
-    <row r="129" ht="16" customHeight="1">
-      <c r="A129" s="10" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="B129" s="9" t="inlineStr">
-        <is>
-          <t>`STI-416`</t>
-        </is>
-      </c>
-      <c r="C129" s="9" t="inlineStr">
-        <is>
-          <t>Web Back End Development</t>
-        </is>
-      </c>
-      <c r="D129" s="10" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E129" s="9" t="inlineStr">
-        <is>
-          <t>+P</t>
-        </is>
-      </c>
-      <c r="F129" s="9" t="inlineStr">
-        <is>
-          <t>Core STI</t>
-        </is>
-      </c>
-      <c r="G129" s="9" t="inlineStr">
-        <is>
-          <t>`FST-207`, `STI-311`</t>
-        </is>
-      </c>
-    </row>
-    <row r="130" ht="16" customHeight="1">
-      <c r="A130" s="8" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="B130" s="7" t="inlineStr">
-        <is>
-          <t>`STI-417`</t>
-        </is>
-      </c>
-      <c r="C130" s="7" t="inlineStr">
-        <is>
-          <t>Komputasi Awan (Cloud Computing)</t>
-        </is>
-      </c>
-      <c r="D130" s="8" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E130" s="7" t="inlineStr">
-        <is>
-          <t>Teori</t>
-        </is>
-      </c>
-      <c r="F130" s="7" t="inlineStr">
-        <is>
-          <t>Core STI</t>
-        </is>
-      </c>
-      <c r="G130" s="7" t="inlineStr">
-        <is>
-          <t>`STI-312`, `STI-310`</t>
-        </is>
-      </c>
-    </row>
-    <row r="131" ht="16" customHeight="1">
-      <c r="A131" s="10" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="B131" s="9" t="inlineStr">
-        <is>
-          <t>`STI-418`</t>
-        </is>
-      </c>
-      <c r="C131" s="9" t="inlineStr">
-        <is>
-          <t>Dasar Keamanan Informasi</t>
-        </is>
-      </c>
-      <c r="D131" s="10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E131" s="9" t="inlineStr">
-        <is>
-          <t>Teori</t>
-        </is>
-      </c>
-      <c r="F131" s="9" t="inlineStr">
-        <is>
-          <t>Core STI</t>
-        </is>
-      </c>
-      <c r="G131" s="9" t="inlineStr">
-        <is>
-          <t>`STI-312`</t>
-        </is>
-      </c>
-    </row>
-    <row r="132" ht="16" customHeight="1">
-      <c r="A132" s="8" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="B132" s="7" t="inlineStr">
-        <is>
-          <t>`FST-408`</t>
-        </is>
-      </c>
-      <c r="C132" s="7" t="inlineStr">
-        <is>
-          <t>Probabilitas dan Statistika</t>
-        </is>
-      </c>
-      <c r="D132" s="8" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E132" s="7" t="inlineStr">
-        <is>
-          <t>Teori</t>
-        </is>
-      </c>
-      <c r="F132" s="7" t="inlineStr">
-        <is>
-          <t>FSTI</t>
-        </is>
-      </c>
-      <c r="G132" s="7" t="inlineStr">
-        <is>
-          <t>`STI-102`</t>
-        </is>
-      </c>
-    </row>
-    <row r="133" ht="16" customHeight="1">
-      <c r="A133" s="10" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="B133" s="9" t="inlineStr">
-        <is>
-          <t>`MKU-405`</t>
-        </is>
-      </c>
-      <c r="C133" s="9" t="inlineStr">
-        <is>
-          <t>Kewarganegaraan</t>
-        </is>
-      </c>
-      <c r="D133" s="10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E133" s="9" t="inlineStr">
-        <is>
-          <t>Teori</t>
-        </is>
-      </c>
-      <c r="F133" s="9" t="inlineStr">
-        <is>
-          <t>MKWU</t>
-        </is>
-      </c>
-      <c r="G133" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="134" ht="16" customHeight="1">
-      <c r="A134" s="8" t="inlineStr">
-        <is>
-          <t>31.B</t>
-        </is>
-      </c>
-      <c r="B134" s="7" t="inlineStr">
-        <is>
-          <t>`MKU-406`</t>
-        </is>
-      </c>
-      <c r="C134" s="8" t="inlineStr">
-        <is>
-          <t>Agama II</t>
-        </is>
-      </c>
-      <c r="D134" s="8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E134" s="7" t="inlineStr">
-        <is>
-          <t>Teori</t>
-        </is>
-      </c>
-      <c r="F134" s="7" t="inlineStr">
-        <is>
-          <t>MKWU</t>
-        </is>
-      </c>
-      <c r="G134" s="7" t="inlineStr">
-        <is>
-          <t>— (Kebijakan UWG, Sem 4)</t>
-        </is>
-      </c>
-    </row>
-    <row r="135" ht="16" customHeight="1">
-      <c r="A135" s="9" t="inlineStr">
-        <is>
-          <t>**SUBTOTAL**</t>
-        </is>
-      </c>
-      <c r="B135" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C135" s="9" t="inlineStr">
-        <is>
-          <t>**Total SKS Semester 4 (8 MK + 1 MK 0 SKS)**</t>
-        </is>
-      </c>
-      <c r="D135" s="10" t="inlineStr">
-        <is>
-          <t>**21**</t>
-        </is>
-      </c>
-      <c r="E135" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F135" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G135" s="9" t="inlineStr">
-        <is>
-          <t>**Kumulatif: 80 SKS**</t>
-        </is>
-      </c>
-    </row>
-    <row r="136"/>
-    <row r="137" ht="20" customHeight="1">
-      <c r="A137" s="3" t="inlineStr">
-        <is>
-          <t>SEMESTER 5 (21 SKS) — Tahap Spesialisasi Keamanan Lanjut, IoT &amp; Peminatan 1</t>
-        </is>
-      </c>
-      <c r="B137" s="4" t="n"/>
-      <c r="C137" s="4" t="n"/>
-      <c r="D137" s="4" t="n"/>
-      <c r="E137" s="4" t="n"/>
-      <c r="F137" s="4" t="n"/>
-      <c r="G137" s="5" t="n"/>
-    </row>
-    <row r="138" ht="26" customHeight="1">
-      <c r="A138" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="B138" s="6" t="inlineStr">
-        <is>
-          <t>Kode MK</t>
-        </is>
-      </c>
-      <c r="C138" s="6" t="inlineStr">
-        <is>
-          <t>Nama Mata Kuliah</t>
-        </is>
-      </c>
-      <c r="D138" s="6" t="inlineStr">
-        <is>
-          <t>SKS</t>
-        </is>
-      </c>
-      <c r="E138" s="6" t="inlineStr">
-        <is>
-          <t>Tipe</t>
-        </is>
-      </c>
-      <c r="F138" s="6" t="inlineStr">
-        <is>
-          <t>Kategori</t>
-        </is>
-      </c>
-      <c r="G138" s="6" t="inlineStr">
-        <is>
-          <t>Prasyarat</t>
+      <c r="G138" s="9" t="inlineStr">
+        <is>
+          <t>`STI-204`, `FST-204`</t>
         </is>
       </c>
     </row>
     <row r="139" ht="16" customHeight="1">
       <c r="A139" s="8" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B139" s="7" t="inlineStr">
         <is>
-          <t>`STI-519`</t>
+          <t>`STI-308`</t>
         </is>
       </c>
       <c r="C139" s="7" t="inlineStr">
         <is>
-          <t>Keamanan Informasi Lanjut</t>
+          <t>UI/UX Design &amp; Prototyping</t>
         </is>
       </c>
       <c r="D139" s="8" t="inlineStr">
@@ -4832,7 +4993,7 @@
       </c>
       <c r="E139" s="7" t="inlineStr">
         <is>
-          <t>Teori</t>
+          <t>+P</t>
         </is>
       </c>
       <c r="F139" s="7" t="inlineStr">
@@ -4842,24 +5003,24 @@
       </c>
       <c r="G139" s="7" t="inlineStr">
         <is>
-          <t>`STI-418`</t>
+          <t>`FST-101`</t>
         </is>
       </c>
     </row>
     <row r="140" ht="16" customHeight="1">
       <c r="A140" s="10" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B140" s="9" t="inlineStr">
         <is>
-          <t>`STI-520`</t>
+          <t>`STI-309`</t>
         </is>
       </c>
       <c r="C140" s="9" t="inlineStr">
         <is>
-          <t>Data Mining &amp; Visualisasi Data</t>
+          <t>Rekayasa Perangkat Lunak</t>
         </is>
       </c>
       <c r="D140" s="10" t="inlineStr">
@@ -4869,7 +5030,7 @@
       </c>
       <c r="E140" s="9" t="inlineStr">
         <is>
-          <t>+P</t>
+          <t>Teori</t>
         </is>
       </c>
       <c r="F140" s="9" t="inlineStr">
@@ -4879,24 +5040,24 @@
       </c>
       <c r="G140" s="9" t="inlineStr">
         <is>
-          <t>`STI-413`, `STI-415`</t>
+          <t>`FST-203`</t>
         </is>
       </c>
     </row>
     <row r="141" ht="16" customHeight="1">
       <c r="A141" s="8" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B141" s="7" t="inlineStr">
         <is>
-          <t>`STI-521`</t>
+          <t>`STI-310`</t>
         </is>
       </c>
       <c r="C141" s="7" t="inlineStr">
         <is>
-          <t>Internet of Things (IoT)</t>
+          <t>Sistem Operasi</t>
         </is>
       </c>
       <c r="D141" s="8" t="inlineStr">
@@ -4906,7 +5067,7 @@
       </c>
       <c r="E141" s="7" t="inlineStr">
         <is>
-          <t>+P</t>
+          <t>Teori</t>
         </is>
       </c>
       <c r="F141" s="7" t="inlineStr">
@@ -4916,24 +5077,24 @@
       </c>
       <c r="G141" s="7" t="inlineStr">
         <is>
-          <t>`STI-312`, `STI-310`</t>
+          <t>`STI-103`</t>
         </is>
       </c>
     </row>
     <row r="142" ht="16" customHeight="1">
       <c r="A142" s="10" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B142" s="9" t="inlineStr">
         <is>
-          <t>`STI-522`</t>
+          <t>`STI-311`</t>
         </is>
       </c>
       <c r="C142" s="9" t="inlineStr">
         <is>
-          <t>Pemrograman Aplikasi Mobile</t>
+          <t>Web Front End Development</t>
         </is>
       </c>
       <c r="D142" s="10" t="inlineStr">
@@ -4953,886 +5114,886 @@
       </c>
       <c r="G142" s="9" t="inlineStr">
         <is>
-          <t>`STI-311`, `STI-416`</t>
+          <t>`FST-102`</t>
         </is>
       </c>
     </row>
     <row r="143" ht="16" customHeight="1">
       <c r="A143" s="8" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B143" s="7" t="inlineStr">
+        <is>
+          <t>`STI-312`</t>
+        </is>
+      </c>
+      <c r="C143" s="7" t="inlineStr">
+        <is>
+          <t>Jaringan Komputer</t>
+        </is>
+      </c>
+      <c r="D143" s="8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E143" s="7" t="inlineStr">
+        <is>
+          <t>+P</t>
+        </is>
+      </c>
+      <c r="F143" s="7" t="inlineStr">
+        <is>
+          <t>Core STI</t>
+        </is>
+      </c>
+      <c r="G143" s="7" t="inlineStr">
+        <is>
+          <t>`STI-103`</t>
+        </is>
+      </c>
+    </row>
+    <row r="144" ht="16" customHeight="1">
+      <c r="A144" s="9" t="inlineStr">
+        <is>
+          <t>**SUBTOTAL**</t>
+        </is>
+      </c>
+      <c r="B144" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C144" s="9" t="inlineStr">
+        <is>
+          <t>**Total SKS Semester 3 (7 MK)**</t>
+        </is>
+      </c>
+      <c r="D144" s="10" t="inlineStr">
+        <is>
+          <t>**20**</t>
+        </is>
+      </c>
+      <c r="E144" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F144" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G144" s="9" t="inlineStr">
+        <is>
+          <t>**Kumulatif: 59 SKS**</t>
+        </is>
+      </c>
+    </row>
+    <row r="145"/>
+    <row r="146" ht="20" customHeight="1">
+      <c r="A146" s="3" t="inlineStr">
+        <is>
+          <t>SEMESTER 4 (21 SKS) — Penguatan Core AI/ML, NLP, DW &amp; Cloud</t>
+        </is>
+      </c>
+      <c r="B146" s="4" t="n"/>
+      <c r="C146" s="4" t="n"/>
+      <c r="D146" s="4" t="n"/>
+      <c r="E146" s="4" t="n"/>
+      <c r="F146" s="4" t="n"/>
+      <c r="G146" s="5" t="n"/>
+    </row>
+    <row r="147" ht="26" customHeight="1">
+      <c r="A147" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B147" s="6" t="inlineStr">
+        <is>
+          <t>Kode MK</t>
+        </is>
+      </c>
+      <c r="C147" s="6" t="inlineStr">
+        <is>
+          <t>Nama Mata Kuliah</t>
+        </is>
+      </c>
+      <c r="D147" s="6" t="inlineStr">
+        <is>
+          <t>SKS</t>
+        </is>
+      </c>
+      <c r="E147" s="6" t="inlineStr">
+        <is>
+          <t>Tipe</t>
+        </is>
+      </c>
+      <c r="F147" s="6" t="inlineStr">
+        <is>
+          <t>Kategori</t>
+        </is>
+      </c>
+      <c r="G147" s="6" t="inlineStr">
+        <is>
+          <t>Prasyarat</t>
+        </is>
+      </c>
+    </row>
+    <row r="148" ht="16" customHeight="1">
+      <c r="A148" s="8" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="B148" s="7" t="inlineStr">
+        <is>
+          <t>`STI-413`</t>
+        </is>
+      </c>
+      <c r="C148" s="7" t="inlineStr">
+        <is>
+          <t>Machine Learning</t>
+        </is>
+      </c>
+      <c r="D148" s="8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E148" s="7" t="inlineStr">
+        <is>
+          <t>+P</t>
+        </is>
+      </c>
+      <c r="F148" s="7" t="inlineStr">
+        <is>
+          <t>Core STI</t>
+        </is>
+      </c>
+      <c r="G148" s="7" t="inlineStr">
+        <is>
+          <t>`STI-205`, `STI-307`</t>
+        </is>
+      </c>
+    </row>
+    <row r="149" ht="16" customHeight="1">
+      <c r="A149" s="10" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B149" s="9" t="inlineStr">
+        <is>
+          <t>`STI-414`</t>
+        </is>
+      </c>
+      <c r="C149" s="9" t="inlineStr">
+        <is>
+          <t>Pengantar NLP &amp; Information Retrieval</t>
+        </is>
+      </c>
+      <c r="D149" s="10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E149" s="9" t="inlineStr">
+        <is>
+          <t>+P</t>
+        </is>
+      </c>
+      <c r="F149" s="9" t="inlineStr">
+        <is>
+          <t>Core STI</t>
+        </is>
+      </c>
+      <c r="G149" s="9" t="inlineStr">
+        <is>
+          <t>`STI-307`</t>
+        </is>
+      </c>
+    </row>
+    <row r="150" ht="16" customHeight="1">
+      <c r="A150" s="8" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B150" s="7" t="inlineStr">
+        <is>
+          <t>`STI-415`</t>
+        </is>
+      </c>
+      <c r="C150" s="7" t="inlineStr">
+        <is>
+          <t>Data Warehouse &amp; Business Intelligence</t>
+        </is>
+      </c>
+      <c r="D150" s="8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E150" s="7" t="inlineStr">
+        <is>
+          <t>+P</t>
+        </is>
+      </c>
+      <c r="F150" s="7" t="inlineStr">
+        <is>
+          <t>Core STI</t>
+        </is>
+      </c>
+      <c r="G150" s="7" t="inlineStr">
+        <is>
+          <t>`FST-207`</t>
+        </is>
+      </c>
+    </row>
+    <row r="151" ht="16" customHeight="1">
+      <c r="A151" s="10" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B151" s="9" t="inlineStr">
+        <is>
+          <t>`STI-416`</t>
+        </is>
+      </c>
+      <c r="C151" s="9" t="inlineStr">
+        <is>
+          <t>Web Back End Development</t>
+        </is>
+      </c>
+      <c r="D151" s="10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E151" s="9" t="inlineStr">
+        <is>
+          <t>+P</t>
+        </is>
+      </c>
+      <c r="F151" s="9" t="inlineStr">
+        <is>
+          <t>Core STI</t>
+        </is>
+      </c>
+      <c r="G151" s="9" t="inlineStr">
+        <is>
+          <t>`FST-207`, `STI-311`</t>
+        </is>
+      </c>
+    </row>
+    <row r="152" ht="16" customHeight="1">
+      <c r="A152" s="8" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B152" s="7" t="inlineStr">
+        <is>
+          <t>`STI-417`</t>
+        </is>
+      </c>
+      <c r="C152" s="7" t="inlineStr">
+        <is>
+          <t>Komputasi Awan (Cloud Computing)</t>
+        </is>
+      </c>
+      <c r="D152" s="8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E152" s="7" t="inlineStr">
+        <is>
+          <t>Teori</t>
+        </is>
+      </c>
+      <c r="F152" s="7" t="inlineStr">
+        <is>
+          <t>Core STI</t>
+        </is>
+      </c>
+      <c r="G152" s="7" t="inlineStr">
+        <is>
+          <t>`STI-312`, `STI-310`</t>
+        </is>
+      </c>
+    </row>
+    <row r="153" ht="16" customHeight="1">
+      <c r="A153" s="10" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B153" s="9" t="inlineStr">
+        <is>
+          <t>`STI-418`</t>
+        </is>
+      </c>
+      <c r="C153" s="9" t="inlineStr">
+        <is>
+          <t>Dasar Keamanan Informasi</t>
+        </is>
+      </c>
+      <c r="D153" s="10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E153" s="9" t="inlineStr">
+        <is>
+          <t>Teori</t>
+        </is>
+      </c>
+      <c r="F153" s="9" t="inlineStr">
+        <is>
+          <t>Core STI</t>
+        </is>
+      </c>
+      <c r="G153" s="9" t="inlineStr">
+        <is>
+          <t>`STI-312`</t>
+        </is>
+      </c>
+    </row>
+    <row r="154" ht="16" customHeight="1">
+      <c r="A154" s="8" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B154" s="7" t="inlineStr">
+        <is>
+          <t>`FST-408`</t>
+        </is>
+      </c>
+      <c r="C154" s="7" t="inlineStr">
+        <is>
+          <t>Probabilitas dan Statistika</t>
+        </is>
+      </c>
+      <c r="D154" s="8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E154" s="7" t="inlineStr">
+        <is>
+          <t>Teori</t>
+        </is>
+      </c>
+      <c r="F154" s="7" t="inlineStr">
+        <is>
+          <t>FSTI</t>
+        </is>
+      </c>
+      <c r="G154" s="7" t="inlineStr">
+        <is>
+          <t>`STI-102`</t>
+        </is>
+      </c>
+    </row>
+    <row r="155" ht="16" customHeight="1">
+      <c r="A155" s="10" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B155" s="9" t="inlineStr">
+        <is>
+          <t>`MKU-405`</t>
+        </is>
+      </c>
+      <c r="C155" s="9" t="inlineStr">
+        <is>
+          <t>Kewarganegaraan</t>
+        </is>
+      </c>
+      <c r="D155" s="10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E155" s="9" t="inlineStr">
+        <is>
+          <t>Teori</t>
+        </is>
+      </c>
+      <c r="F155" s="9" t="inlineStr">
+        <is>
+          <t>MKWU</t>
+        </is>
+      </c>
+      <c r="G155" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="156" ht="16" customHeight="1">
+      <c r="A156" s="8" t="inlineStr">
+        <is>
+          <t>31.B</t>
+        </is>
+      </c>
+      <c r="B156" s="7" t="inlineStr">
+        <is>
+          <t>`MKU-406`</t>
+        </is>
+      </c>
+      <c r="C156" s="8" t="inlineStr">
+        <is>
+          <t>Agama II</t>
+        </is>
+      </c>
+      <c r="D156" s="8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E156" s="7" t="inlineStr">
+        <is>
+          <t>Teori</t>
+        </is>
+      </c>
+      <c r="F156" s="7" t="inlineStr">
+        <is>
+          <t>MKWU</t>
+        </is>
+      </c>
+      <c r="G156" s="7" t="inlineStr">
+        <is>
+          <t>— (Kebijakan UWG, Sem 4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="157" ht="16" customHeight="1">
+      <c r="A157" s="9" t="inlineStr">
+        <is>
+          <t>**SUBTOTAL**</t>
+        </is>
+      </c>
+      <c r="B157" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C157" s="9" t="inlineStr">
+        <is>
+          <t>**Total SKS Semester 4 (8 MK + 1 MK 0 SKS)**</t>
+        </is>
+      </c>
+      <c r="D157" s="10" t="inlineStr">
+        <is>
+          <t>**21**</t>
+        </is>
+      </c>
+      <c r="E157" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F157" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G157" s="9" t="inlineStr">
+        <is>
+          <t>**Kumulatif: 80 SKS**</t>
+        </is>
+      </c>
+    </row>
+    <row r="158"/>
+    <row r="159" ht="20" customHeight="1">
+      <c r="A159" s="3" t="inlineStr">
+        <is>
+          <t>SEMESTER 5 (21 SKS) — Tahap Spesialisasi Keamanan Lanjut, IoT &amp; Peminatan 1</t>
+        </is>
+      </c>
+      <c r="B159" s="4" t="n"/>
+      <c r="C159" s="4" t="n"/>
+      <c r="D159" s="4" t="n"/>
+      <c r="E159" s="4" t="n"/>
+      <c r="F159" s="4" t="n"/>
+      <c r="G159" s="5" t="n"/>
+    </row>
+    <row r="160" ht="26" customHeight="1">
+      <c r="A160" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B160" s="6" t="inlineStr">
+        <is>
+          <t>Kode MK</t>
+        </is>
+      </c>
+      <c r="C160" s="6" t="inlineStr">
+        <is>
+          <t>Nama Mata Kuliah</t>
+        </is>
+      </c>
+      <c r="D160" s="6" t="inlineStr">
+        <is>
+          <t>SKS</t>
+        </is>
+      </c>
+      <c r="E160" s="6" t="inlineStr">
+        <is>
+          <t>Tipe</t>
+        </is>
+      </c>
+      <c r="F160" s="6" t="inlineStr">
+        <is>
+          <t>Kategori</t>
+        </is>
+      </c>
+      <c r="G160" s="6" t="inlineStr">
+        <is>
+          <t>Prasyarat</t>
+        </is>
+      </c>
+    </row>
+    <row r="161" ht="16" customHeight="1">
+      <c r="A161" s="8" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B161" s="7" t="inlineStr">
+        <is>
+          <t>`STI-519`</t>
+        </is>
+      </c>
+      <c r="C161" s="7" t="inlineStr">
+        <is>
+          <t>Keamanan Informasi Lanjut</t>
+        </is>
+      </c>
+      <c r="D161" s="8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E161" s="7" t="inlineStr">
+        <is>
+          <t>Teori</t>
+        </is>
+      </c>
+      <c r="F161" s="7" t="inlineStr">
+        <is>
+          <t>Core STI</t>
+        </is>
+      </c>
+      <c r="G161" s="7" t="inlineStr">
+        <is>
+          <t>`STI-418`</t>
+        </is>
+      </c>
+    </row>
+    <row r="162" ht="16" customHeight="1">
+      <c r="A162" s="10" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B162" s="9" t="inlineStr">
+        <is>
+          <t>`STI-520`</t>
+        </is>
+      </c>
+      <c r="C162" s="9" t="inlineStr">
+        <is>
+          <t>Data Mining &amp; Visualisasi Data</t>
+        </is>
+      </c>
+      <c r="D162" s="10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E162" s="9" t="inlineStr">
+        <is>
+          <t>+P</t>
+        </is>
+      </c>
+      <c r="F162" s="9" t="inlineStr">
+        <is>
+          <t>Core STI</t>
+        </is>
+      </c>
+      <c r="G162" s="9" t="inlineStr">
+        <is>
+          <t>`STI-413`, `STI-415`</t>
+        </is>
+      </c>
+    </row>
+    <row r="163" ht="16" customHeight="1">
+      <c r="A163" s="8" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="B163" s="7" t="inlineStr">
+        <is>
+          <t>`STI-521`</t>
+        </is>
+      </c>
+      <c r="C163" s="7" t="inlineStr">
+        <is>
+          <t>Internet of Things (IoT)</t>
+        </is>
+      </c>
+      <c r="D163" s="8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E163" s="7" t="inlineStr">
+        <is>
+          <t>+P</t>
+        </is>
+      </c>
+      <c r="F163" s="7" t="inlineStr">
+        <is>
+          <t>Core STI</t>
+        </is>
+      </c>
+      <c r="G163" s="7" t="inlineStr">
+        <is>
+          <t>`STI-312`, `STI-310`</t>
+        </is>
+      </c>
+    </row>
+    <row r="164" ht="16" customHeight="1">
+      <c r="A164" s="10" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B164" s="9" t="inlineStr">
+        <is>
+          <t>`STI-522`</t>
+        </is>
+      </c>
+      <c r="C164" s="9" t="inlineStr">
+        <is>
+          <t>Pemrograman Aplikasi Mobile</t>
+        </is>
+      </c>
+      <c r="D164" s="10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E164" s="9" t="inlineStr">
+        <is>
+          <t>+P</t>
+        </is>
+      </c>
+      <c r="F164" s="9" t="inlineStr">
+        <is>
+          <t>Core STI</t>
+        </is>
+      </c>
+      <c r="G164" s="9" t="inlineStr">
+        <is>
+          <t>`STI-311`, `STI-416`</t>
+        </is>
+      </c>
+    </row>
+    <row r="165" ht="16" customHeight="1">
+      <c r="A165" s="8" t="inlineStr">
+        <is>
           <t>36</t>
         </is>
       </c>
-      <c r="B143" s="7" t="inlineStr">
+      <c r="B165" s="7" t="inlineStr">
         <is>
           <t>`STI-523`</t>
         </is>
       </c>
-      <c r="C143" s="7" t="inlineStr">
+      <c r="C165" s="7" t="inlineStr">
         <is>
           <t>Manajemen Proyek TI</t>
         </is>
       </c>
-      <c r="D143" s="8" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E143" s="7" t="inlineStr">
+      <c r="D165" s="8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E165" s="7" t="inlineStr">
         <is>
           <t>Teori</t>
         </is>
       </c>
-      <c r="F143" s="7" t="inlineStr">
+      <c r="F165" s="7" t="inlineStr">
         <is>
           <t>Core STI</t>
         </is>
       </c>
-      <c r="G143" s="7" t="inlineStr">
+      <c r="G165" s="7" t="inlineStr">
         <is>
           <t>`STI-306`, `STI-309`</t>
         </is>
       </c>
     </row>
-    <row r="144" ht="16" customHeight="1">
-      <c r="A144" s="10" t="inlineStr">
+    <row r="166" ht="16" customHeight="1">
+      <c r="A166" s="10" t="inlineStr">
         <is>
           <t>37</t>
         </is>
       </c>
-      <c r="B144" s="9" t="inlineStr">
+      <c r="B166" s="9" t="inlineStr">
         <is>
           <t>`MKU-507`</t>
         </is>
       </c>
-      <c r="C144" s="9" t="inlineStr">
+      <c r="C166" s="9" t="inlineStr">
         <is>
           <t>Kuliah Pengabdian Kepada Masyarakat (KPM)</t>
         </is>
       </c>
-      <c r="D144" s="10" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E144" s="9" t="inlineStr">
+      <c r="D166" s="10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E166" s="9" t="inlineStr">
         <is>
           <t>Praktik</t>
         </is>
       </c>
-      <c r="F144" s="9" t="inlineStr">
+      <c r="F166" s="9" t="inlineStr">
         <is>
           <t>MKWU</t>
         </is>
       </c>
-      <c r="G144" s="9" t="inlineStr">
+      <c r="G166" s="9" t="inlineStr">
         <is>
           <t>$\ge 80\text{ SKS}$</t>
         </is>
       </c>
     </row>
-    <row r="145" ht="16" customHeight="1">
-      <c r="A145" s="8" t="inlineStr">
+    <row r="167" ht="16" customHeight="1">
+      <c r="A167" s="8" t="inlineStr">
         <is>
           <t>38</t>
         </is>
       </c>
-      <c r="B145" s="7" t="inlineStr">
+      <c r="B167" s="7" t="inlineStr">
         <is>
           <t>`STA/B/C`</t>
         </is>
       </c>
-      <c r="C145" s="7" t="inlineStr">
+      <c r="C167" s="7" t="inlineStr">
         <is>
           <t>**MK Pilihan Peminatan 1**</t>
         </is>
       </c>
-      <c r="D145" s="8" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E145" s="7" t="inlineStr">
+      <c r="D167" s="8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E167" s="7" t="inlineStr">
         <is>
           <t>Elektif</t>
         </is>
       </c>
-      <c r="F145" s="7" t="inlineStr">
+      <c r="F167" s="7" t="inlineStr">
         <is>
           <t>Peminatan</t>
         </is>
       </c>
-      <c r="G145" s="7" t="inlineStr">
+      <c r="G167" s="7" t="inlineStr">
         <is>
           <t>Prasyarat Peminatan</t>
         </is>
       </c>
     </row>
-    <row r="146" ht="16" customHeight="1">
-      <c r="A146" s="10" t="inlineStr">
+    <row r="168" ht="16" customHeight="1">
+      <c r="A168" s="10" t="inlineStr">
         <is>
           <t>38.B</t>
         </is>
       </c>
-      <c r="B146" s="9" t="inlineStr">
+      <c r="B168" s="9" t="inlineStr">
         <is>
           <t>`MKU-508`</t>
         </is>
       </c>
-      <c r="C146" s="9" t="inlineStr">
+      <c r="C168" s="9" t="inlineStr">
         <is>
           <t>Kewirausahaan II</t>
         </is>
       </c>
-      <c r="D146" s="10" t="inlineStr">
+      <c r="D168" s="10" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E146" s="9" t="inlineStr">
+      <c r="E168" s="9" t="inlineStr">
         <is>
           <t>Teori</t>
         </is>
       </c>
-      <c r="F146" s="9" t="inlineStr">
+      <c r="F168" s="9" t="inlineStr">
         <is>
           <t>MKWU</t>
         </is>
       </c>
-      <c r="G146" s="9" t="inlineStr">
+      <c r="G168" s="9" t="inlineStr">
         <is>
           <t>— (Kebijakan UWG, Sem 5)</t>
         </is>
       </c>
     </row>
-    <row r="147" ht="16" customHeight="1">
-      <c r="A147" s="7" t="inlineStr">
+    <row r="169" ht="16" customHeight="1">
+      <c r="A169" s="7" t="inlineStr">
         <is>
           <t>**SUBTOTAL**</t>
         </is>
       </c>
-      <c r="B147" s="8" t="inlineStr">
+      <c r="B169" s="8" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C147" s="7" t="inlineStr">
+      <c r="C169" s="7" t="inlineStr">
         <is>
           <t>**Total SKS Semester 5 (7 MK + 1 MK 0 SKS)**</t>
         </is>
       </c>
-      <c r="D147" s="8" t="inlineStr">
+      <c r="D169" s="8" t="inlineStr">
         <is>
           <t>**21**</t>
         </is>
       </c>
-      <c r="E147" s="7" t="inlineStr">
+      <c r="E169" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F147" s="7" t="inlineStr">
+      <c r="F169" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G147" s="7" t="inlineStr">
+      <c r="G169" s="7" t="inlineStr">
         <is>
           <t>**Kumulatif: 101 SKS**</t>
-        </is>
-      </c>
-    </row>
-    <row r="148"/>
-    <row r="149" ht="20" customHeight="1">
-      <c r="A149" s="3" t="inlineStr">
-        <is>
-          <t>SEMESTER 6 (19 SKS) — Tahap Spesialisasi Deep Learning, Platform Engineering &amp; MBKM</t>
-        </is>
-      </c>
-      <c r="B149" s="4" t="n"/>
-      <c r="C149" s="4" t="n"/>
-      <c r="D149" s="4" t="n"/>
-      <c r="E149" s="4" t="n"/>
-      <c r="F149" s="4" t="n"/>
-      <c r="G149" s="5" t="n"/>
-    </row>
-    <row r="150" ht="26" customHeight="1">
-      <c r="A150" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="B150" s="6" t="inlineStr">
-        <is>
-          <t>Kode MK</t>
-        </is>
-      </c>
-      <c r="C150" s="6" t="inlineStr">
-        <is>
-          <t>Nama Mata Kuliah</t>
-        </is>
-      </c>
-      <c r="D150" s="6" t="inlineStr">
-        <is>
-          <t>SKS</t>
-        </is>
-      </c>
-      <c r="E150" s="6" t="inlineStr">
-        <is>
-          <t>Tipe</t>
-        </is>
-      </c>
-      <c r="F150" s="6" t="inlineStr">
-        <is>
-          <t>Kategori</t>
-        </is>
-      </c>
-      <c r="G150" s="6" t="inlineStr">
-        <is>
-          <t>Prasyarat</t>
-        </is>
-      </c>
-    </row>
-    <row r="151" ht="16" customHeight="1">
-      <c r="A151" s="8" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="B151" s="7" t="inlineStr">
-        <is>
-          <t>`STI-624`</t>
-        </is>
-      </c>
-      <c r="C151" s="7" t="inlineStr">
-        <is>
-          <t>Integrasi Layanan Cerdas Berbasis AI</t>
-        </is>
-      </c>
-      <c r="D151" s="8" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E151" s="7" t="inlineStr">
-        <is>
-          <t>+P</t>
-        </is>
-      </c>
-      <c r="F151" s="7" t="inlineStr">
-        <is>
-          <t>Core STI</t>
-        </is>
-      </c>
-      <c r="G151" s="7" t="inlineStr">
-        <is>
-          <t>`STI-413`, `STI-416`</t>
-        </is>
-      </c>
-    </row>
-    <row r="152" ht="16" customHeight="1">
-      <c r="A152" s="10" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="B152" s="9" t="inlineStr">
-        <is>
-          <t>`STI-625`</t>
-        </is>
-      </c>
-      <c r="C152" s="9" t="inlineStr">
-        <is>
-          <t>Smart City &amp; Pemerintahan Digital</t>
-        </is>
-      </c>
-      <c r="D152" s="10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E152" s="9" t="inlineStr">
-        <is>
-          <t>Teori</t>
-        </is>
-      </c>
-      <c r="F152" s="9" t="inlineStr">
-        <is>
-          <t>Core STI</t>
-        </is>
-      </c>
-      <c r="G152" s="9" t="inlineStr">
-        <is>
-          <t>`STI-521`</t>
-        </is>
-      </c>
-    </row>
-    <row r="153" ht="16" customHeight="1">
-      <c r="A153" s="8" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="B153" s="7" t="inlineStr">
-        <is>
-          <t>`STI-626`</t>
-        </is>
-      </c>
-      <c r="C153" s="7" t="inlineStr">
-        <is>
-          <t>Deep Learning &amp; Neural Networks</t>
-        </is>
-      </c>
-      <c r="D153" s="8" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E153" s="7" t="inlineStr">
-        <is>
-          <t>+P</t>
-        </is>
-      </c>
-      <c r="F153" s="7" t="inlineStr">
-        <is>
-          <t>Core STI</t>
-        </is>
-      </c>
-      <c r="G153" s="7" t="inlineStr">
-        <is>
-          <t>`STI-413`</t>
-        </is>
-      </c>
-    </row>
-    <row r="154" ht="16" customHeight="1">
-      <c r="A154" s="10" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="B154" s="9" t="inlineStr">
-        <is>
-          <t>`STI-627`</t>
-        </is>
-      </c>
-      <c r="C154" s="9" t="inlineStr">
-        <is>
-          <t>Digital Platform Engineering</t>
-        </is>
-      </c>
-      <c r="D154" s="10" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E154" s="9" t="inlineStr">
-        <is>
-          <t>+P</t>
-        </is>
-      </c>
-      <c r="F154" s="9" t="inlineStr">
-        <is>
-          <t>Core STI</t>
-        </is>
-      </c>
-      <c r="G154" s="9" t="inlineStr">
-        <is>
-          <t>`STI-416`</t>
-        </is>
-      </c>
-    </row>
-    <row r="155" ht="16" customHeight="1">
-      <c r="A155" s="8" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="B155" s="7" t="inlineStr">
-        <is>
-          <t>`FST-611`</t>
-        </is>
-      </c>
-      <c r="C155" s="7" t="inlineStr">
-        <is>
-          <t>Metodologi Penelitian</t>
-        </is>
-      </c>
-      <c r="D155" s="8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E155" s="7" t="inlineStr">
-        <is>
-          <t>Teori</t>
-        </is>
-      </c>
-      <c r="F155" s="7" t="inlineStr">
-        <is>
-          <t>FSTI</t>
-        </is>
-      </c>
-      <c r="G155" s="7" t="inlineStr">
-        <is>
-          <t>$\ge 76\text{ SKS}$</t>
-        </is>
-      </c>
-    </row>
-    <row r="156" ht="16" customHeight="1">
-      <c r="A156" s="10" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="B156" s="9" t="inlineStr">
-        <is>
-          <t>`STA/B/C`</t>
-        </is>
-      </c>
-      <c r="C156" s="9" t="inlineStr">
-        <is>
-          <t>**MK Pilihan Peminatan 2**</t>
-        </is>
-      </c>
-      <c r="D156" s="10" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E156" s="9" t="inlineStr">
-        <is>
-          <t>Elektif</t>
-        </is>
-      </c>
-      <c r="F156" s="9" t="inlineStr">
-        <is>
-          <t>Peminatan</t>
-        </is>
-      </c>
-      <c r="G156" s="9" t="inlineStr">
-        <is>
-          <t>Prasyarat Peminatan</t>
-        </is>
-      </c>
-    </row>
-    <row r="157" ht="16" customHeight="1">
-      <c r="A157" s="8" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="B157" s="7" t="inlineStr">
-        <is>
-          <t>`STA/B/C`</t>
-        </is>
-      </c>
-      <c r="C157" s="7" t="inlineStr">
-        <is>
-          <t>**MK Pilihan Peminatan 3**</t>
-        </is>
-      </c>
-      <c r="D157" s="8" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E157" s="7" t="inlineStr">
-        <is>
-          <t>Elektif</t>
-        </is>
-      </c>
-      <c r="F157" s="7" t="inlineStr">
-        <is>
-          <t>Peminatan</t>
-        </is>
-      </c>
-      <c r="G157" s="7" t="inlineStr">
-        <is>
-          <t>Prasyarat Peminatan</t>
-        </is>
-      </c>
-    </row>
-    <row r="158" ht="16" customHeight="1">
-      <c r="A158" s="9" t="inlineStr">
-        <is>
-          <t>**SUBTOTAL**</t>
-        </is>
-      </c>
-      <c r="B158" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C158" s="9" t="inlineStr">
-        <is>
-          <t>**Total SKS Semester 6 (7 MK)**</t>
-        </is>
-      </c>
-      <c r="D158" s="10" t="inlineStr">
-        <is>
-          <t>**19**</t>
-        </is>
-      </c>
-      <c r="E158" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F158" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G158" s="9" t="inlineStr">
-        <is>
-          <t>**Kumulatif: 120 SKS**</t>
-        </is>
-      </c>
-    </row>
-    <row r="159"/>
-    <row r="160" ht="20" customHeight="1">
-      <c r="A160" s="3" t="inlineStr">
-        <is>
-          <t>SEMESTER 7 (20 SKS) — Tahap Integrasi Capstone, PKL &amp; Pra-Skripsi</t>
-        </is>
-      </c>
-      <c r="B160" s="4" t="n"/>
-      <c r="C160" s="4" t="n"/>
-      <c r="D160" s="4" t="n"/>
-      <c r="E160" s="4" t="n"/>
-      <c r="F160" s="4" t="n"/>
-      <c r="G160" s="5" t="n"/>
-    </row>
-    <row r="161" ht="26" customHeight="1">
-      <c r="A161" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="B161" s="6" t="inlineStr">
-        <is>
-          <t>Kode MK</t>
-        </is>
-      </c>
-      <c r="C161" s="6" t="inlineStr">
-        <is>
-          <t>Nama Mata Kuliah</t>
-        </is>
-      </c>
-      <c r="D161" s="6" t="inlineStr">
-        <is>
-          <t>SKS</t>
-        </is>
-      </c>
-      <c r="E161" s="6" t="inlineStr">
-        <is>
-          <t>Tipe</t>
-        </is>
-      </c>
-      <c r="F161" s="6" t="inlineStr">
-        <is>
-          <t>Kategori</t>
-        </is>
-      </c>
-      <c r="G161" s="6" t="inlineStr">
-        <is>
-          <t>Prasyarat</t>
-        </is>
-      </c>
-    </row>
-    <row r="162" ht="16" customHeight="1">
-      <c r="A162" s="8" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="B162" s="7" t="inlineStr">
-        <is>
-          <t>`STI-728`</t>
-        </is>
-      </c>
-      <c r="C162" s="7" t="inlineStr">
-        <is>
-          <t>Inovasi Teknologi dan Startup Digital</t>
-        </is>
-      </c>
-      <c r="D162" s="8" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E162" s="7" t="inlineStr">
-        <is>
-          <t>+P</t>
-        </is>
-      </c>
-      <c r="F162" s="7" t="inlineStr">
-        <is>
-          <t>Core STI</t>
-        </is>
-      </c>
-      <c r="G162" s="7" t="inlineStr">
-        <is>
-          <t>`STI-627`, `MKU-204`</t>
-        </is>
-      </c>
-    </row>
-    <row r="163" ht="16" customHeight="1">
-      <c r="A163" s="10" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="B163" s="9" t="inlineStr">
-        <is>
-          <t>`FST-610`</t>
-        </is>
-      </c>
-      <c r="C163" s="9" t="inlineStr">
-        <is>
-          <t>Capstone Project FSTI</t>
-        </is>
-      </c>
-      <c r="D163" s="10" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E163" s="9" t="inlineStr">
-        <is>
-          <t>Proyek</t>
-        </is>
-      </c>
-      <c r="F163" s="9" t="inlineStr">
-        <is>
-          <t>FSTI</t>
-        </is>
-      </c>
-      <c r="G163" s="9" t="inlineStr">
-        <is>
-          <t>`STI-523`, $\ge 100\text{ SKS}$</t>
-        </is>
-      </c>
-    </row>
-    <row r="164" ht="16" customHeight="1">
-      <c r="A164" s="8" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="B164" s="7" t="inlineStr">
-        <is>
-          <t>`FST-612`</t>
-        </is>
-      </c>
-      <c r="C164" s="7" t="inlineStr">
-        <is>
-          <t>Praktik Kerja Lapangan (PKL)</t>
-        </is>
-      </c>
-      <c r="D164" s="8" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E164" s="7" t="inlineStr">
-        <is>
-          <t>Magang</t>
-        </is>
-      </c>
-      <c r="F164" s="7" t="inlineStr">
-        <is>
-          <t>FSTI</t>
-        </is>
-      </c>
-      <c r="G164" s="7" t="inlineStr">
-        <is>
-          <t>$\ge 100\text{ SKS}$</t>
-        </is>
-      </c>
-    </row>
-    <row r="165" ht="16" customHeight="1">
-      <c r="A165" s="10" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="B165" s="9" t="inlineStr">
-        <is>
-          <t>`FST-613`</t>
-        </is>
-      </c>
-      <c r="C165" s="9" t="inlineStr">
-        <is>
-          <t>Pra-Skripsi / Seminar Proposal</t>
-        </is>
-      </c>
-      <c r="D165" s="10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E165" s="9" t="inlineStr">
-        <is>
-          <t>Seminar</t>
-        </is>
-      </c>
-      <c r="F165" s="9" t="inlineStr">
-        <is>
-          <t>FSTI</t>
-        </is>
-      </c>
-      <c r="G165" s="9" t="inlineStr">
-        <is>
-          <t>`FST-611`, $\ge 100\text{ SKS}$</t>
-        </is>
-      </c>
-    </row>
-    <row r="166" ht="16" customHeight="1">
-      <c r="A166" s="8" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="B166" s="7" t="inlineStr">
-        <is>
-          <t>`STA/B/C`</t>
-        </is>
-      </c>
-      <c r="C166" s="7" t="inlineStr">
-        <is>
-          <t>**MK Pilihan Peminatan 4**</t>
-        </is>
-      </c>
-      <c r="D166" s="8" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E166" s="7" t="inlineStr">
-        <is>
-          <t>Elektif</t>
-        </is>
-      </c>
-      <c r="F166" s="7" t="inlineStr">
-        <is>
-          <t>Peminatan</t>
-        </is>
-      </c>
-      <c r="G166" s="7" t="inlineStr">
-        <is>
-          <t>Prasyarat Peminatan</t>
-        </is>
-      </c>
-    </row>
-    <row r="167" ht="16" customHeight="1">
-      <c r="A167" s="10" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="B167" s="9" t="inlineStr">
-        <is>
-          <t>`STA/B/C`</t>
-        </is>
-      </c>
-      <c r="C167" s="9" t="inlineStr">
-        <is>
-          <t>**MK Pilihan Peminatan 5**</t>
-        </is>
-      </c>
-      <c r="D167" s="10" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E167" s="9" t="inlineStr">
-        <is>
-          <t>Elektif</t>
-        </is>
-      </c>
-      <c r="F167" s="9" t="inlineStr">
-        <is>
-          <t>Peminatan</t>
-        </is>
-      </c>
-      <c r="G167" s="9" t="inlineStr">
-        <is>
-          <t>Prasyarat Peminatan</t>
-        </is>
-      </c>
-    </row>
-    <row r="168" ht="16" customHeight="1">
-      <c r="A168" s="8" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="B168" s="7" t="inlineStr">
-        <is>
-          <t>`STA/B/C`</t>
-        </is>
-      </c>
-      <c r="C168" s="7" t="inlineStr">
-        <is>
-          <t>**MK Pilihan Peminatan 6**</t>
-        </is>
-      </c>
-      <c r="D168" s="8" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E168" s="7" t="inlineStr">
-        <is>
-          <t>Elektif</t>
-        </is>
-      </c>
-      <c r="F168" s="7" t="inlineStr">
-        <is>
-          <t>Peminatan</t>
-        </is>
-      </c>
-      <c r="G168" s="7" t="inlineStr">
-        <is>
-          <t>Prasyarat Peminatan</t>
-        </is>
-      </c>
-    </row>
-    <row r="169" ht="16" customHeight="1">
-      <c r="A169" s="9" t="inlineStr">
-        <is>
-          <t>**SUBTOTAL**</t>
-        </is>
-      </c>
-      <c r="B169" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C169" s="9" t="inlineStr">
-        <is>
-          <t>**Total SKS Semester 7 (7 MK)**</t>
-        </is>
-      </c>
-      <c r="D169" s="10" t="inlineStr">
-        <is>
-          <t>**20**</t>
-        </is>
-      </c>
-      <c r="E169" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F169" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G169" s="9" t="inlineStr">
-        <is>
-          <t>**Kumulatif: 140 SKS**</t>
         </is>
       </c>
     </row>
@@ -5840,7 +6001,7 @@
     <row r="171" ht="20" customHeight="1">
       <c r="A171" s="3" t="inlineStr">
         <is>
-          <t>SEMESTER 8 (6 SKS) — Tahap Penyelesaian Skripsi / Non-Skripsi</t>
+          <t>SEMESTER 6 (19 SKS) — Tahap Spesialisasi Deep Learning, Platform Engineering &amp; MBKM</t>
         </is>
       </c>
       <c r="B171" s="4" t="n"/>
@@ -5890,511 +6051,2136 @@
     <row r="173" ht="16" customHeight="1">
       <c r="A173" s="8" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B173" s="7" t="inlineStr">
         <is>
-          <t>`FST-714`</t>
+          <t>`STI-624`</t>
         </is>
       </c>
       <c r="C173" s="7" t="inlineStr">
         <is>
-          <t>Skripsi / Tugas Akhir</t>
+          <t>Integrasi Layanan Cerdas Berbasis AI</t>
         </is>
       </c>
       <c r="D173" s="8" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E173" s="7" t="inlineStr">
         <is>
-          <t>Mandiri</t>
+          <t>+P</t>
         </is>
       </c>
       <c r="F173" s="7" t="inlineStr">
         <is>
+          <t>Core STI</t>
+        </is>
+      </c>
+      <c r="G173" s="7" t="inlineStr">
+        <is>
+          <t>`STI-413`, `STI-416`</t>
+        </is>
+      </c>
+    </row>
+    <row r="174" ht="16" customHeight="1">
+      <c r="A174" s="10" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B174" s="9" t="inlineStr">
+        <is>
+          <t>`STI-625`</t>
+        </is>
+      </c>
+      <c r="C174" s="9" t="inlineStr">
+        <is>
+          <t>Smart City &amp; Pemerintahan Digital</t>
+        </is>
+      </c>
+      <c r="D174" s="10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E174" s="9" t="inlineStr">
+        <is>
+          <t>Teori</t>
+        </is>
+      </c>
+      <c r="F174" s="9" t="inlineStr">
+        <is>
+          <t>Core STI</t>
+        </is>
+      </c>
+      <c r="G174" s="9" t="inlineStr">
+        <is>
+          <t>`STI-521`</t>
+        </is>
+      </c>
+    </row>
+    <row r="175" ht="16" customHeight="1">
+      <c r="A175" s="8" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="B175" s="7" t="inlineStr">
+        <is>
+          <t>`STI-626`</t>
+        </is>
+      </c>
+      <c r="C175" s="7" t="inlineStr">
+        <is>
+          <t>Deep Learning &amp; Neural Networks</t>
+        </is>
+      </c>
+      <c r="D175" s="8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E175" s="7" t="inlineStr">
+        <is>
+          <t>+P</t>
+        </is>
+      </c>
+      <c r="F175" s="7" t="inlineStr">
+        <is>
+          <t>Core STI</t>
+        </is>
+      </c>
+      <c r="G175" s="7" t="inlineStr">
+        <is>
+          <t>`STI-413`</t>
+        </is>
+      </c>
+    </row>
+    <row r="176" ht="16" customHeight="1">
+      <c r="A176" s="10" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B176" s="9" t="inlineStr">
+        <is>
+          <t>`STI-627`</t>
+        </is>
+      </c>
+      <c r="C176" s="9" t="inlineStr">
+        <is>
+          <t>Digital Platform Engineering</t>
+        </is>
+      </c>
+      <c r="D176" s="10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E176" s="9" t="inlineStr">
+        <is>
+          <t>+P</t>
+        </is>
+      </c>
+      <c r="F176" s="9" t="inlineStr">
+        <is>
+          <t>Core STI</t>
+        </is>
+      </c>
+      <c r="G176" s="9" t="inlineStr">
+        <is>
+          <t>`STI-416`</t>
+        </is>
+      </c>
+    </row>
+    <row r="177" ht="16" customHeight="1">
+      <c r="A177" s="8" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="B177" s="7" t="inlineStr">
+        <is>
+          <t>`FST-611`</t>
+        </is>
+      </c>
+      <c r="C177" s="7" t="inlineStr">
+        <is>
+          <t>Metodologi Penelitian</t>
+        </is>
+      </c>
+      <c r="D177" s="8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E177" s="7" t="inlineStr">
+        <is>
+          <t>Teori</t>
+        </is>
+      </c>
+      <c r="F177" s="7" t="inlineStr">
+        <is>
           <t>FSTI</t>
         </is>
       </c>
-      <c r="G173" s="7" t="inlineStr">
-        <is>
-          <t>`FST-613`, $\ge 120\text{ SKS}$</t>
-        </is>
-      </c>
-    </row>
-    <row r="174" ht="16" customHeight="1">
-      <c r="A174" s="9" t="inlineStr">
+      <c r="G177" s="7" t="inlineStr">
+        <is>
+          <t>$\ge 76\text{ SKS}$</t>
+        </is>
+      </c>
+    </row>
+    <row r="178" ht="16" customHeight="1">
+      <c r="A178" s="10" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="B178" s="9" t="inlineStr">
+        <is>
+          <t>`STA/B/C`</t>
+        </is>
+      </c>
+      <c r="C178" s="9" t="inlineStr">
+        <is>
+          <t>**MK Pilihan Peminatan 2**</t>
+        </is>
+      </c>
+      <c r="D178" s="10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E178" s="9" t="inlineStr">
+        <is>
+          <t>Elektif</t>
+        </is>
+      </c>
+      <c r="F178" s="9" t="inlineStr">
+        <is>
+          <t>Peminatan</t>
+        </is>
+      </c>
+      <c r="G178" s="9" t="inlineStr">
+        <is>
+          <t>Prasyarat Peminatan</t>
+        </is>
+      </c>
+    </row>
+    <row r="179" ht="16" customHeight="1">
+      <c r="A179" s="8" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="B179" s="7" t="inlineStr">
+        <is>
+          <t>`STA/B/C`</t>
+        </is>
+      </c>
+      <c r="C179" s="7" t="inlineStr">
+        <is>
+          <t>**MK Pilihan Peminatan 3**</t>
+        </is>
+      </c>
+      <c r="D179" s="8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E179" s="7" t="inlineStr">
+        <is>
+          <t>Elektif</t>
+        </is>
+      </c>
+      <c r="F179" s="7" t="inlineStr">
+        <is>
+          <t>Peminatan</t>
+        </is>
+      </c>
+      <c r="G179" s="7" t="inlineStr">
+        <is>
+          <t>Prasyarat Peminatan</t>
+        </is>
+      </c>
+    </row>
+    <row r="180" ht="16" customHeight="1">
+      <c r="A180" s="9" t="inlineStr">
         <is>
           <t>**SUBTOTAL**</t>
         </is>
       </c>
-      <c r="B174" s="10" t="inlineStr">
+      <c r="B180" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C174" s="9" t="inlineStr">
-        <is>
-          <t>**Total SKS Semester 8 (1 MK)**</t>
-        </is>
-      </c>
-      <c r="D174" s="10" t="inlineStr">
-        <is>
-          <t>**6**</t>
-        </is>
-      </c>
-      <c r="E174" s="9" t="inlineStr">
+      <c r="C180" s="9" t="inlineStr">
+        <is>
+          <t>**Total SKS Semester 6 (7 MK)**</t>
+        </is>
+      </c>
+      <c r="D180" s="10" t="inlineStr">
+        <is>
+          <t>**19**</t>
+        </is>
+      </c>
+      <c r="E180" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F174" s="9" t="inlineStr">
+      <c r="F180" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G174" s="9" t="inlineStr">
-        <is>
-          <t>**Kumulatif: 146 SKS**</t>
-        </is>
-      </c>
-    </row>
-    <row r="175"/>
-    <row r="176" ht="20" customHeight="1">
-      <c r="A176" s="3" t="inlineStr">
-        <is>
-          <t>3.1 REKAPITULASI &amp; MATRIKS KALKULASI SKS AKUMULATIF SEMESTER 1 – 8</t>
-        </is>
-      </c>
-      <c r="B176" s="4" t="n"/>
-      <c r="C176" s="4" t="n"/>
-      <c r="D176" s="4" t="n"/>
-      <c r="E176" s="4" t="n"/>
-      <c r="F176" s="5" t="n"/>
-    </row>
-    <row r="177" ht="26" customHeight="1">
-      <c r="A177" s="6" t="inlineStr">
-        <is>
-          <t>Semester</t>
-        </is>
-      </c>
-      <c r="B177" s="6" t="inlineStr">
-        <is>
-          <t>Jumlah MK</t>
-        </is>
-      </c>
-      <c r="C177" s="6" t="inlineStr">
-        <is>
-          <t>Beban SKS</t>
-        </is>
-      </c>
-      <c r="D177" s="6" t="inlineStr">
-        <is>
-          <t>SKS Kumulatif</t>
-        </is>
-      </c>
-      <c r="E177" s="6" t="inlineStr">
-        <is>
-          <t>Persentase</t>
-        </is>
-      </c>
-      <c r="F177" s="6" t="inlineStr">
-        <is>
-          <t>Tahapan Akademik &amp; Karakteristik</t>
-        </is>
-      </c>
-    </row>
-    <row r="178" ht="16" customHeight="1">
-      <c r="A178" s="7" t="inlineStr">
-        <is>
-          <t>**Sem 1**</t>
-        </is>
-      </c>
-      <c r="B178" s="8" t="inlineStr">
-        <is>
-          <t>8 MK</t>
-        </is>
-      </c>
-      <c r="C178" s="8" t="inlineStr">
-        <is>
-          <t>19 SKS</t>
-        </is>
-      </c>
-      <c r="D178" s="8" t="inlineStr">
-        <is>
-          <t>19 SKS</t>
-        </is>
-      </c>
-      <c r="E178" s="7" t="inlineStr">
-        <is>
-          <t>13,0%</t>
-        </is>
-      </c>
-      <c r="F178" s="7" t="inlineStr">
-        <is>
-          <t>Tahap Fondasi Sains, Algoritma &amp; Logika</t>
-        </is>
-      </c>
-    </row>
-    <row r="179" ht="16" customHeight="1">
-      <c r="A179" s="9" t="inlineStr">
-        <is>
-          <t>**Sem 2**</t>
-        </is>
-      </c>
-      <c r="B179" s="10" t="inlineStr">
-        <is>
-          <t>8 MK</t>
-        </is>
-      </c>
-      <c r="C179" s="10" t="inlineStr">
-        <is>
-          <t>20 SKS</t>
-        </is>
-      </c>
-      <c r="D179" s="10" t="inlineStr">
-        <is>
-          <t>39 SKS</t>
-        </is>
-      </c>
-      <c r="E179" s="9" t="inlineStr">
-        <is>
-          <t>13,7%</t>
-        </is>
-      </c>
-      <c r="F179" s="9" t="inlineStr">
-        <is>
-          <t>Tahap Fondasi Data, Matdis &amp; OOP</t>
-        </is>
-      </c>
-    </row>
-    <row r="180" ht="16" customHeight="1">
-      <c r="A180" s="7" t="inlineStr">
-        <is>
-          <t>**Sem 3**</t>
-        </is>
-      </c>
-      <c r="B180" s="8" t="inlineStr">
-        <is>
-          <t>7 MK</t>
-        </is>
-      </c>
-      <c r="C180" s="8" t="inlineStr">
-        <is>
-          <t>20 SKS</t>
-        </is>
-      </c>
-      <c r="D180" s="8" t="inlineStr">
-        <is>
-          <t>59 SKS</t>
-        </is>
-      </c>
-      <c r="E180" s="7" t="inlineStr">
-        <is>
-          <t>13,7%</t>
-        </is>
-      </c>
-      <c r="F180" s="7" t="inlineStr">
-        <is>
-          <t>Tahap Penguatan Core RPL, OS &amp; Jaringan</t>
-        </is>
-      </c>
-    </row>
-    <row r="181" ht="16" customHeight="1">
-      <c r="A181" s="9" t="inlineStr">
-        <is>
-          <t>**Sem 4**</t>
-        </is>
-      </c>
-      <c r="B181" s="10" t="inlineStr">
-        <is>
-          <t>8 MK</t>
-        </is>
-      </c>
-      <c r="C181" s="10" t="inlineStr">
-        <is>
-          <t>21 SKS</t>
-        </is>
-      </c>
-      <c r="D181" s="10" t="inlineStr">
-        <is>
-          <t>80 SKS</t>
-        </is>
-      </c>
-      <c r="E181" s="9" t="inlineStr">
-        <is>
-          <t>14,4%</t>
-        </is>
-      </c>
-      <c r="F181" s="9" t="inlineStr">
-        <is>
-          <t>Tahap Penguatan Core AI/ML, NLP &amp; Cloud</t>
-        </is>
-      </c>
-    </row>
-    <row r="182" ht="16" customHeight="1">
-      <c r="A182" s="7" t="inlineStr">
-        <is>
-          <t>**Sem 5**</t>
-        </is>
-      </c>
-      <c r="B182" s="8" t="inlineStr">
-        <is>
-          <t>7 MK</t>
-        </is>
-      </c>
-      <c r="C182" s="8" t="inlineStr">
-        <is>
-          <t>21 SKS</t>
-        </is>
-      </c>
-      <c r="D182" s="8" t="inlineStr">
-        <is>
-          <t>101 SKS</t>
-        </is>
-      </c>
-      <c r="E182" s="7" t="inlineStr">
-        <is>
-          <t>14,4%</t>
-        </is>
-      </c>
-      <c r="F182" s="7" t="inlineStr">
-        <is>
-          <t>Tahap Spesialisasi Keamanan Lanjut &amp; IoT</t>
-        </is>
-      </c>
-    </row>
-    <row r="183" ht="16" customHeight="1">
-      <c r="A183" s="9" t="inlineStr">
-        <is>
-          <t>**Sem 6**</t>
-        </is>
-      </c>
-      <c r="B183" s="10" t="inlineStr">
-        <is>
-          <t>7 MK</t>
-        </is>
-      </c>
-      <c r="C183" s="10" t="inlineStr">
-        <is>
-          <t>19 SKS</t>
-        </is>
-      </c>
-      <c r="D183" s="10" t="inlineStr">
-        <is>
-          <t>120 SKS</t>
-        </is>
-      </c>
-      <c r="E183" s="9" t="inlineStr">
-        <is>
-          <t>13,0%</t>
-        </is>
-      </c>
-      <c r="F183" s="9" t="inlineStr">
-        <is>
-          <t>Tahap Spesialisasi Deep Learning &amp; Platform Eng</t>
+      <c r="G180" s="9" t="inlineStr">
+        <is>
+          <t>**Kumulatif: 120 SKS**</t>
+        </is>
+      </c>
+    </row>
+    <row r="181"/>
+    <row r="182" ht="20" customHeight="1">
+      <c r="A182" s="3" t="inlineStr">
+        <is>
+          <t>SEMESTER 7 (20 SKS) — Tahap Integrasi Capstone, PKL &amp; Pra-Skripsi</t>
+        </is>
+      </c>
+      <c r="B182" s="4" t="n"/>
+      <c r="C182" s="4" t="n"/>
+      <c r="D182" s="4" t="n"/>
+      <c r="E182" s="4" t="n"/>
+      <c r="F182" s="4" t="n"/>
+      <c r="G182" s="5" t="n"/>
+    </row>
+    <row r="183" ht="26" customHeight="1">
+      <c r="A183" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B183" s="6" t="inlineStr">
+        <is>
+          <t>Kode MK</t>
+        </is>
+      </c>
+      <c r="C183" s="6" t="inlineStr">
+        <is>
+          <t>Nama Mata Kuliah</t>
+        </is>
+      </c>
+      <c r="D183" s="6" t="inlineStr">
+        <is>
+          <t>SKS</t>
+        </is>
+      </c>
+      <c r="E183" s="6" t="inlineStr">
+        <is>
+          <t>Tipe</t>
+        </is>
+      </c>
+      <c r="F183" s="6" t="inlineStr">
+        <is>
+          <t>Kategori</t>
+        </is>
+      </c>
+      <c r="G183" s="6" t="inlineStr">
+        <is>
+          <t>Prasyarat</t>
         </is>
       </c>
     </row>
     <row r="184" ht="16" customHeight="1">
-      <c r="A184" s="7" t="inlineStr">
-        <is>
-          <t>**Sem 7**</t>
-        </is>
-      </c>
-      <c r="B184" s="8" t="inlineStr">
-        <is>
-          <t>7 MK</t>
-        </is>
-      </c>
-      <c r="C184" s="8" t="inlineStr">
-        <is>
-          <t>20 SKS</t>
+      <c r="A184" s="8" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="B184" s="7" t="inlineStr">
+        <is>
+          <t>`STI-728`</t>
+        </is>
+      </c>
+      <c r="C184" s="7" t="inlineStr">
+        <is>
+          <t>Inovasi Teknologi dan Startup Digital</t>
         </is>
       </c>
       <c r="D184" s="8" t="inlineStr">
         <is>
-          <t>140 SKS</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E184" s="7" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>+P</t>
         </is>
       </c>
       <c r="F184" s="7" t="inlineStr">
         <is>
-          <t>Tahap Integrasi Capstone, PKL &amp; Sempro</t>
+          <t>Core STI</t>
+        </is>
+      </c>
+      <c r="G184" s="7" t="inlineStr">
+        <is>
+          <t>`STI-627`, `MKU-204`</t>
         </is>
       </c>
     </row>
     <row r="185" ht="16" customHeight="1">
-      <c r="A185" s="9" t="inlineStr">
-        <is>
-          <t>**Sem 8**</t>
-        </is>
-      </c>
-      <c r="B185" s="10" t="inlineStr">
-        <is>
-          <t>1 MK</t>
-        </is>
-      </c>
-      <c r="C185" s="10" t="inlineStr">
-        <is>
-          <t>6 SKS</t>
+      <c r="A185" s="10" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="B185" s="9" t="inlineStr">
+        <is>
+          <t>`FST-610`</t>
+        </is>
+      </c>
+      <c r="C185" s="9" t="inlineStr">
+        <is>
+          <t>Capstone Project FSTI</t>
         </is>
       </c>
       <c r="D185" s="10" t="inlineStr">
         <is>
-          <t>146 SKS</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E185" s="9" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>Proyek</t>
         </is>
       </c>
       <c r="F185" s="9" t="inlineStr">
         <is>
-          <t>Tahap Penyelesaian Skripsi / Non-Skripsi</t>
+          <t>FSTI</t>
+        </is>
+      </c>
+      <c r="G185" s="9" t="inlineStr">
+        <is>
+          <t>`STI-523`, $\ge 100\text{ SKS}$</t>
         </is>
       </c>
     </row>
     <row r="186" ht="16" customHeight="1">
-      <c r="A186" s="7" t="inlineStr">
-        <is>
-          <t>**TOTAL**</t>
+      <c r="A186" s="8" t="inlineStr">
+        <is>
+          <t>48</t>
         </is>
       </c>
       <c r="B186" s="7" t="inlineStr">
         <is>
-          <t>**55 MK**</t>
+          <t>`FST-612`</t>
         </is>
       </c>
       <c r="C186" s="7" t="inlineStr">
         <is>
-          <t>**146 SKS**</t>
-        </is>
-      </c>
-      <c r="D186" s="7" t="inlineStr">
-        <is>
-          <t>**146 SKS**</t>
+          <t>Praktik Kerja Lapangan (PKL)</t>
+        </is>
+      </c>
+      <c r="D186" s="8" t="inlineStr">
+        <is>
+          <t>3</t>
         </is>
       </c>
       <c r="E186" s="7" t="inlineStr">
         <is>
-          <t>**100,0%**</t>
+          <t>Magang</t>
         </is>
       </c>
       <c r="F186" s="7" t="inlineStr">
         <is>
-          <t>**Paket Lulus Tepat Waktu (4 Tahun)**</t>
-        </is>
-      </c>
-    </row>
-    <row r="187"/>
-    <row r="188" ht="20" customHeight="1">
-      <c r="A188" s="3" t="inlineStr">
-        <is>
-          <t>3 PEMINATAN SPESIALISASI KEAHLIAN SISTEKIN</t>
-        </is>
-      </c>
-      <c r="B188" s="4" t="n"/>
-      <c r="C188" s="4" t="n"/>
-      <c r="D188" s="4" t="n"/>
-      <c r="E188" s="4" t="n"/>
-      <c r="F188" s="5" t="n"/>
-    </row>
-    <row r="189" ht="26" customHeight="1">
-      <c r="A189" s="6" t="inlineStr">
+          <t>FSTI</t>
+        </is>
+      </c>
+      <c r="G186" s="7" t="inlineStr">
+        <is>
+          <t>$\ge 100\text{ SKS}$</t>
+        </is>
+      </c>
+    </row>
+    <row r="187" ht="16" customHeight="1">
+      <c r="A187" s="10" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="B187" s="9" t="inlineStr">
+        <is>
+          <t>`FST-613`</t>
+        </is>
+      </c>
+      <c r="C187" s="9" t="inlineStr">
+        <is>
+          <t>Pra-Skripsi / Seminar Proposal</t>
+        </is>
+      </c>
+      <c r="D187" s="10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E187" s="9" t="inlineStr">
+        <is>
+          <t>Seminar</t>
+        </is>
+      </c>
+      <c r="F187" s="9" t="inlineStr">
+        <is>
+          <t>FSTI</t>
+        </is>
+      </c>
+      <c r="G187" s="9" t="inlineStr">
+        <is>
+          <t>`FST-611`, $\ge 100\text{ SKS}$</t>
+        </is>
+      </c>
+    </row>
+    <row r="188" ht="16" customHeight="1">
+      <c r="A188" s="8" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="B188" s="7" t="inlineStr">
+        <is>
+          <t>`STA/B/C`</t>
+        </is>
+      </c>
+      <c r="C188" s="7" t="inlineStr">
+        <is>
+          <t>**MK Pilihan Peminatan 4**</t>
+        </is>
+      </c>
+      <c r="D188" s="8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E188" s="7" t="inlineStr">
+        <is>
+          <t>Elektif</t>
+        </is>
+      </c>
+      <c r="F188" s="7" t="inlineStr">
         <is>
           <t>Peminatan</t>
         </is>
       </c>
-      <c r="B189" s="6" t="inlineStr">
-        <is>
-          <t>Basis Profil (PL)</t>
-        </is>
-      </c>
-      <c r="C189" s="6" t="inlineStr">
-        <is>
-          <t>Mata Kuliah Pilihan (@ 3 SKS)</t>
+      <c r="G188" s="7" t="inlineStr">
+        <is>
+          <t>Prasyarat Peminatan</t>
+        </is>
+      </c>
+    </row>
+    <row r="189" ht="16" customHeight="1">
+      <c r="A189" s="10" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="B189" s="9" t="inlineStr">
+        <is>
+          <t>`STA/B/C`</t>
+        </is>
+      </c>
+      <c r="C189" s="9" t="inlineStr">
+        <is>
+          <t>**MK Pilihan Peminatan 5**</t>
+        </is>
+      </c>
+      <c r="D189" s="10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E189" s="9" t="inlineStr">
+        <is>
+          <t>Elektif</t>
+        </is>
+      </c>
+      <c r="F189" s="9" t="inlineStr">
+        <is>
+          <t>Peminatan</t>
+        </is>
+      </c>
+      <c r="G189" s="9" t="inlineStr">
+        <is>
+          <t>Prasyarat Peminatan</t>
         </is>
       </c>
     </row>
     <row r="190" ht="16" customHeight="1">
-      <c r="A190" s="7" t="inlineStr">
-        <is>
-          <t>**P1: Integrated Smart Systems** *(Flagship)*</t>
+      <c r="A190" s="8" t="inlineStr">
+        <is>
+          <t>52</t>
         </is>
       </c>
       <c r="B190" s="7" t="inlineStr">
         <is>
-          <t>**PL-1:** Intelligent IS &amp; Data/AI Engineer</t>
+          <t>`STA/B/C`</t>
         </is>
       </c>
       <c r="C190" s="7" t="inlineStr">
         <is>
-          <t>1. `STA-01` Decision Support Systems (+P, Sem 5)&lt;br&gt;2. `STA-02` Computational Methods &amp; Numerics (+P, Sem 6)&lt;br&gt;3. `STA-03` Intelligent Agent Systems (+P, Sem 6)&lt;br&gt;4. `STA-04` MLOps and AI Pipeline (+P, Sem 7)&lt;br&gt;5. `STA-05` Conversational AI &amp; Assistant (+P, Sem 7)&lt;br&gt;6. `STA-06` Smart Surveillance &amp; IoT Analytics (+P, Sem 7)</t>
+          <t>**MK Pilihan Peminatan 6**</t>
+        </is>
+      </c>
+      <c r="D190" s="8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E190" s="7" t="inlineStr">
+        <is>
+          <t>Elektif</t>
+        </is>
+      </c>
+      <c r="F190" s="7" t="inlineStr">
+        <is>
+          <t>Peminatan</t>
+        </is>
+      </c>
+      <c r="G190" s="7" t="inlineStr">
+        <is>
+          <t>Prasyarat Peminatan</t>
         </is>
       </c>
     </row>
     <row r="191" ht="16" customHeight="1">
       <c r="A191" s="9" t="inlineStr">
         <is>
+          <t>**SUBTOTAL**</t>
+        </is>
+      </c>
+      <c r="B191" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C191" s="9" t="inlineStr">
+        <is>
+          <t>**Total SKS Semester 7 (7 MK)**</t>
+        </is>
+      </c>
+      <c r="D191" s="10" t="inlineStr">
+        <is>
+          <t>**20**</t>
+        </is>
+      </c>
+      <c r="E191" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F191" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G191" s="9" t="inlineStr">
+        <is>
+          <t>**Kumulatif: 140 SKS**</t>
+        </is>
+      </c>
+    </row>
+    <row r="192"/>
+    <row r="193" ht="20" customHeight="1">
+      <c r="A193" s="3" t="inlineStr">
+        <is>
+          <t>SEMESTER 8 (6 SKS) — Tahap Penyelesaian Skripsi / Non-Skripsi</t>
+        </is>
+      </c>
+      <c r="B193" s="4" t="n"/>
+      <c r="C193" s="4" t="n"/>
+      <c r="D193" s="4" t="n"/>
+      <c r="E193" s="4" t="n"/>
+      <c r="F193" s="4" t="n"/>
+      <c r="G193" s="5" t="n"/>
+    </row>
+    <row r="194" ht="26" customHeight="1">
+      <c r="A194" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B194" s="6" t="inlineStr">
+        <is>
+          <t>Kode MK</t>
+        </is>
+      </c>
+      <c r="C194" s="6" t="inlineStr">
+        <is>
+          <t>Nama Mata Kuliah</t>
+        </is>
+      </c>
+      <c r="D194" s="6" t="inlineStr">
+        <is>
+          <t>SKS</t>
+        </is>
+      </c>
+      <c r="E194" s="6" t="inlineStr">
+        <is>
+          <t>Tipe</t>
+        </is>
+      </c>
+      <c r="F194" s="6" t="inlineStr">
+        <is>
+          <t>Kategori</t>
+        </is>
+      </c>
+      <c r="G194" s="6" t="inlineStr">
+        <is>
+          <t>Prasyarat</t>
+        </is>
+      </c>
+    </row>
+    <row r="195" ht="16" customHeight="1">
+      <c r="A195" s="8" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="B195" s="7" t="inlineStr">
+        <is>
+          <t>`FST-714`</t>
+        </is>
+      </c>
+      <c r="C195" s="7" t="inlineStr">
+        <is>
+          <t>Skripsi / Tugas Akhir</t>
+        </is>
+      </c>
+      <c r="D195" s="8" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E195" s="7" t="inlineStr">
+        <is>
+          <t>Mandiri</t>
+        </is>
+      </c>
+      <c r="F195" s="7" t="inlineStr">
+        <is>
+          <t>FSTI</t>
+        </is>
+      </c>
+      <c r="G195" s="7" t="inlineStr">
+        <is>
+          <t>`FST-613`, $\ge 120\text{ SKS}$</t>
+        </is>
+      </c>
+    </row>
+    <row r="196" ht="16" customHeight="1">
+      <c r="A196" s="9" t="inlineStr">
+        <is>
+          <t>**SUBTOTAL**</t>
+        </is>
+      </c>
+      <c r="B196" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C196" s="9" t="inlineStr">
+        <is>
+          <t>**Total SKS Semester 8 (1 MK)**</t>
+        </is>
+      </c>
+      <c r="D196" s="10" t="inlineStr">
+        <is>
+          <t>**6**</t>
+        </is>
+      </c>
+      <c r="E196" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F196" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G196" s="9" t="inlineStr">
+        <is>
+          <t>**Kumulatif: 146 SKS**</t>
+        </is>
+      </c>
+    </row>
+    <row r="197"/>
+    <row r="198" ht="20" customHeight="1">
+      <c r="A198" s="3" t="inlineStr">
+        <is>
+          <t>3.1 REKAPITULASI &amp; MATRIKS KALKULASI SKS AKUMULATIF SEMESTER 1 – 8</t>
+        </is>
+      </c>
+      <c r="B198" s="4" t="n"/>
+      <c r="C198" s="4" t="n"/>
+      <c r="D198" s="4" t="n"/>
+      <c r="E198" s="4" t="n"/>
+      <c r="F198" s="5" t="n"/>
+    </row>
+    <row r="199" ht="26" customHeight="1">
+      <c r="A199" s="6" t="inlineStr">
+        <is>
+          <t>Semester</t>
+        </is>
+      </c>
+      <c r="B199" s="6" t="inlineStr">
+        <is>
+          <t>Jumlah MK</t>
+        </is>
+      </c>
+      <c r="C199" s="6" t="inlineStr">
+        <is>
+          <t>Beban SKS</t>
+        </is>
+      </c>
+      <c r="D199" s="6" t="inlineStr">
+        <is>
+          <t>SKS Kumulatif</t>
+        </is>
+      </c>
+      <c r="E199" s="6" t="inlineStr">
+        <is>
+          <t>Persentase</t>
+        </is>
+      </c>
+      <c r="F199" s="6" t="inlineStr">
+        <is>
+          <t>Tahapan Akademik &amp; Karakteristik</t>
+        </is>
+      </c>
+    </row>
+    <row r="200" ht="16" customHeight="1">
+      <c r="A200" s="7" t="inlineStr">
+        <is>
+          <t>**Sem 1**</t>
+        </is>
+      </c>
+      <c r="B200" s="8" t="inlineStr">
+        <is>
+          <t>8 MK</t>
+        </is>
+      </c>
+      <c r="C200" s="8" t="inlineStr">
+        <is>
+          <t>19 SKS</t>
+        </is>
+      </c>
+      <c r="D200" s="8" t="inlineStr">
+        <is>
+          <t>19 SKS</t>
+        </is>
+      </c>
+      <c r="E200" s="7" t="inlineStr">
+        <is>
+          <t>13,0%</t>
+        </is>
+      </c>
+      <c r="F200" s="7" t="inlineStr">
+        <is>
+          <t>Tahap Fondasi Sains, Algoritma &amp; Logika</t>
+        </is>
+      </c>
+    </row>
+    <row r="201" ht="16" customHeight="1">
+      <c r="A201" s="9" t="inlineStr">
+        <is>
+          <t>**Sem 2**</t>
+        </is>
+      </c>
+      <c r="B201" s="10" t="inlineStr">
+        <is>
+          <t>8 MK</t>
+        </is>
+      </c>
+      <c r="C201" s="10" t="inlineStr">
+        <is>
+          <t>20 SKS</t>
+        </is>
+      </c>
+      <c r="D201" s="10" t="inlineStr">
+        <is>
+          <t>39 SKS</t>
+        </is>
+      </c>
+      <c r="E201" s="9" t="inlineStr">
+        <is>
+          <t>13,7%</t>
+        </is>
+      </c>
+      <c r="F201" s="9" t="inlineStr">
+        <is>
+          <t>Tahap Fondasi Data, Matdis &amp; OOP</t>
+        </is>
+      </c>
+    </row>
+    <row r="202" ht="16" customHeight="1">
+      <c r="A202" s="7" t="inlineStr">
+        <is>
+          <t>**Sem 3**</t>
+        </is>
+      </c>
+      <c r="B202" s="8" t="inlineStr">
+        <is>
+          <t>7 MK</t>
+        </is>
+      </c>
+      <c r="C202" s="8" t="inlineStr">
+        <is>
+          <t>20 SKS</t>
+        </is>
+      </c>
+      <c r="D202" s="8" t="inlineStr">
+        <is>
+          <t>59 SKS</t>
+        </is>
+      </c>
+      <c r="E202" s="7" t="inlineStr">
+        <is>
+          <t>13,7%</t>
+        </is>
+      </c>
+      <c r="F202" s="7" t="inlineStr">
+        <is>
+          <t>Tahap Penguatan Core RPL, OS &amp; Jaringan</t>
+        </is>
+      </c>
+    </row>
+    <row r="203" ht="16" customHeight="1">
+      <c r="A203" s="9" t="inlineStr">
+        <is>
+          <t>**Sem 4**</t>
+        </is>
+      </c>
+      <c r="B203" s="10" t="inlineStr">
+        <is>
+          <t>8 MK</t>
+        </is>
+      </c>
+      <c r="C203" s="10" t="inlineStr">
+        <is>
+          <t>21 SKS</t>
+        </is>
+      </c>
+      <c r="D203" s="10" t="inlineStr">
+        <is>
+          <t>80 SKS</t>
+        </is>
+      </c>
+      <c r="E203" s="9" t="inlineStr">
+        <is>
+          <t>14,4%</t>
+        </is>
+      </c>
+      <c r="F203" s="9" t="inlineStr">
+        <is>
+          <t>Tahap Penguatan Core AI/ML, NLP &amp; Cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="204" ht="16" customHeight="1">
+      <c r="A204" s="7" t="inlineStr">
+        <is>
+          <t>**Sem 5**</t>
+        </is>
+      </c>
+      <c r="B204" s="8" t="inlineStr">
+        <is>
+          <t>7 MK</t>
+        </is>
+      </c>
+      <c r="C204" s="8" t="inlineStr">
+        <is>
+          <t>21 SKS</t>
+        </is>
+      </c>
+      <c r="D204" s="8" t="inlineStr">
+        <is>
+          <t>101 SKS</t>
+        </is>
+      </c>
+      <c r="E204" s="7" t="inlineStr">
+        <is>
+          <t>14,4%</t>
+        </is>
+      </c>
+      <c r="F204" s="7" t="inlineStr">
+        <is>
+          <t>Tahap Spesialisasi Keamanan Lanjut &amp; IoT</t>
+        </is>
+      </c>
+    </row>
+    <row r="205" ht="16" customHeight="1">
+      <c r="A205" s="9" t="inlineStr">
+        <is>
+          <t>**Sem 6**</t>
+        </is>
+      </c>
+      <c r="B205" s="10" t="inlineStr">
+        <is>
+          <t>7 MK</t>
+        </is>
+      </c>
+      <c r="C205" s="10" t="inlineStr">
+        <is>
+          <t>19 SKS</t>
+        </is>
+      </c>
+      <c r="D205" s="10" t="inlineStr">
+        <is>
+          <t>120 SKS</t>
+        </is>
+      </c>
+      <c r="E205" s="9" t="inlineStr">
+        <is>
+          <t>13,0%</t>
+        </is>
+      </c>
+      <c r="F205" s="9" t="inlineStr">
+        <is>
+          <t>Tahap Spesialisasi Deep Learning &amp; Platform Eng</t>
+        </is>
+      </c>
+    </row>
+    <row r="206" ht="16" customHeight="1">
+      <c r="A206" s="7" t="inlineStr">
+        <is>
+          <t>**Sem 7**</t>
+        </is>
+      </c>
+      <c r="B206" s="8" t="inlineStr">
+        <is>
+          <t>7 MK</t>
+        </is>
+      </c>
+      <c r="C206" s="8" t="inlineStr">
+        <is>
+          <t>20 SKS</t>
+        </is>
+      </c>
+      <c r="D206" s="8" t="inlineStr">
+        <is>
+          <t>140 SKS</t>
+        </is>
+      </c>
+      <c r="E206" s="7" t="inlineStr">
+        <is>
+          <t>13,7%</t>
+        </is>
+      </c>
+      <c r="F206" s="7" t="inlineStr">
+        <is>
+          <t>Tahap Integrasi Capstone, PKL &amp; Sempro</t>
+        </is>
+      </c>
+    </row>
+    <row r="207" ht="16" customHeight="1">
+      <c r="A207" s="9" t="inlineStr">
+        <is>
+          <t>**Sem 8**</t>
+        </is>
+      </c>
+      <c r="B207" s="10" t="inlineStr">
+        <is>
+          <t>1 MK</t>
+        </is>
+      </c>
+      <c r="C207" s="10" t="inlineStr">
+        <is>
+          <t>6 SKS</t>
+        </is>
+      </c>
+      <c r="D207" s="10" t="inlineStr">
+        <is>
+          <t>146 SKS</t>
+        </is>
+      </c>
+      <c r="E207" s="9" t="inlineStr">
+        <is>
+          <t>4,1%</t>
+        </is>
+      </c>
+      <c r="F207" s="9" t="inlineStr">
+        <is>
+          <t>Tahap Penyelesaian Skripsi / Non-Skripsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="208" ht="16" customHeight="1">
+      <c r="A208" s="7" t="inlineStr">
+        <is>
+          <t>**TOTAL**</t>
+        </is>
+      </c>
+      <c r="B208" s="7" t="inlineStr">
+        <is>
+          <t>**55 MK**</t>
+        </is>
+      </c>
+      <c r="C208" s="7" t="inlineStr">
+        <is>
+          <t>**146 SKS**</t>
+        </is>
+      </c>
+      <c r="D208" s="7" t="inlineStr">
+        <is>
+          <t>**146 SKS**</t>
+        </is>
+      </c>
+      <c r="E208" s="7" t="inlineStr">
+        <is>
+          <t>**100,0%**</t>
+        </is>
+      </c>
+      <c r="F208" s="7" t="inlineStr">
+        <is>
+          <t>**Paket Lulus Tepat Waktu (4 Tahun)**</t>
+        </is>
+      </c>
+    </row>
+    <row r="209"/>
+    <row r="210" ht="20" customHeight="1">
+      <c r="A210" s="3" t="inlineStr">
+        <is>
+          <t>3 PEMINATAN SPESIALISASI KEAHLIAN SISTEKIN</t>
+        </is>
+      </c>
+      <c r="B210" s="4" t="n"/>
+      <c r="C210" s="4" t="n"/>
+      <c r="D210" s="4" t="n"/>
+      <c r="E210" s="4" t="n"/>
+      <c r="F210" s="5" t="n"/>
+    </row>
+    <row r="211" ht="26" customHeight="1">
+      <c r="A211" s="6" t="inlineStr">
+        <is>
+          <t>Peminatan</t>
+        </is>
+      </c>
+      <c r="B211" s="6" t="inlineStr">
+        <is>
+          <t>Basis Profil (PL)</t>
+        </is>
+      </c>
+      <c r="C211" s="6" t="inlineStr">
+        <is>
+          <t>Mata Kuliah Pilihan (@ 3 SKS)</t>
+        </is>
+      </c>
+    </row>
+    <row r="212" ht="16" customHeight="1">
+      <c r="A212" s="7" t="inlineStr">
+        <is>
+          <t>**P1: Integrated Smart Systems** *(Flagship)*</t>
+        </is>
+      </c>
+      <c r="B212" s="7" t="inlineStr">
+        <is>
+          <t>**PL-1:** Intelligent IS &amp; Data/AI Engineer</t>
+        </is>
+      </c>
+      <c r="C212" s="7" t="inlineStr">
+        <is>
+          <t>1. `STA-01` Decision Support Systems (+P, Sem 5)&lt;br&gt;2. `STA-02` Computational Methods &amp; Numerics (+P, Sem 6)&lt;br&gt;3. `STA-03` Intelligent Agent Systems (+P, Sem 6)&lt;br&gt;4. `STA-04` MLOps and AI Pipeline (+P, Sem 7)&lt;br&gt;5. `STA-05` Conversational AI &amp; Assistant (+P, Sem 7)&lt;br&gt;6. `STA-06` Smart Surveillance &amp; IoT Analytics (+P, Sem 7)</t>
+        </is>
+      </c>
+    </row>
+    <row r="213" ht="16" customHeight="1">
+      <c r="A213" s="9" t="inlineStr">
+        <is>
           <t>**P2: Cloud Infrastructure &amp; Cybersecurity** *(Volume)*</t>
         </is>
       </c>
-      <c r="B191" s="9" t="inlineStr">
+      <c r="B213" s="9" t="inlineStr">
         <is>
           <t>**PL-2:** Cloud, Cyber &amp; Smart Systems Integrator</t>
         </is>
       </c>
-      <c r="C191" s="9" t="inlineStr">
+      <c r="C213" s="9" t="inlineStr">
         <is>
           <t>1. `STB-01` Network Security &amp; Digital Forensics (+P, Sem 5)&lt;br&gt;2. `STB-02` Cloud Architecture &amp; DevOps (+P, Sem 6)&lt;br&gt;3. `STB-03` Cybersecurity Risk Management (Teori, Sem 6)&lt;br&gt;4. `STB-04` IT Governance &amp; Compliance COBIT 2019 (Teori, Sem 7)&lt;br&gt;5. `STB-05` IT Service Management ITIL 4 (Teori, Sem 7)&lt;br&gt;6. `STB-06` Enterprise Architecture TOGAF (Teori, Sem 7)</t>
         </is>
       </c>
     </row>
-    <row r="192" ht="16" customHeight="1">
-      <c r="A192" s="7" t="inlineStr">
+    <row r="214" ht="16" customHeight="1">
+      <c r="A214" s="7" t="inlineStr">
         <is>
           <t>**P3: Digital Platform Engineering** *(Niche &amp; Techno)*</t>
         </is>
       </c>
-      <c r="B192" s="7" t="inlineStr">
+      <c r="B214" s="7" t="inlineStr">
         <is>
           <t>**PL-3:** UI/UX Designer &amp; Platform Engineer</t>
         </is>
       </c>
-      <c r="C192" s="7" t="inlineStr">
+      <c r="C214" s="7" t="inlineStr">
         <is>
           <t>1. `STC-01` UX Research &amp; Design (+P, Sem 5)&lt;br&gt;2. `STC-02` Rekayasa &amp; Otomasi Proses Bisnis (+P, Sem 6)&lt;br&gt;3. `STC-03` Rekayasa Aplikasi Industri Vertikal (+P, Sem 6)&lt;br&gt;4. `STC-04` Immersive Media &amp; XR Development (+P, Sem 7)&lt;br&gt;5. `STC-05` SaaS Architecture &amp; Multi-Tenancy (+P, Sem 7)&lt;br&gt;6. `STC-06` Digital Product Management (Teori, Sem 7)</t>
         </is>
       </c>
     </row>
+    <row r="215"/>
+    <row r="216" ht="20" customHeight="1">
+      <c r="A216" s="3" t="inlineStr">
+        <is>
+          <t>4.1 PEMINATAN 1: INTEGRATED SMART SYSTEMS (FLAGSHIP — 6 MK / 18 SKS)</t>
+        </is>
+      </c>
+      <c r="B216" s="4" t="n"/>
+      <c r="C216" s="4" t="n"/>
+      <c r="D216" s="4" t="n"/>
+      <c r="E216" s="4" t="n"/>
+      <c r="F216" s="4" t="n"/>
+      <c r="G216" s="4" t="n"/>
+      <c r="H216" s="5" t="n"/>
+    </row>
+    <row r="217" ht="26" customHeight="1">
+      <c r="A217" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B217" s="6" t="inlineStr">
+        <is>
+          <t>Kode MK</t>
+        </is>
+      </c>
+      <c r="C217" s="6" t="inlineStr">
+        <is>
+          <t>Nama Mata Kuliah</t>
+        </is>
+      </c>
+      <c r="D217" s="6" t="inlineStr">
+        <is>
+          <t>SKS</t>
+        </is>
+      </c>
+      <c r="E217" s="6" t="inlineStr">
+        <is>
+          <t>Tipe</t>
+        </is>
+      </c>
+      <c r="F217" s="6" t="inlineStr">
+        <is>
+          <t>Semester</t>
+        </is>
+      </c>
+      <c r="G217" s="6" t="inlineStr">
+        <is>
+          <t>Prasyarat Akademik</t>
+        </is>
+      </c>
+      <c r="H217" s="6" t="inlineStr">
+        <is>
+          <t>Bahan Kajian Utama</t>
+        </is>
+      </c>
+    </row>
+    <row r="218" ht="16" customHeight="1">
+      <c r="A218" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B218" s="8" t="inlineStr">
+        <is>
+          <t>`STA-01`</t>
+        </is>
+      </c>
+      <c r="C218" s="7" t="inlineStr">
+        <is>
+          <t>Decision Support Systems</t>
+        </is>
+      </c>
+      <c r="D218" s="8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E218" s="7" t="inlineStr">
+        <is>
+          <t>+P</t>
+        </is>
+      </c>
+      <c r="F218" s="7" t="inlineStr">
+        <is>
+          <t>Sem 5</t>
+        </is>
+      </c>
+      <c r="G218" s="7" t="inlineStr">
+        <is>
+          <t>`STI-307` Sistem Cerdas</t>
+        </is>
+      </c>
+      <c r="H218" s="7" t="inlineStr">
+        <is>
+          <t>BK-IS17 Business Analytics, AHP/TOPSIS</t>
+        </is>
+      </c>
+    </row>
+    <row r="219" ht="16" customHeight="1">
+      <c r="A219" s="10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B219" s="10" t="inlineStr">
+        <is>
+          <t>`STA-02`</t>
+        </is>
+      </c>
+      <c r="C219" s="9" t="inlineStr">
+        <is>
+          <t>Computational Methods and Numerics</t>
+        </is>
+      </c>
+      <c r="D219" s="10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E219" s="9" t="inlineStr">
+        <is>
+          <t>+P</t>
+        </is>
+      </c>
+      <c r="F219" s="9" t="inlineStr">
+        <is>
+          <t>Sem 6</t>
+        </is>
+      </c>
+      <c r="G219" s="9" t="inlineStr">
+        <is>
+          <t>`STI-102`, `STI-205` Aljabar Linear</t>
+        </is>
+      </c>
+      <c r="H219" s="9" t="inlineStr">
+        <is>
+          <t>BK-IS10 / BK-IT01 Komputasi Saintifik</t>
+        </is>
+      </c>
+    </row>
+    <row r="220" ht="16" customHeight="1">
+      <c r="A220" s="8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B220" s="8" t="inlineStr">
+        <is>
+          <t>`STA-03`</t>
+        </is>
+      </c>
+      <c r="C220" s="7" t="inlineStr">
+        <is>
+          <t>Intelligent Agent Systems</t>
+        </is>
+      </c>
+      <c r="D220" s="8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E220" s="7" t="inlineStr">
+        <is>
+          <t>+P</t>
+        </is>
+      </c>
+      <c r="F220" s="7" t="inlineStr">
+        <is>
+          <t>Sem 6</t>
+        </is>
+      </c>
+      <c r="G220" s="7" t="inlineStr">
+        <is>
+          <t>`STI-307` Sistem Cerdas</t>
+        </is>
+      </c>
+      <c r="H220" s="7" t="inlineStr">
+        <is>
+          <t>BK-IT02 Multi-Agent Systems, Reinforcement</t>
+        </is>
+      </c>
+    </row>
+    <row r="221" ht="16" customHeight="1">
+      <c r="A221" s="10" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B221" s="10" t="inlineStr">
+        <is>
+          <t>`STA-04`</t>
+        </is>
+      </c>
+      <c r="C221" s="9" t="inlineStr">
+        <is>
+          <t>MLOps and AI Pipeline</t>
+        </is>
+      </c>
+      <c r="D221" s="10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E221" s="9" t="inlineStr">
+        <is>
+          <t>+P</t>
+        </is>
+      </c>
+      <c r="F221" s="9" t="inlineStr">
+        <is>
+          <t>Sem 7</t>
+        </is>
+      </c>
+      <c r="G221" s="9" t="inlineStr">
+        <is>
+          <t>`STI-413`, `STI-624` Integrasi AI</t>
+        </is>
+      </c>
+      <c r="H221" s="9" t="inlineStr">
+        <is>
+          <t>BK-IS18 Machine Learning Engineering</t>
+        </is>
+      </c>
+    </row>
+    <row r="222" ht="16" customHeight="1">
+      <c r="A222" s="8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B222" s="8" t="inlineStr">
+        <is>
+          <t>`STA-05`</t>
+        </is>
+      </c>
+      <c r="C222" s="7" t="inlineStr">
+        <is>
+          <t>Conversational AI and Intelligent Assistant</t>
+        </is>
+      </c>
+      <c r="D222" s="8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E222" s="7" t="inlineStr">
+        <is>
+          <t>+P</t>
+        </is>
+      </c>
+      <c r="F222" s="7" t="inlineStr">
+        <is>
+          <t>Sem 7</t>
+        </is>
+      </c>
+      <c r="G222" s="7" t="inlineStr">
+        <is>
+          <t>`STI-413`, `STI-416` Web Back End</t>
+        </is>
+      </c>
+      <c r="H222" s="7" t="inlineStr">
+        <is>
+          <t>BK-IT02 LLM, RAG Architecture, Prompt Eng</t>
+        </is>
+      </c>
+    </row>
+    <row r="223" ht="16" customHeight="1">
+      <c r="A223" s="10" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B223" s="10" t="inlineStr">
+        <is>
+          <t>`STA-06`</t>
+        </is>
+      </c>
+      <c r="C223" s="9" t="inlineStr">
+        <is>
+          <t>Smart Surveillance and IoT Analytics</t>
+        </is>
+      </c>
+      <c r="D223" s="10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E223" s="9" t="inlineStr">
+        <is>
+          <t>+P</t>
+        </is>
+      </c>
+      <c r="F223" s="9" t="inlineStr">
+        <is>
+          <t>Sem 7</t>
+        </is>
+      </c>
+      <c r="G223" s="9" t="inlineStr">
+        <is>
+          <t>`STI-626`, `STI-521` IoT</t>
+        </is>
+      </c>
+      <c r="H223" s="9" t="inlineStr">
+        <is>
+          <t>BK-IT02 Video Analytics, Edge AI, Vision</t>
+        </is>
+      </c>
+    </row>
+    <row r="224"/>
+    <row r="225" ht="20" customHeight="1">
+      <c r="A225" s="3" t="inlineStr">
+        <is>
+          <t>4.2 PEMINATAN 2: CLOUD INFRASTRUCTURE &amp; CYBERSECURITY (VOLUME — 6 MK / 18 SKS)</t>
+        </is>
+      </c>
+      <c r="B225" s="4" t="n"/>
+      <c r="C225" s="4" t="n"/>
+      <c r="D225" s="4" t="n"/>
+      <c r="E225" s="4" t="n"/>
+      <c r="F225" s="4" t="n"/>
+      <c r="G225" s="4" t="n"/>
+      <c r="H225" s="5" t="n"/>
+    </row>
+    <row r="226" ht="26" customHeight="1">
+      <c r="A226" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B226" s="6" t="inlineStr">
+        <is>
+          <t>Kode MK</t>
+        </is>
+      </c>
+      <c r="C226" s="6" t="inlineStr">
+        <is>
+          <t>Nama Mata Kuliah</t>
+        </is>
+      </c>
+      <c r="D226" s="6" t="inlineStr">
+        <is>
+          <t>SKS</t>
+        </is>
+      </c>
+      <c r="E226" s="6" t="inlineStr">
+        <is>
+          <t>Tipe</t>
+        </is>
+      </c>
+      <c r="F226" s="6" t="inlineStr">
+        <is>
+          <t>Semester</t>
+        </is>
+      </c>
+      <c r="G226" s="6" t="inlineStr">
+        <is>
+          <t>Prasyarat Akademik</t>
+        </is>
+      </c>
+      <c r="H226" s="6" t="inlineStr">
+        <is>
+          <t>Bahan Kajian Utama</t>
+        </is>
+      </c>
+    </row>
+    <row r="227" ht="16" customHeight="1">
+      <c r="A227" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B227" s="8" t="inlineStr">
+        <is>
+          <t>`STB-01`</t>
+        </is>
+      </c>
+      <c r="C227" s="7" t="inlineStr">
+        <is>
+          <t>Network Security and Digital Forensics</t>
+        </is>
+      </c>
+      <c r="D227" s="8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E227" s="7" t="inlineStr">
+        <is>
+          <t>+P</t>
+        </is>
+      </c>
+      <c r="F227" s="7" t="inlineStr">
+        <is>
+          <t>Sem 5</t>
+        </is>
+      </c>
+      <c r="G227" s="7" t="inlineStr">
+        <is>
+          <t>`STI-312`, `STI-418` Dasar Keamanan</t>
+        </is>
+      </c>
+      <c r="H227" s="7" t="inlineStr">
+        <is>
+          <t>BK-IT06 Cyber Defense, Forensik Jaringan</t>
+        </is>
+      </c>
+    </row>
+    <row r="228" ht="16" customHeight="1">
+      <c r="A228" s="10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B228" s="10" t="inlineStr">
+        <is>
+          <t>`STB-02`</t>
+        </is>
+      </c>
+      <c r="C228" s="9" t="inlineStr">
+        <is>
+          <t>Cloud Architecture &amp; DevOps</t>
+        </is>
+      </c>
+      <c r="D228" s="10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E228" s="9" t="inlineStr">
+        <is>
+          <t>+P</t>
+        </is>
+      </c>
+      <c r="F228" s="9" t="inlineStr">
+        <is>
+          <t>Sem 6</t>
+        </is>
+      </c>
+      <c r="G228" s="9" t="inlineStr">
+        <is>
+          <t>`STI-417` Komputasi Awan</t>
+        </is>
+      </c>
+      <c r="H228" s="9" t="inlineStr">
+        <is>
+          <t>BK-IT05 Cloud Systems, CI/CD, Kubernetes</t>
+        </is>
+      </c>
+    </row>
+    <row r="229" ht="16" customHeight="1">
+      <c r="A229" s="8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B229" s="8" t="inlineStr">
+        <is>
+          <t>`STB-03`</t>
+        </is>
+      </c>
+      <c r="C229" s="7" t="inlineStr">
+        <is>
+          <t>Cybersecurity Risk Management</t>
+        </is>
+      </c>
+      <c r="D229" s="8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E229" s="7" t="inlineStr">
+        <is>
+          <t>Teori</t>
+        </is>
+      </c>
+      <c r="F229" s="7" t="inlineStr">
+        <is>
+          <t>Sem 6</t>
+        </is>
+      </c>
+      <c r="G229" s="7" t="inlineStr">
+        <is>
+          <t>`STI-418` Dasar Keamanan Informasi</t>
+        </is>
+      </c>
+      <c r="H229" s="7" t="inlineStr">
+        <is>
+          <t>BK-IS06 Risk Management, ISO 27005, NIST</t>
+        </is>
+      </c>
+    </row>
+    <row r="230" ht="16" customHeight="1">
+      <c r="A230" s="10" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B230" s="10" t="inlineStr">
+        <is>
+          <t>`STB-04`</t>
+        </is>
+      </c>
+      <c r="C230" s="9" t="inlineStr">
+        <is>
+          <t>IT Governance &amp; Compliance (COBIT 2019)</t>
+        </is>
+      </c>
+      <c r="D230" s="10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E230" s="9" t="inlineStr">
+        <is>
+          <t>Teori</t>
+        </is>
+      </c>
+      <c r="F230" s="9" t="inlineStr">
+        <is>
+          <t>Sem 7</t>
+        </is>
+      </c>
+      <c r="G230" s="9" t="inlineStr">
+        <is>
+          <t>`STI-101` Pengantar Sistem &amp; TI</t>
+        </is>
+      </c>
+      <c r="H230" s="9" t="inlineStr">
+        <is>
+          <t>BK-IS07 IT Governance, COBIT 2019 Focus</t>
+        </is>
+      </c>
+    </row>
+    <row r="231" ht="16" customHeight="1">
+      <c r="A231" s="8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B231" s="8" t="inlineStr">
+        <is>
+          <t>`STB-05`</t>
+        </is>
+      </c>
+      <c r="C231" s="7" t="inlineStr">
+        <is>
+          <t>IT Service Management (ITIL 4)</t>
+        </is>
+      </c>
+      <c r="D231" s="8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E231" s="7" t="inlineStr">
+        <is>
+          <t>Teori</t>
+        </is>
+      </c>
+      <c r="F231" s="7" t="inlineStr">
+        <is>
+          <t>Sem 7</t>
+        </is>
+      </c>
+      <c r="G231" s="7" t="inlineStr">
+        <is>
+          <t>`STI-101` Pengantar Sistem &amp; TI</t>
+        </is>
+      </c>
+      <c r="H231" s="7" t="inlineStr">
+        <is>
+          <t>BK-IS08 Service Management, ITIL 4 Foundation</t>
+        </is>
+      </c>
+    </row>
+    <row r="232" ht="16" customHeight="1">
+      <c r="A232" s="10" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B232" s="10" t="inlineStr">
+        <is>
+          <t>`STB-06`</t>
+        </is>
+      </c>
+      <c r="C232" s="9" t="inlineStr">
+        <is>
+          <t>Enterprise Architecture (TOGAF)</t>
+        </is>
+      </c>
+      <c r="D232" s="10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E232" s="9" t="inlineStr">
+        <is>
+          <t>Teori</t>
+        </is>
+      </c>
+      <c r="F232" s="9" t="inlineStr">
+        <is>
+          <t>Sem 7</t>
+        </is>
+      </c>
+      <c r="G232" s="9" t="inlineStr">
+        <is>
+          <t>`STI-306` Analisis &amp; Perancangan SI</t>
+        </is>
+      </c>
+      <c r="H232" s="9" t="inlineStr">
+        <is>
+          <t>BK-IS04 Enterprise Architecture, TOGAF Standard</t>
+        </is>
+      </c>
+    </row>
+    <row r="233"/>
+    <row r="234" ht="20" customHeight="1">
+      <c r="A234" s="3" t="inlineStr">
+        <is>
+          <t>4.3 PEMINATAN 3: DIGITAL PLATFORM ENGINEERING (NICHE &amp; TECHNO — 6 MK / 18 SKS)</t>
+        </is>
+      </c>
+      <c r="B234" s="4" t="n"/>
+      <c r="C234" s="4" t="n"/>
+      <c r="D234" s="4" t="n"/>
+      <c r="E234" s="4" t="n"/>
+      <c r="F234" s="4" t="n"/>
+      <c r="G234" s="4" t="n"/>
+      <c r="H234" s="5" t="n"/>
+    </row>
+    <row r="235" ht="26" customHeight="1">
+      <c r="A235" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B235" s="6" t="inlineStr">
+        <is>
+          <t>Kode MK</t>
+        </is>
+      </c>
+      <c r="C235" s="6" t="inlineStr">
+        <is>
+          <t>Nama Mata Kuliah</t>
+        </is>
+      </c>
+      <c r="D235" s="6" t="inlineStr">
+        <is>
+          <t>SKS</t>
+        </is>
+      </c>
+      <c r="E235" s="6" t="inlineStr">
+        <is>
+          <t>Tipe</t>
+        </is>
+      </c>
+      <c r="F235" s="6" t="inlineStr">
+        <is>
+          <t>Semester</t>
+        </is>
+      </c>
+      <c r="G235" s="6" t="inlineStr">
+        <is>
+          <t>Prasyarat Akademik</t>
+        </is>
+      </c>
+      <c r="H235" s="6" t="inlineStr">
+        <is>
+          <t>Bahan Kajian Utama</t>
+        </is>
+      </c>
+    </row>
+    <row r="236" ht="16" customHeight="1">
+      <c r="A236" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B236" s="8" t="inlineStr">
+        <is>
+          <t>`STC-01`</t>
+        </is>
+      </c>
+      <c r="C236" s="7" t="inlineStr">
+        <is>
+          <t>User Experience Research &amp; Design</t>
+        </is>
+      </c>
+      <c r="D236" s="8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E236" s="7" t="inlineStr">
+        <is>
+          <t>+P</t>
+        </is>
+      </c>
+      <c r="F236" s="7" t="inlineStr">
+        <is>
+          <t>Sem 5</t>
+        </is>
+      </c>
+      <c r="G236" s="7" t="inlineStr">
+        <is>
+          <t>`STI-308` UI/UX Design &amp; Prototyping</t>
+        </is>
+      </c>
+      <c r="H236" s="7" t="inlineStr">
+        <is>
+          <t>BK-IS13 Human-Centered Design, Usability</t>
+        </is>
+      </c>
+    </row>
+    <row r="237" ht="16" customHeight="1">
+      <c r="A237" s="10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B237" s="10" t="inlineStr">
+        <is>
+          <t>`STC-02`</t>
+        </is>
+      </c>
+      <c r="C237" s="9" t="inlineStr">
+        <is>
+          <t>Rekayasa &amp; Otomasi Proses Bisnis (BPA)</t>
+        </is>
+      </c>
+      <c r="D237" s="10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E237" s="9" t="inlineStr">
+        <is>
+          <t>+P</t>
+        </is>
+      </c>
+      <c r="F237" s="9" t="inlineStr">
+        <is>
+          <t>Sem 6</t>
+        </is>
+      </c>
+      <c r="G237" s="9" t="inlineStr">
+        <is>
+          <t>`STI-306` Analisis &amp; Perancangan SI</t>
+        </is>
+      </c>
+      <c r="H237" s="9" t="inlineStr">
+        <is>
+          <t>BK-IS09 Business Process, Workflow &amp; RPA</t>
+        </is>
+      </c>
+    </row>
+    <row r="238" ht="16" customHeight="1">
+      <c r="A238" s="8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B238" s="8" t="inlineStr">
+        <is>
+          <t>`STC-03`</t>
+        </is>
+      </c>
+      <c r="C238" s="7" t="inlineStr">
+        <is>
+          <t>Rekayasa Aplikasi Industri Vertikal (FinTech &amp; EdTech)</t>
+        </is>
+      </c>
+      <c r="D238" s="8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E238" s="7" t="inlineStr">
+        <is>
+          <t>+P</t>
+        </is>
+      </c>
+      <c r="F238" s="7" t="inlineStr">
+        <is>
+          <t>Sem 6</t>
+        </is>
+      </c>
+      <c r="G238" s="7" t="inlineStr">
+        <is>
+          <t>`STI-416` Web Back End Development</t>
+        </is>
+      </c>
+      <c r="H238" s="7" t="inlineStr">
+        <is>
+          <t>BK-IS05 Application Domains, Microservices</t>
+        </is>
+      </c>
+    </row>
+    <row r="239" ht="16" customHeight="1">
+      <c r="A239" s="10" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B239" s="10" t="inlineStr">
+        <is>
+          <t>`STC-04`</t>
+        </is>
+      </c>
+      <c r="C239" s="9" t="inlineStr">
+        <is>
+          <t>Immersive Media &amp; XR Development</t>
+        </is>
+      </c>
+      <c r="D239" s="10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E239" s="9" t="inlineStr">
+        <is>
+          <t>+P</t>
+        </is>
+      </c>
+      <c r="F239" s="9" t="inlineStr">
+        <is>
+          <t>Sem 7</t>
+        </is>
+      </c>
+      <c r="G239" s="9" t="inlineStr">
+        <is>
+          <t>`STI-311` Web Front End Development</t>
+        </is>
+      </c>
+      <c r="H239" s="9" t="inlineStr">
+        <is>
+          <t>BK-IT14 Computer Graphics, Unity/WebXR</t>
+        </is>
+      </c>
+    </row>
+    <row r="240" ht="16" customHeight="1">
+      <c r="A240" s="8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B240" s="8" t="inlineStr">
+        <is>
+          <t>`STC-05`</t>
+        </is>
+      </c>
+      <c r="C240" s="7" t="inlineStr">
+        <is>
+          <t>SaaS Architecture &amp; Multi-Tenancy</t>
+        </is>
+      </c>
+      <c r="D240" s="8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E240" s="7" t="inlineStr">
+        <is>
+          <t>+P</t>
+        </is>
+      </c>
+      <c r="F240" s="7" t="inlineStr">
+        <is>
+          <t>Sem 7</t>
+        </is>
+      </c>
+      <c r="G240" s="7" t="inlineStr">
+        <is>
+          <t>`STI-416` Web Back End Development</t>
+        </is>
+      </c>
+      <c r="H240" s="7" t="inlineStr">
+        <is>
+          <t>BK-IT08 Distributed Systems, Multi-Tenancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="241" ht="16" customHeight="1">
+      <c r="A241" s="10" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B241" s="10" t="inlineStr">
+        <is>
+          <t>`STC-06`</t>
+        </is>
+      </c>
+      <c r="C241" s="9" t="inlineStr">
+        <is>
+          <t>Digital Product Management &amp; Agile Practices</t>
+        </is>
+      </c>
+      <c r="D241" s="10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E241" s="9" t="inlineStr">
+        <is>
+          <t>Teori</t>
+        </is>
+      </c>
+      <c r="F241" s="9" t="inlineStr">
+        <is>
+          <t>Sem 7</t>
+        </is>
+      </c>
+      <c r="G241" s="9" t="inlineStr">
+        <is>
+          <t>`STI-523` Manajemen Proyek TI</t>
+        </is>
+      </c>
+      <c r="H241" s="9" t="inlineStr">
+        <is>
+          <t>BK-IS14 Product Management, Scrum, Lean</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="18">
+  <mergeCells count="22">
+    <mergeCell ref="A159:G159"/>
+    <mergeCell ref="A99:F99"/>
+    <mergeCell ref="A77:H77"/>
+    <mergeCell ref="A135:G135"/>
+    <mergeCell ref="A171:G171"/>
+    <mergeCell ref="A198:F198"/>
+    <mergeCell ref="A225:H225"/>
+    <mergeCell ref="A216:H216"/>
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A210:F210"/>
+    <mergeCell ref="A28:G28"/>
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A89:G89"/>
-    <mergeCell ref="A149:G149"/>
+    <mergeCell ref="A111:G111"/>
+    <mergeCell ref="A16:H16"/>
+    <mergeCell ref="A182:G182"/>
     <mergeCell ref="A45:G45"/>
-    <mergeCell ref="A124:G124"/>
-    <mergeCell ref="A16:H16"/>
+    <mergeCell ref="A123:G123"/>
+    <mergeCell ref="A146:G146"/>
+    <mergeCell ref="A234:H234"/>
+    <mergeCell ref="A193:G193"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A188:F188"/>
-    <mergeCell ref="A176:F176"/>
-    <mergeCell ref="A101:G101"/>
-    <mergeCell ref="A171:G171"/>
-    <mergeCell ref="A137:G137"/>
-    <mergeCell ref="A160:G160"/>
-    <mergeCell ref="A3:F3"/>
-    <mergeCell ref="A113:G113"/>
-    <mergeCell ref="A77:F77"/>
     <mergeCell ref="A7:F7"/>
-    <mergeCell ref="A28:G28"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/KURIKULUM2026_REVISI/005_STRUKTUR_KURIKULUM_8_SEMESTER_DAN_PEMINATAN.xlsx
+++ b/KURIKULUM2026_REVISI/005_STRUKTUR_KURIKULUM_8_SEMESTER_DAN_PEMINATAN.xlsx
@@ -3002,9 +3002,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="B79" s="8" t="inlineStr">
-        <is>
-          <t>`STA-01`</t>
+      <c r="B79" s="7" t="inlineStr">
+        <is>
+          <t>`STA-501`</t>
         </is>
       </c>
       <c r="C79" s="7" t="inlineStr">
@@ -3044,9 +3044,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="B80" s="10" t="inlineStr">
-        <is>
-          <t>`STA-02`</t>
+      <c r="B80" s="9" t="inlineStr">
+        <is>
+          <t>`STA-601`</t>
         </is>
       </c>
       <c r="C80" s="9" t="inlineStr">
@@ -3086,9 +3086,9 @@
           <t>3</t>
         </is>
       </c>
-      <c r="B81" s="8" t="inlineStr">
-        <is>
-          <t>`STA-03`</t>
+      <c r="B81" s="7" t="inlineStr">
+        <is>
+          <t>`STA-602`</t>
         </is>
       </c>
       <c r="C81" s="7" t="inlineStr">
@@ -3128,9 +3128,9 @@
           <t>4</t>
         </is>
       </c>
-      <c r="B82" s="10" t="inlineStr">
-        <is>
-          <t>`STA-04`</t>
+      <c r="B82" s="9" t="inlineStr">
+        <is>
+          <t>`STA-701`</t>
         </is>
       </c>
       <c r="C82" s="9" t="inlineStr">
@@ -3170,9 +3170,9 @@
           <t>5</t>
         </is>
       </c>
-      <c r="B83" s="8" t="inlineStr">
-        <is>
-          <t>`STA-05`</t>
+      <c r="B83" s="7" t="inlineStr">
+        <is>
+          <t>`STA-702`</t>
         </is>
       </c>
       <c r="C83" s="7" t="inlineStr">
@@ -3212,9 +3212,9 @@
           <t>6</t>
         </is>
       </c>
-      <c r="B84" s="10" t="inlineStr">
-        <is>
-          <t>`STA-06`</t>
+      <c r="B84" s="9" t="inlineStr">
+        <is>
+          <t>`STA-703`</t>
         </is>
       </c>
       <c r="C84" s="9" t="inlineStr">
@@ -3254,9 +3254,9 @@
           <t>7</t>
         </is>
       </c>
-      <c r="B85" s="8" t="inlineStr">
-        <is>
-          <t>`STB-01`</t>
+      <c r="B85" s="7" t="inlineStr">
+        <is>
+          <t>`STB-501`</t>
         </is>
       </c>
       <c r="C85" s="7" t="inlineStr">
@@ -3296,9 +3296,9 @@
           <t>8</t>
         </is>
       </c>
-      <c r="B86" s="10" t="inlineStr">
-        <is>
-          <t>`STB-02`</t>
+      <c r="B86" s="9" t="inlineStr">
+        <is>
+          <t>`STB-601`</t>
         </is>
       </c>
       <c r="C86" s="9" t="inlineStr">
@@ -3338,9 +3338,9 @@
           <t>9</t>
         </is>
       </c>
-      <c r="B87" s="8" t="inlineStr">
-        <is>
-          <t>`STB-03`</t>
+      <c r="B87" s="7" t="inlineStr">
+        <is>
+          <t>`STB-602`</t>
         </is>
       </c>
       <c r="C87" s="7" t="inlineStr">
@@ -3380,9 +3380,9 @@
           <t>10</t>
         </is>
       </c>
-      <c r="B88" s="10" t="inlineStr">
-        <is>
-          <t>`STB-04`</t>
+      <c r="B88" s="9" t="inlineStr">
+        <is>
+          <t>`STB-701`</t>
         </is>
       </c>
       <c r="C88" s="9" t="inlineStr">
@@ -3422,9 +3422,9 @@
           <t>11</t>
         </is>
       </c>
-      <c r="B89" s="8" t="inlineStr">
-        <is>
-          <t>`STB-05`</t>
+      <c r="B89" s="7" t="inlineStr">
+        <is>
+          <t>`STB-702`</t>
         </is>
       </c>
       <c r="C89" s="7" t="inlineStr">
@@ -3464,9 +3464,9 @@
           <t>12</t>
         </is>
       </c>
-      <c r="B90" s="10" t="inlineStr">
-        <is>
-          <t>`STB-06`</t>
+      <c r="B90" s="9" t="inlineStr">
+        <is>
+          <t>`STB-703`</t>
         </is>
       </c>
       <c r="C90" s="9" t="inlineStr">
@@ -3506,9 +3506,9 @@
           <t>13</t>
         </is>
       </c>
-      <c r="B91" s="8" t="inlineStr">
-        <is>
-          <t>`STC-01`</t>
+      <c r="B91" s="7" t="inlineStr">
+        <is>
+          <t>`STC-501`</t>
         </is>
       </c>
       <c r="C91" s="7" t="inlineStr">
@@ -3548,9 +3548,9 @@
           <t>14</t>
         </is>
       </c>
-      <c r="B92" s="10" t="inlineStr">
-        <is>
-          <t>`STC-02`</t>
+      <c r="B92" s="9" t="inlineStr">
+        <is>
+          <t>`STC-601`</t>
         </is>
       </c>
       <c r="C92" s="9" t="inlineStr">
@@ -3590,9 +3590,9 @@
           <t>15</t>
         </is>
       </c>
-      <c r="B93" s="8" t="inlineStr">
-        <is>
-          <t>`STC-03`</t>
+      <c r="B93" s="7" t="inlineStr">
+        <is>
+          <t>`STC-602`</t>
         </is>
       </c>
       <c r="C93" s="7" t="inlineStr">
@@ -3632,9 +3632,9 @@
           <t>16</t>
         </is>
       </c>
-      <c r="B94" s="10" t="inlineStr">
-        <is>
-          <t>`STC-04`</t>
+      <c r="B94" s="9" t="inlineStr">
+        <is>
+          <t>`STC-701`</t>
         </is>
       </c>
       <c r="C94" s="9" t="inlineStr">
@@ -3674,9 +3674,9 @@
           <t>17</t>
         </is>
       </c>
-      <c r="B95" s="8" t="inlineStr">
-        <is>
-          <t>`STC-05`</t>
+      <c r="B95" s="7" t="inlineStr">
+        <is>
+          <t>`STC-702`</t>
         </is>
       </c>
       <c r="C95" s="7" t="inlineStr">
@@ -3716,9 +3716,9 @@
           <t>18</t>
         </is>
       </c>
-      <c r="B96" s="10" t="inlineStr">
-        <is>
-          <t>`STC-06`</t>
+      <c r="B96" s="9" t="inlineStr">
+        <is>
+          <t>`STC-703`</t>
         </is>
       </c>
       <c r="C96" s="9" t="inlineStr">
@@ -7192,7 +7192,7 @@
       </c>
       <c r="C212" s="7" t="inlineStr">
         <is>
-          <t>1. `STA-01` Decision Support Systems (+P, Sem 5)&lt;br&gt;2. `STA-02` Computational Methods &amp; Numerics (+P, Sem 6)&lt;br&gt;3. `STA-03` Intelligent Agent Systems (+P, Sem 6)&lt;br&gt;4. `STA-04` MLOps and AI Pipeline (+P, Sem 7)&lt;br&gt;5. `STA-05` Conversational AI &amp; Assistant (+P, Sem 7)&lt;br&gt;6. `STA-06` Smart Surveillance &amp; IoT Analytics (+P, Sem 7)</t>
+          <t>1. `STA-501` Decision Support Systems (+P, Sem 5)&lt;br&gt;2. `STA-601` Computational Methods &amp; Numerics (+P, Sem 6)&lt;br&gt;3. `STA-602` Intelligent Agent Systems (+P, Sem 6)&lt;br&gt;4. `STA-701` MLOps and AI Pipeline (+P, Sem 7)&lt;br&gt;5. `STA-702` Conversational AI &amp; Assistant (+P, Sem 7)&lt;br&gt;6. `STA-703` Smart Surveillance &amp; IoT Analytics (+P, Sem 7)</t>
         </is>
       </c>
     </row>
@@ -7209,7 +7209,7 @@
       </c>
       <c r="C213" s="9" t="inlineStr">
         <is>
-          <t>1. `STB-01` Network Security &amp; Digital Forensics (+P, Sem 5)&lt;br&gt;2. `STB-02` Cloud Architecture &amp; DevOps (+P, Sem 6)&lt;br&gt;3. `STB-03` Cybersecurity Risk Management (Teori, Sem 6)&lt;br&gt;4. `STB-04` IT Governance &amp; Compliance COBIT 2019 (Teori, Sem 7)&lt;br&gt;5. `STB-05` IT Service Management ITIL 4 (Teori, Sem 7)&lt;br&gt;6. `STB-06` Enterprise Architecture TOGAF (Teori, Sem 7)</t>
+          <t>1. `STB-501` Network Security &amp; Digital Forensics (+P, Sem 5)&lt;br&gt;2. `STB-601` Cloud Architecture &amp; DevOps (+P, Sem 6)&lt;br&gt;3. `STB-602` Cybersecurity Risk Management (Teori, Sem 6)&lt;br&gt;4. `STB-701` IT Governance &amp; Compliance COBIT 2019 (Teori, Sem 7)&lt;br&gt;5. `STB-702` IT Service Management ITIL 4 (Teori, Sem 7)&lt;br&gt;6. `STB-703` Enterprise Architecture TOGAF (Teori, Sem 7)</t>
         </is>
       </c>
     </row>
@@ -7226,7 +7226,7 @@
       </c>
       <c r="C214" s="7" t="inlineStr">
         <is>
-          <t>1. `STC-01` UX Research &amp; Design (+P, Sem 5)&lt;br&gt;2. `STC-02` Rekayasa &amp; Otomasi Proses Bisnis (+P, Sem 6)&lt;br&gt;3. `STC-03` Rekayasa Aplikasi Industri Vertikal (+P, Sem 6)&lt;br&gt;4. `STC-04` Immersive Media &amp; XR Development (+P, Sem 7)&lt;br&gt;5. `STC-05` SaaS Architecture &amp; Multi-Tenancy (+P, Sem 7)&lt;br&gt;6. `STC-06` Digital Product Management (Teori, Sem 7)</t>
+          <t>1. `STC-501` UX Research &amp; Design (+P, Sem 5)&lt;br&gt;2. `STC-601` Rekayasa &amp; Otomasi Proses Bisnis (+P, Sem 6)&lt;br&gt;3. `STC-602` Rekayasa Aplikasi Industri Vertikal (+P, Sem 6)&lt;br&gt;4. `STC-701` Immersive Media &amp; XR Development (+P, Sem 7)&lt;br&gt;5. `STC-702` SaaS Architecture &amp; Multi-Tenancy (+P, Sem 7)&lt;br&gt;6. `STC-703` Digital Product Management (Teori, Sem 7)</t>
         </is>
       </c>
     </row>
@@ -7293,9 +7293,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="B218" s="8" t="inlineStr">
-        <is>
-          <t>`STA-01`</t>
+      <c r="B218" s="7" t="inlineStr">
+        <is>
+          <t>`STA-501`</t>
         </is>
       </c>
       <c r="C218" s="7" t="inlineStr">
@@ -7335,9 +7335,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="B219" s="10" t="inlineStr">
-        <is>
-          <t>`STA-02`</t>
+      <c r="B219" s="9" t="inlineStr">
+        <is>
+          <t>`STA-601`</t>
         </is>
       </c>
       <c r="C219" s="9" t="inlineStr">
@@ -7377,9 +7377,9 @@
           <t>3</t>
         </is>
       </c>
-      <c r="B220" s="8" t="inlineStr">
-        <is>
-          <t>`STA-03`</t>
+      <c r="B220" s="7" t="inlineStr">
+        <is>
+          <t>`STA-602`</t>
         </is>
       </c>
       <c r="C220" s="7" t="inlineStr">
@@ -7419,9 +7419,9 @@
           <t>4</t>
         </is>
       </c>
-      <c r="B221" s="10" t="inlineStr">
-        <is>
-          <t>`STA-04`</t>
+      <c r="B221" s="9" t="inlineStr">
+        <is>
+          <t>`STA-701`</t>
         </is>
       </c>
       <c r="C221" s="9" t="inlineStr">
@@ -7461,9 +7461,9 @@
           <t>5</t>
         </is>
       </c>
-      <c r="B222" s="8" t="inlineStr">
-        <is>
-          <t>`STA-05`</t>
+      <c r="B222" s="7" t="inlineStr">
+        <is>
+          <t>`STA-702`</t>
         </is>
       </c>
       <c r="C222" s="7" t="inlineStr">
@@ -7503,9 +7503,9 @@
           <t>6</t>
         </is>
       </c>
-      <c r="B223" s="10" t="inlineStr">
-        <is>
-          <t>`STA-06`</t>
+      <c r="B223" s="9" t="inlineStr">
+        <is>
+          <t>`STA-703`</t>
         </is>
       </c>
       <c r="C223" s="9" t="inlineStr">
@@ -7602,9 +7602,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="B227" s="8" t="inlineStr">
-        <is>
-          <t>`STB-01`</t>
+      <c r="B227" s="7" t="inlineStr">
+        <is>
+          <t>`STB-501`</t>
         </is>
       </c>
       <c r="C227" s="7" t="inlineStr">
@@ -7644,9 +7644,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="B228" s="10" t="inlineStr">
-        <is>
-          <t>`STB-02`</t>
+      <c r="B228" s="9" t="inlineStr">
+        <is>
+          <t>`STB-601`</t>
         </is>
       </c>
       <c r="C228" s="9" t="inlineStr">
@@ -7686,9 +7686,9 @@
           <t>3</t>
         </is>
       </c>
-      <c r="B229" s="8" t="inlineStr">
-        <is>
-          <t>`STB-03`</t>
+      <c r="B229" s="7" t="inlineStr">
+        <is>
+          <t>`STB-602`</t>
         </is>
       </c>
       <c r="C229" s="7" t="inlineStr">
@@ -7728,9 +7728,9 @@
           <t>4</t>
         </is>
       </c>
-      <c r="B230" s="10" t="inlineStr">
-        <is>
-          <t>`STB-04`</t>
+      <c r="B230" s="9" t="inlineStr">
+        <is>
+          <t>`STB-701`</t>
         </is>
       </c>
       <c r="C230" s="9" t="inlineStr">
@@ -7770,9 +7770,9 @@
           <t>5</t>
         </is>
       </c>
-      <c r="B231" s="8" t="inlineStr">
-        <is>
-          <t>`STB-05`</t>
+      <c r="B231" s="7" t="inlineStr">
+        <is>
+          <t>`STB-702`</t>
         </is>
       </c>
       <c r="C231" s="7" t="inlineStr">
@@ -7812,9 +7812,9 @@
           <t>6</t>
         </is>
       </c>
-      <c r="B232" s="10" t="inlineStr">
-        <is>
-          <t>`STB-06`</t>
+      <c r="B232" s="9" t="inlineStr">
+        <is>
+          <t>`STB-703`</t>
         </is>
       </c>
       <c r="C232" s="9" t="inlineStr">
@@ -7911,9 +7911,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="B236" s="8" t="inlineStr">
-        <is>
-          <t>`STC-01`</t>
+      <c r="B236" s="7" t="inlineStr">
+        <is>
+          <t>`STC-501`</t>
         </is>
       </c>
       <c r="C236" s="7" t="inlineStr">
@@ -7953,9 +7953,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="B237" s="10" t="inlineStr">
-        <is>
-          <t>`STC-02`</t>
+      <c r="B237" s="9" t="inlineStr">
+        <is>
+          <t>`STC-601`</t>
         </is>
       </c>
       <c r="C237" s="9" t="inlineStr">
@@ -7995,9 +7995,9 @@
           <t>3</t>
         </is>
       </c>
-      <c r="B238" s="8" t="inlineStr">
-        <is>
-          <t>`STC-03`</t>
+      <c r="B238" s="7" t="inlineStr">
+        <is>
+          <t>`STC-602`</t>
         </is>
       </c>
       <c r="C238" s="7" t="inlineStr">
@@ -8037,9 +8037,9 @@
           <t>4</t>
         </is>
       </c>
-      <c r="B239" s="10" t="inlineStr">
-        <is>
-          <t>`STC-04`</t>
+      <c r="B239" s="9" t="inlineStr">
+        <is>
+          <t>`STC-701`</t>
         </is>
       </c>
       <c r="C239" s="9" t="inlineStr">
@@ -8079,9 +8079,9 @@
           <t>5</t>
         </is>
       </c>
-      <c r="B240" s="8" t="inlineStr">
-        <is>
-          <t>`STC-05`</t>
+      <c r="B240" s="7" t="inlineStr">
+        <is>
+          <t>`STC-702`</t>
         </is>
       </c>
       <c r="C240" s="7" t="inlineStr">
@@ -8121,9 +8121,9 @@
           <t>6</t>
         </is>
       </c>
-      <c r="B241" s="10" t="inlineStr">
-        <is>
-          <t>`STC-06`</t>
+      <c r="B241" s="9" t="inlineStr">
+        <is>
+          <t>`STC-703`</t>
         </is>
       </c>
       <c r="C241" s="9" t="inlineStr">
